--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="556">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1198,11 +1198,11 @@
     <t>MedicationRequest.dosageInstruction</t>
   </si>
   <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-dosierung}
+    <t xml:space="preserve">Dosage
 </t>
   </si>
   <si>
-    <t>Angabe der Dosierinformationen.</t>
+    <t>Angabe der Dosierinformationen strukturiert oder als Freitext.</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -1211,10 +1211,70 @@
     <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:extension.value}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>Request.occurrence[x]</t>
   </si>
   <si>
     <t>see dosageInstruction mapping</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:otherDosage</t>
+  </si>
+  <si>
+    <t>otherDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-other-administration}
+</t>
+  </si>
+  <si>
+    <t>How the medication should be taken</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:timedDosage</t>
+  </si>
+  <si>
+    <t>timedDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-timed-administration}
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:frequencyDosage</t>
+  </si>
+  <si>
+    <t>frequencyDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-frequency-administration}
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:freitextDosage</t>
+  </si>
+  <si>
+    <t>freitextDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-freetext-administration}
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:standardDosage</t>
+  </si>
+  <si>
+    <t>standardDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-standard-administration}
+</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest</t>
@@ -2056,7 +2116,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO73"/>
+  <dimension ref="A1:AO78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
@@ -6774,13 +6834,13 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6836,16 +6896,14 @@
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>368</v>
@@ -6863,13 +6921,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6880,21 +6938,23 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>91</v>
@@ -6906,15 +6966,17 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6963,13 +7025,13 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
@@ -6978,13 +7040,13 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>379</v>
+        <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -6993,14 +7055,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>381</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>21</v>
       </c>
@@ -7009,10 +7073,10 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -7021,15 +7085,17 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -7078,46 +7144,48 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C44" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AG43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44" hidden="true">
-      <c r="A44" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7127,7 +7195,7 @@
         <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -7136,16 +7204,16 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>135</v>
+        <v>386</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>159</v>
+        <v>372</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7195,7 +7263,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7207,16 +7275,16 @@
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7225,16 +7293,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="D45" t="s" s="2">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7244,29 +7314,27 @@
         <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>135</v>
+        <v>389</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -7314,7 +7382,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7326,16 +7394,16 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>133</v>
+        <v>376</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7344,14 +7412,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="D46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7360,10 +7430,10 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -7372,16 +7442,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7431,13 +7501,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>396</v>
+        <v>368</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7446,13 +7516,13 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7461,12 +7531,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7474,13 +7544,13 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
@@ -7489,13 +7559,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7546,7 +7616,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7558,16 +7628,16 @@
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7578,21 +7648,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7604,17 +7674,15 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>135</v>
+        <v>400</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7663,19 +7731,19 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>21</v>
@@ -7684,7 +7752,7 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7695,14 +7763,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>392</v>
+        <v>156</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7715,26 +7783,24 @@
         <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="O49" t="s" s="2">
-        <v>160</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7782,7 +7848,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7803,7 +7869,7 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>133</v>
+        <v>404</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7814,42 +7880,46 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>21</v>
+        <v>410</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>405</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7897,19 +7967,19 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>21</v>
@@ -7918,7 +7988,7 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>408</v>
+        <v>133</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7929,10 +7999,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7943,7 +8013,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -7955,15 +8025,17 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -8012,7 +8084,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8033,7 +8105,7 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8044,10 +8116,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8058,7 +8130,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -8070,13 +8142,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8127,7 +8199,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8139,7 +8211,7 @@
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -8148,7 +8220,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8157,26 +8229,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
@@ -8185,20 +8257,18 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>418</v>
+        <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -8246,28 +8316,28 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>423</v>
+        <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8276,46 +8346,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>21</v>
+        <v>410</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I54" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I54" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>426</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8363,42 +8435,42 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>430</v>
+        <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>431</v>
+        <v>133</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>432</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8406,13 +8478,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
@@ -8421,13 +8493,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8478,7 +8550,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8496,24 +8568,24 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>436</v>
+        <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>438</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8524,7 +8596,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -8536,17 +8608,15 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8595,7 +8665,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8613,10 +8683,10 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>443</v>
+        <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8627,10 +8697,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8641,7 +8711,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -8653,13 +8723,13 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>382</v>
+        <v>428</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>383</v>
+        <v>433</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8710,7 +8780,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>385</v>
+        <v>432</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8722,7 +8792,7 @@
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -8731,7 +8801,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8740,26 +8810,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>21</v>
@@ -8768,18 +8838,20 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>135</v>
+        <v>436</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>388</v>
+        <v>437</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>389</v>
+        <v>438</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8815,40 +8887,40 @@
         <v>21</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>447</v>
+        <v>21</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>390</v>
+        <v>435</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>21</v>
+        <v>441</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>386</v>
+        <v>442</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8857,12 +8929,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8870,35 +8942,33 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8946,7 +9016,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8964,24 +9034,24 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>21</v>
+        <v>448</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8989,39 +9059,35 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>110</v>
+        <v>423</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>460</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q60" t="s" s="2">
-        <v>461</v>
-      </c>
+      <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
         <v>21</v>
       </c>
@@ -9041,13 +9107,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>462</v>
+        <v>21</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>463</v>
+        <v>21</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9065,7 +9131,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9083,24 +9149,24 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9111,7 +9177,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -9120,21 +9186,21 @@
         <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>382</v>
+        <v>428</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -9182,7 +9248,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9200,24 +9266,24 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>21</v>
+        <v>461</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>473</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9237,21 +9303,19 @@
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>104</v>
+        <v>400</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>475</v>
+        <v>401</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>476</v>
+        <v>402</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>477</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9299,7 +9363,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>478</v>
+        <v>403</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9308,10 +9372,10 @@
         <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>479</v>
+        <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
@@ -9320,32 +9384,32 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>480</v>
+        <v>404</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>473</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -9354,23 +9418,21 @@
         <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>482</v>
+        <v>406</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>483</v>
+        <v>407</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9406,31 +9468,31 @@
         <v>21</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>21</v>
+        <v>465</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>486</v>
+        <v>408</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
@@ -9439,21 +9501,21 @@
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>487</v>
+        <v>404</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>473</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9464,7 +9526,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
@@ -9473,19 +9535,23 @@
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>490</v>
+        <v>468</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>471</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9533,7 +9599,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9554,21 +9620,21 @@
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>492</v>
+        <v>473</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>21</v>
+        <v>474</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9579,32 +9645,36 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>376</v>
+        <v>110</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q65" s="2"/>
+      <c r="Q65" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="R65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9624,13 +9694,13 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>21</v>
+        <v>480</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>21</v>
+        <v>481</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -9648,7 +9718,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9666,24 +9736,24 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>21</v>
+        <v>484</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9703,19 +9773,21 @@
         <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>383</v>
+        <v>486</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>384</v>
+        <v>487</v>
       </c>
       <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9763,7 +9835,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>385</v>
+        <v>489</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9775,7 +9847,7 @@
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
@@ -9784,32 +9856,32 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>386</v>
+        <v>490</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>21</v>
+        <v>491</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9818,21 +9890,21 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>388</v>
+        <v>493</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9880,19 +9952,19 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>390</v>
+        <v>496</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>21</v>
+        <v>497</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>21</v>
@@ -9901,56 +9973,56 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>386</v>
+        <v>498</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>21</v>
+        <v>491</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>393</v>
+        <v>500</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>394</v>
+        <v>501</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>159</v>
+        <v>502</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>160</v>
+        <v>503</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9999,19 +10071,19 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>395</v>
+        <v>504</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
@@ -10020,21 +10092,21 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>133</v>
+        <v>505</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>21</v>
+        <v>491</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10042,10 +10114,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -10057,17 +10129,15 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -10092,34 +10162,34 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>501</v>
-      </c>
       <c r="AG69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>90</v>
@@ -10134,24 +10204,24 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>509</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10162,7 +10232,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -10174,13 +10244,13 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>183</v>
+        <v>394</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10207,13 +10277,13 @@
         <v>21</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>513</v>
+        <v>21</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>514</v>
+        <v>21</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -10231,7 +10301,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10249,24 +10319,24 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="AM70" t="s" s="2">
-        <v>516</v>
-      </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>517</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10277,7 +10347,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
@@ -10289,13 +10359,13 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>519</v>
+        <v>400</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>520</v>
+        <v>401</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>521</v>
+        <v>402</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10346,7 +10416,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>518</v>
+        <v>403</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10358,16 +10428,16 @@
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>522</v>
+        <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>515</v>
+        <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>523</v>
+        <v>404</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
@@ -10378,21 +10448,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>525</v>
+        <v>156</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>21</v>
@@ -10404,16 +10474,16 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>526</v>
+        <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>527</v>
+        <v>406</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>528</v>
+        <v>407</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>529</v>
+        <v>159</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10463,7 +10533,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>524</v>
+        <v>408</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10475,7 +10545,7 @@
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
@@ -10484,7 +10554,7 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>530</v>
+        <v>404</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
@@ -10495,44 +10565,46 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>21</v>
+        <v>410</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>532</v>
+        <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>533</v>
+        <v>411</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>534</v>
+        <v>412</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
       </c>
@@ -10580,7 +10652,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>531</v>
+        <v>413</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10592,26 +10664,607 @@
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK73" t="s" s="2">
+      <c r="AK74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AL73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM73" t="s" s="2">
+      <c r="B76" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K76" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AN73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO73" t="s" s="2">
+      <c r="L76" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO73">
+  <autoFilter ref="A1:AO78">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10621,7 +11274,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI72">
+  <conditionalFormatting sqref="A2:AI77">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$89</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3321" uniqueCount="626">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -720,35 +720,274 @@
     <t>https://termgit.elga.gv.at/ValueSet/elga-medikationrezeptart</t>
   </si>
   <si>
-    <t>MedicationRequest.priority</t>
-  </si>
-  <si>
-    <t>Priorität der geplanten Abgabe. Keine Verwendung in der geplanten Abgabe.</t>
-  </si>
-  <si>
-    <t>Indicates how quickly the Medication Request should be addressed with respect to other requests.</t>
-  </si>
-  <si>
-    <t>Identifies the level of importance to be assigned to actioning the request.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.priority</t>
-  </si>
-  <si>
-    <t>.priorityCode</t>
-  </si>
-  <si>
-    <t>FiveWs.grade</t>
-  </si>
-  <si>
-    <t>MedicationRequest.doNotPerform</t>
+    <t>MedicationRequest.category:recipetype.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.system</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/medikationrezeptart</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.version</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.code</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.display</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.userSelected</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.coding.userSelected</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.text</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>MedicationRequest.priority</t>
+  </si>
+  <si>
+    <t>Priorität der geplanten Abgabe. Keine Verwendung in der geplanten Abgabe.</t>
+  </si>
+  <si>
+    <t>Indicates how quickly the Medication Request should be addressed with respect to other requests.</t>
+  </si>
+  <si>
+    <t>Identifies the level of importance to be assigned to actioning the request.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.priority</t>
+  </si>
+  <si>
+    <t>.priorityCode</t>
+  </si>
+  <si>
+    <t>FiveWs.grade</t>
+  </si>
+  <si>
+    <t>MedicationRequest.doNotPerform</t>
   </si>
   <si>
     <t>Gibt an, ob die Geplante Abgabe untersagt ist. Keine Verwendung in der geplanten Abgabe.</t>
@@ -1299,32 +1538,7 @@
     <t>MedicationRequest.dispenseRequest.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>MedicationRequest.dispenseRequest.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.modifierExtension</t>
@@ -1508,9 +1722,6 @@
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.extension</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.value</t>
@@ -2116,7 +2327,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO78"/>
+  <dimension ref="A1:AO89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
@@ -4393,7 +4604,7 @@
         <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4404,7 +4615,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -4413,16 +4624,16 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>110</v>
+        <v>222</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4449,13 +4660,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -4473,7 +4684,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4485,10 +4696,10 @@
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
@@ -4497,7 +4708,7 @@
         <v>226</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>21</v>
@@ -4505,42 +4716,42 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>231</v>
-      </c>
       <c r="N21" t="s" s="2">
-        <v>232</v>
+        <v>159</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4578,31 +4789,31 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
@@ -4611,7 +4822,7 @@
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>21</v>
@@ -4622,7 +4833,7 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>234</v>
@@ -4633,10 +4844,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -4656,8 +4867,12 @@
       <c r="M22" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+      <c r="N22" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4705,13 +4920,13 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
@@ -4726,21 +4941,21 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4748,32 +4963,30 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4822,10 +5035,10 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>90</v>
@@ -4834,62 +5047,62 @@
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" hidden="true">
+      <c r="A24" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="B24" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>250</v>
+        <v>135</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>253</v>
+        <v>159</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4927,54 +5140,54 @@
         <v>21</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>254</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>255</v>
+        <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>258</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4982,10 +5195,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4994,21 +5207,23 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>260</v>
+        <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -5017,7 +5232,7 @@
         <v>21</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>21</v>
+        <v>253</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>21</v>
@@ -5056,7 +5271,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5071,27 +5286,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>264</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>266</v>
+        <v>21</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5102,7 +5317,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -5111,18 +5326,20 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>269</v>
+        <v>222</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -5171,13 +5388,13 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
@@ -5186,27 +5403,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5220,7 +5437,7 @@
         <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
@@ -5229,16 +5446,18 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>275</v>
+        <v>110</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -5262,13 +5481,11 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -5286,7 +5503,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5301,27 +5518,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>281</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5329,13 +5546,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -5344,16 +5561,18 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>284</v>
+        <v>222</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -5401,7 +5620,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5416,27 +5635,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>288</v>
+        <v>21</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5447,7 +5666,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -5456,19 +5675,23 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5516,7 +5739,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5531,27 +5754,27 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>293</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>295</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5562,7 +5785,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5574,18 +5797,20 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>236</v>
+        <v>293</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5609,13 +5834,13 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>299</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>300</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5633,7 +5858,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5648,27 +5873,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>301</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>21</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5688,16 +5913,16 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>304</v>
+        <v>110</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5724,13 +5949,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>21</v>
+        <v>303</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5748,7 +5973,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5763,16 +5988,16 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>21</v>
+        <v>305</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>21</v>
@@ -5780,10 +6005,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5800,22 +6025,22 @@
         <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>183</v>
+        <v>283</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5841,13 +6066,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>313</v>
+        <v>21</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>314</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5865,13 +6090,13 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
@@ -5880,27 +6105,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>315</v>
+        <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>316</v>
+        <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>318</v>
+        <v>21</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>319</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5911,7 +6136,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5920,20 +6145,18 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5982,13 +6205,13 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
@@ -5997,27 +6220,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>325</v>
+        <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AO33" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" hidden="true">
-      <c r="A34" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6025,13 +6248,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
@@ -6040,15 +6263,17 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -6097,13 +6322,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -6112,27 +6337,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
+        <v>324</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>21</v>
+        <v>327</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6140,13 +6365,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -6155,15 +6380,17 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>104</v>
+        <v>329</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -6212,13 +6439,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -6227,27 +6454,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>21</v>
+        <v>333</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>21</v>
+        <v>334</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>21</v>
+        <v>336</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6255,30 +6482,32 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6327,13 +6556,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -6342,27 +6571,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6370,33 +6599,31 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>345</v>
-      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -6444,13 +6671,13 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -6459,27 +6686,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6487,32 +6714,30 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>183</v>
+        <v>354</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6537,31 +6762,31 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>352</v>
+        <v>21</v>
       </c>
       <c r="Z38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6576,27 +6801,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>21</v>
+        <v>358</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6604,28 +6829,28 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6676,13 +6901,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6691,27 +6916,27 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>21</v>
+        <v>367</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6722,10 +6947,10 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -6734,13 +6959,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6791,13 +7016,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6806,16 +7031,16 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>366</v>
+        <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6823,10 +7048,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6834,31 +7059,31 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K41" t="s" s="2">
-        <v>369</v>
+        <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>370</v>
+        <v>315</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6884,35 +7109,37 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>21</v>
+        <v>378</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>21</v>
+        <v>379</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -6921,13 +7148,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6936,16 +7163,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6954,10 +7179,10 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
@@ -6966,17 +7191,15 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -7025,13 +7248,13 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
@@ -7040,31 +7263,29 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>21</v>
+        <v>387</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>21</v>
       </c>
@@ -7073,10 +7294,10 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -7085,16 +7306,16 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>383</v>
+        <v>183</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7120,13 +7341,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -7144,7 +7365,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7159,31 +7380,29 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>21</v>
+        <v>398</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>21</v>
       </c>
@@ -7195,7 +7414,7 @@
         <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -7204,16 +7423,16 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>372</v>
+        <v>403</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7263,7 +7482,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7278,31 +7497,29 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>21</v>
       </c>
@@ -7311,29 +7528,27 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K45" t="s" s="2">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7382,7 +7597,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>406</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7397,13 +7612,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>375</v>
+        <v>410</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7412,16 +7627,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7430,29 +7643,27 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K46" t="s" s="2">
-        <v>392</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>380</v>
+        <v>413</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7501,7 +7712,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>412</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7516,13 +7727,13 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7533,10 +7744,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7556,16 +7767,16 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7616,13 +7827,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7631,13 +7842,13 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7646,12 +7857,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7659,31 +7870,33 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>400</v>
+        <v>163</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7731,7 +7944,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7743,16 +7956,16 @@
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7763,21 +7976,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7789,16 +8002,16 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>159</v>
+        <v>430</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7824,13 +8037,13 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -7848,19 +8061,19 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
@@ -7869,7 +8082,7 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>404</v>
+        <v>433</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7880,46 +8093,42 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>410</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>435</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7967,7 +8176,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7979,16 +8188,16 @@
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>133</v>
+        <v>439</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7997,12 +8206,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8013,10 +8222,10 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
@@ -8025,17 +8234,15 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>394</v>
+        <v>441</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -8084,13 +8291,13 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -8099,13 +8306,13 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>21</v>
+        <v>444</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>21</v>
+        <v>445</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8116,10 +8323,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8127,13 +8334,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>21</v>
@@ -8142,15 +8349,17 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>401</v>
+        <v>449</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8187,40 +8396,38 @@
         <v>21</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>21</v>
+        <v>453</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>403</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>404</v>
+        <v>455</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8229,16 +8436,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="D53" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8248,7 +8457,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
@@ -8257,16 +8466,16 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>135</v>
+        <v>458</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>406</v>
+        <v>459</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>407</v>
+        <v>450</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>159</v>
+        <v>451</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8316,7 +8525,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8328,16 +8537,16 @@
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>404</v>
+        <v>455</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8346,16 +8555,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="D54" t="s" s="2">
-        <v>410</v>
+        <v>21</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8365,29 +8576,27 @@
         <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>462</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>411</v>
+        <v>459</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8435,7 +8644,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>413</v>
+        <v>447</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8447,16 +8656,16 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>133</v>
+        <v>455</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8465,14 +8674,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>422</v>
+        <v>463</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8481,10 +8692,10 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
@@ -8493,15 +8704,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>423</v>
+        <v>465</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>424</v>
+        <v>459</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8550,13 +8763,13 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
@@ -8565,13 +8778,13 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8580,14 +8793,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>427</v>
+        <v>466</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8596,10 +8811,10 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -8608,15 +8823,17 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8665,13 +8882,13 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
@@ -8680,13 +8897,13 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8695,14 +8912,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>432</v>
+        <v>469</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8711,10 +8930,10 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
@@ -8723,15 +8942,17 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>428</v>
+        <v>471</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8780,13 +9001,13 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
@@ -8795,13 +9016,13 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8812,10 +9033,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8838,20 +9059,16 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8899,7 +9116,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8917,10 +9134,10 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>441</v>
+        <v>476</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>442</v>
+        <v>477</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8929,12 +9146,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8942,13 +9159,13 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>21</v>
@@ -8957,17 +9174,15 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>444</v>
+        <v>222</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>445</v>
+        <v>223</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9016,7 +9231,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>443</v>
+        <v>225</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9028,44 +9243,44 @@
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>448</v>
+        <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>449</v>
+        <v>226</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>450</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
@@ -9074,15 +9289,17 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>423</v>
+        <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>452</v>
+        <v>229</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -9131,76 +9348,78 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>451</v>
+        <v>232</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>454</v>
+        <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>455</v>
+        <v>226</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>456</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>21</v>
+        <v>481</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>428</v>
+        <v>135</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>458</v>
+        <v>482</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>459</v>
+        <v>483</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -9248,28 +9467,28 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>457</v>
+        <v>484</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>461</v>
+        <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>462</v>
+        <v>133</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9280,10 +9499,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9294,7 +9513,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -9306,15 +9525,17 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>400</v>
+        <v>473</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>401</v>
+        <v>486</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9363,7 +9584,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>403</v>
+        <v>485</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9375,7 +9596,7 @@
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
@@ -9384,7 +9605,7 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>404</v>
+        <v>489</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9395,21 +9616,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -9421,17 +9642,15 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>135</v>
+        <v>222</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>406</v>
+        <v>223</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9468,31 +9687,31 @@
         <v>21</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>465</v>
+        <v>21</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>408</v>
+        <v>225</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
@@ -9501,7 +9720,7 @@
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>404</v>
+        <v>226</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -9512,21 +9731,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
@@ -9535,23 +9754,21 @@
         <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>467</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>468</v>
+        <v>229</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>469</v>
+        <v>230</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9599,19 +9816,19 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>472</v>
+        <v>232</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
@@ -9620,32 +9837,32 @@
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>473</v>
+        <v>226</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>474</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>21</v>
+        <v>481</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9657,24 +9874,24 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>478</v>
+        <v>160</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q65" t="s" s="2">
-        <v>479</v>
-      </c>
+      <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9694,13 +9911,13 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>480</v>
+        <v>21</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>481</v>
+        <v>21</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -9718,19 +9935,19 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
@@ -9739,21 +9956,21 @@
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>483</v>
+        <v>133</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>484</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9773,21 +9990,19 @@
         <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>400</v>
+        <v>494</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>488</v>
-      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9835,7 +10050,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9856,21 +10071,21 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>491</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9890,21 +10105,19 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>104</v>
+        <v>499</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>495</v>
-      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9952,7 +10165,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9961,7 +10174,7 @@
         <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>497</v>
+        <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>102</v>
@@ -9973,21 +10186,21 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>491</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9998,7 +10211,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -10007,23 +10220,19 @@
         <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>110</v>
+        <v>499</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
@@ -10071,7 +10280,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10092,16 +10301,16 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>491</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>506</v>
       </c>
@@ -10114,13 +10323,13 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>21</v>
@@ -10137,8 +10346,12 @@
       <c r="M69" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+      <c r="N69" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>511</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -10204,24 +10417,24 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>21</v>
+        <v>512</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10229,13 +10442,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>21</v>
@@ -10244,15 +10457,17 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>394</v>
+        <v>515</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10301,7 +10516,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10319,24 +10534,24 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>21</v>
+        <v>521</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10344,13 +10559,13 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
@@ -10359,13 +10574,13 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>400</v>
+        <v>494</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>401</v>
+        <v>523</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>402</v>
+        <v>524</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10416,7 +10631,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>403</v>
+        <v>522</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10428,41 +10643,41 @@
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>21</v>
+        <v>525</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>404</v>
+        <v>526</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>21</v>
+        <v>527</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>21</v>
@@ -10474,16 +10689,16 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>135</v>
+        <v>499</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>406</v>
+        <v>529</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>407</v>
+        <v>530</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>159</v>
+        <v>531</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10533,28 +10748,28 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>408</v>
+        <v>528</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>21</v>
+        <v>532</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>404</v>
+        <v>533</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
@@ -10565,46 +10780,42 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>410</v>
+        <v>21</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>135</v>
+        <v>222</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>411</v>
+        <v>223</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
       </c>
@@ -10652,19 +10863,19 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>413</v>
+        <v>225</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>21</v>
@@ -10673,7 +10884,7 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>133</v>
+        <v>226</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10684,21 +10895,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>21</v>
@@ -10710,16 +10921,16 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>520</v>
+        <v>135</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>521</v>
+        <v>229</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>522</v>
+        <v>230</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>523</v>
+        <v>159</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10745,66 +10956,66 @@
         <v>21</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>524</v>
+        <v>21</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>525</v>
+        <v>21</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>519</v>
+        <v>232</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>514</v>
+        <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>526</v>
+        <v>226</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>527</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10824,19 +11035,23 @@
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>183</v>
+        <v>537</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
       </c>
@@ -10860,13 +11075,13 @@
         <v>21</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>531</v>
+        <v>21</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>532</v>
+        <v>21</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>21</v>
@@ -10884,7 +11099,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10902,24 +11117,24 @@
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>533</v>
+        <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10930,32 +11145,36 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>537</v>
+        <v>110</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q76" s="2"/>
+      <c r="Q76" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="R76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10975,13 +11194,13 @@
         <v>21</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>21</v>
+        <v>550</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>21</v>
+        <v>551</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>21</v>
@@ -10999,7 +11218,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>536</v>
+        <v>552</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11014,38 +11233,38 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>540</v>
+        <v>21</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>533</v>
+        <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>21</v>
+        <v>554</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>543</v>
+        <v>21</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>21</v>
@@ -11054,21 +11273,21 @@
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>544</v>
+        <v>222</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -11116,13 +11335,13 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
@@ -11137,21 +11356,21 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>21</v>
+        <v>561</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11162,7 +11381,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>21</v>
@@ -11171,21 +11390,21 @@
         <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>550</v>
+        <v>104</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>565</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -11233,38 +11452,1319 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>21</v>
+        <v>567</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>554</v>
+        <v>21</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO78" t="s" s="2">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO78">
+  <autoFilter ref="A1:AO89">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11274,7 +12774,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI77">
+  <conditionalFormatting sqref="A2:AI88">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$100</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3321" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3730" uniqueCount="638">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,7 +676,7 @@
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.code}
+    <t xml:space="preserve">value:coding.system}
 </t>
   </si>
   <si>
@@ -699,28 +699,10 @@
     <t>Kategorie zur Unterscheidung eines Medikationsplaneintrags von einer geplanten Abgabe (beide haben intent order)</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://fhir.hl7.at/elga/emed/r4/CodeSystem/MedicationRequestCategoryCS"/&gt;
-    &lt;code value="2"/&gt;
-    &lt;display value="Geplante Abgabe"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype</t>
-  </si>
-  <si>
-    <t>recipetype</t>
-  </si>
-  <si>
-    <t>Kategorie zur Unterscheidung, ob ein Kassen-, Privat- oder Substitutionsrezept erstellt wurde.</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-medikationrezeptart</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype.id</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedicationRequestCategoryVS</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:mrcategory.id</t>
   </si>
   <si>
     <t>MedicationRequest.category.id</t>
@@ -742,7 +724,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationRequest.category:recipetype.extension</t>
+    <t>MedicationRequest.category:mrcategory.extension</t>
   </si>
   <si>
     <t>MedicationRequest.category.extension</t>
@@ -760,7 +742,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationRequest.category:recipetype.coding</t>
+    <t>MedicationRequest.category:mrcategory.coding</t>
   </si>
   <si>
     <t>MedicationRequest.category.coding</t>
@@ -791,19 +773,19 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>MedicationRequest.category:recipetype.coding.id</t>
+    <t>MedicationRequest.category:mrcategory.coding.id</t>
   </si>
   <si>
     <t>MedicationRequest.category.coding.id</t>
   </si>
   <si>
-    <t>MedicationRequest.category:recipetype.coding.extension</t>
+    <t>MedicationRequest.category:mrcategory.coding.extension</t>
   </si>
   <si>
     <t>MedicationRequest.category.coding.extension</t>
   </si>
   <si>
-    <t>MedicationRequest.category:recipetype.coding.system</t>
+    <t>MedicationRequest.category:mrcategory.coding.system</t>
   </si>
   <si>
     <t>MedicationRequest.category.coding.system</t>
@@ -821,7 +803,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/CodeSystem/medikationrezeptart</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/MedicationRequestCategoryCS</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -833,7 +815,7 @@
     <t>C*E.3</t>
   </si>
   <si>
-    <t>MedicationRequest.category:recipetype.coding.version</t>
+    <t>MedicationRequest.category:mrcategory.coding.version</t>
   </si>
   <si>
     <t>MedicationRequest.category.coding.version</t>
@@ -857,7 +839,7 @@
     <t>C*E.7</t>
   </si>
   <si>
-    <t>MedicationRequest.category:recipetype.coding.code</t>
+    <t>MedicationRequest.category:mrcategory.coding.code</t>
   </si>
   <si>
     <t>MedicationRequest.category.coding.code</t>
@@ -881,7 +863,7 @@
     <t>C*E.1</t>
   </si>
   <si>
-    <t>MedicationRequest.category:recipetype.coding.display</t>
+    <t>MedicationRequest.category:mrcategory.coding.display</t>
   </si>
   <si>
     <t>MedicationRequest.category.coding.display</t>
@@ -905,7 +887,7 @@
     <t>C*E.2 - but note this is not well followed</t>
   </si>
   <si>
-    <t>MedicationRequest.category:recipetype.coding.userSelected</t>
+    <t>MedicationRequest.category:mrcategory.coding.userSelected</t>
   </si>
   <si>
     <t>MedicationRequest.category.coding.userSelected</t>
@@ -936,31 +918,79 @@
     <t>Sometimes implied by being first</t>
   </si>
   <si>
+    <t>MedicationRequest.category:mrcategory.text</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype</t>
+  </si>
+  <si>
+    <t>recipetype</t>
+  </si>
+  <si>
+    <t>Kategorie zur Unterscheidung, ob ein Kassen-, Privat- oder Substitutionsrezept erstellt wurde.</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-medikationrezeptart</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.system</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/medikationrezeptart</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.version</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.code</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.display</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.userSelected</t>
+  </si>
+  <si>
     <t>MedicationRequest.category:recipetype.text</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>MedicationRequest.priority</t>
@@ -1021,7 +1051,7 @@
     <t>MedicationRequest.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-medikation) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
@@ -2327,7 +2357,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO89"/>
+  <dimension ref="A1:AO100"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
@@ -4413,28 +4443,26 @@
         <v>21</v>
       </c>
       <c r="S18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="Y18" s="2"/>
+      <c r="Z18" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="T18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -4482,28 +4510,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C19" t="s" s="2">
         <v>217</v>
       </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
@@ -4512,17 +4538,15 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -4547,11 +4571,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y19" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z19" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -4569,31 +4595,31 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>21</v>
@@ -4601,21 +4627,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -4627,15 +4653,17 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>222</v>
+        <v>135</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -4672,31 +4700,31 @@
         <v>21</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>21</v>
@@ -4705,7 +4733,7 @@
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
@@ -4716,14 +4744,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4739,21 +4767,23 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>135</v>
+        <v>231</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -4789,19 +4819,19 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4813,7 +4843,7 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
@@ -4822,21 +4852,21 @@
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4844,11 +4874,11 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G22" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4856,23 +4886,19 @@
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4920,19 +4946,19 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>21</v>
@@ -4941,32 +4967,32 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
@@ -4978,15 +5004,17 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>222</v>
+        <v>135</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -5023,31 +5051,31 @@
         <v>21</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>21</v>
@@ -5056,7 +5084,7 @@
         <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
@@ -5067,21 +5095,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
@@ -5090,21 +5118,23 @@
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -5113,7 +5143,7 @@
         <v>21</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>21</v>
@@ -5140,31 +5170,31 @@
         <v>21</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>21</v>
@@ -5173,21 +5203,21 @@
         <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5195,7 +5225,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>90</v>
@@ -5210,20 +5240,18 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>104</v>
+        <v>218</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -5232,7 +5260,7 @@
         <v>21</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>21</v>
@@ -5271,7 +5299,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5292,21 +5320,21 @@
         <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5329,18 +5357,18 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>222</v>
+        <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -5349,7 +5377,7 @@
         <v>21</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>21</v>
@@ -5388,7 +5416,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5409,21 +5437,21 @@
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5431,7 +5459,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>90</v>
@@ -5446,17 +5474,17 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>110</v>
+        <v>218</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5481,11 +5509,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -5503,7 +5533,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5524,21 +5554,21 @@
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5561,17 +5591,19 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>222</v>
+        <v>279</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -5620,7 +5652,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5641,21 +5673,21 @@
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5678,19 +5710,19 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>283</v>
+        <v>218</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5739,7 +5771,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5760,57 +5792,57 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>294</v>
+        <v>205</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5834,13 +5866,11 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>21</v>
+        <v>299</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5858,13 +5888,13 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>297</v>
+        <v>202</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -5876,16 +5906,16 @@
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>298</v>
+        <v>211</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>299</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5893,7 +5923,7 @@
         <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5904,7 +5934,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5913,16 +5943,16 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>110</v>
+        <v>218</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>301</v>
+        <v>219</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>302</v>
+        <v>220</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5949,13 +5979,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5973,7 +6003,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>300</v>
+        <v>221</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5985,19 +6015,19 @@
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>305</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>306</v>
+        <v>222</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>307</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>21</v>
@@ -6005,42 +6035,42 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>224</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>283</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>225</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
+        <v>226</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>311</v>
+        <v>159</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6078,31 +6108,31 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
@@ -6111,7 +6141,7 @@
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>312</v>
+        <v>222</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>21</v>
@@ -6122,10 +6152,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>313</v>
+        <v>230</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6133,10 +6163,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -6148,16 +6178,20 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>314</v>
+        <v>231</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>315</v>
+        <v>232</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -6205,13 +6239,13 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>313</v>
+        <v>236</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
@@ -6226,21 +6260,21 @@
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>317</v>
+        <v>237</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>21</v>
+        <v>238</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>240</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6248,32 +6282,30 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>319</v>
+        <v>218</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>320</v>
+        <v>219</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -6322,10 +6354,10 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>221</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>90</v>
@@ -6334,62 +6366,62 @@
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>323</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>324</v>
+        <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>325</v>
+        <v>222</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>326</v>
+        <v>21</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>327</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>242</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>329</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>225</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>226</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>332</v>
+        <v>159</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6427,54 +6459,54 @@
         <v>21</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>328</v>
+        <v>228</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>334</v>
+        <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>335</v>
+        <v>222</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>338</v>
+        <v>244</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6482,10 +6514,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -6494,21 +6526,23 @@
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>339</v>
+        <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>340</v>
+        <v>245</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>341</v>
+        <v>246</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -6517,7 +6551,7 @@
         <v>21</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>21</v>
@@ -6556,7 +6590,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>338</v>
+        <v>250</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6571,27 +6605,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>343</v>
+        <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>344</v>
+        <v>251</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>345</v>
+        <v>21</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>346</v>
+        <v>252</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>347</v>
+        <v>254</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6602,7 +6636,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -6611,18 +6645,20 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>348</v>
+        <v>218</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>349</v>
+        <v>255</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6671,13 +6707,13 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>347</v>
+        <v>258</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -6686,27 +6722,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>351</v>
+        <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>259</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>345</v>
+        <v>21</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>21</v>
+        <v>260</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>262</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6720,7 +6756,7 @@
         <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -6729,16 +6765,18 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>354</v>
+        <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>355</v>
+        <v>263</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>356</v>
+        <v>264</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6786,7 +6824,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>266</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6801,27 +6839,27 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>357</v>
+        <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>359</v>
+        <v>267</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>360</v>
+        <v>21</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>361</v>
+        <v>268</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>362</v>
+        <v>309</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>362</v>
+        <v>270</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6829,13 +6867,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -6844,16 +6882,18 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>363</v>
+        <v>218</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>364</v>
+        <v>271</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>365</v>
+        <v>272</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6901,7 +6941,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>362</v>
+        <v>274</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6916,27 +6956,27 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>366</v>
+        <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>335</v>
+        <v>275</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>367</v>
+        <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>21</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>368</v>
+        <v>310</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>368</v>
+        <v>278</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6947,7 +6987,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6956,19 +6996,23 @@
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>369</v>
+        <v>279</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>370</v>
+        <v>280</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -7016,7 +7060,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>368</v>
+        <v>284</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7031,27 +7075,27 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>372</v>
+        <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>373</v>
+        <v>285</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>375</v>
+        <v>311</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>375</v>
+        <v>288</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7062,7 +7106,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -7074,18 +7118,20 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
+        <v>290</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -7109,13 +7155,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>379</v>
+        <v>21</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -7133,7 +7179,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>375</v>
+        <v>293</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7148,27 +7194,27 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>381</v>
+        <v>294</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>21</v>
+        <v>295</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>312</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>312</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7188,16 +7234,16 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>383</v>
+        <v>110</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>384</v>
+        <v>313</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>385</v>
+        <v>314</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7224,13 +7270,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>21</v>
+        <v>315</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>21</v>
+        <v>316</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -7248,7 +7294,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>382</v>
+        <v>312</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7263,16 +7309,16 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>21</v>
+        <v>317</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>386</v>
+        <v>318</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>387</v>
+        <v>319</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
@@ -7280,10 +7326,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>388</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>388</v>
+        <v>320</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7300,22 +7346,22 @@
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>183</v>
+        <v>279</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>389</v>
+        <v>321</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>390</v>
+        <v>322</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>391</v>
+        <v>323</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7341,13 +7387,13 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>393</v>
+        <v>21</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>21</v>
@@ -7365,13 +7411,13 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>388</v>
+        <v>320</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
@@ -7380,27 +7426,27 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>394</v>
+        <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>396</v>
+        <v>324</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>399</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>399</v>
+        <v>325</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7411,7 +7457,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -7420,20 +7466,18 @@
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>400</v>
+        <v>326</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>401</v>
+        <v>327</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -7482,13 +7526,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>399</v>
+        <v>325</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -7497,27 +7541,27 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>404</v>
+        <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>405</v>
+        <v>329</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>406</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>406</v>
+        <v>330</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7525,13 +7569,13 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -7540,15 +7584,17 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>407</v>
+        <v>331</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>408</v>
+        <v>332</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7597,13 +7643,13 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>406</v>
+        <v>330</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
@@ -7612,27 +7658,27 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>410</v>
+        <v>335</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>21</v>
+        <v>336</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>411</v>
+        <v>337</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>21</v>
+        <v>339</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>412</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7640,13 +7686,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -7655,15 +7701,17 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>104</v>
+        <v>341</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>413</v>
+        <v>342</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7712,13 +7760,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>412</v>
+        <v>340</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7727,27 +7775,27 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>411</v>
+        <v>347</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>21</v>
+        <v>348</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>415</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>415</v>
+        <v>350</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7755,30 +7803,32 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>416</v>
+        <v>351</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>417</v>
+        <v>352</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7827,13 +7877,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>415</v>
+        <v>350</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7842,27 +7892,27 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>419</v>
+        <v>355</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>420</v>
+        <v>356</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>21</v>
+        <v>358</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>421</v>
+        <v>359</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>421</v>
+        <v>359</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7870,33 +7920,31 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>163</v>
+        <v>360</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>422</v>
+        <v>361</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>423</v>
+        <v>362</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>424</v>
-      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7944,13 +7992,13 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>421</v>
+        <v>359</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
@@ -7959,27 +8007,27 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>425</v>
+        <v>363</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>426</v>
+        <v>364</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>427</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>427</v>
+        <v>365</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7987,32 +8035,30 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>183</v>
+        <v>366</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>428</v>
+        <v>367</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -8037,13 +8083,13 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>431</v>
+        <v>21</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>432</v>
+        <v>21</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -8061,7 +8107,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>427</v>
+        <v>365</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8076,27 +8122,27 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>433</v>
+        <v>371</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>21</v>
+        <v>372</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>21</v>
+        <v>373</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8104,28 +8150,28 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>435</v>
+        <v>375</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>436</v>
+        <v>376</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>437</v>
+        <v>377</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8176,13 +8222,13 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
@@ -8191,27 +8237,27 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>438</v>
+        <v>378</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>439</v>
+        <v>347</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>21</v>
+        <v>379</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8222,10 +8268,10 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
@@ -8234,13 +8280,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>441</v>
+        <v>381</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>442</v>
+        <v>382</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>443</v>
+        <v>383</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8291,13 +8337,13 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -8306,16 +8352,16 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>444</v>
+        <v>384</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>445</v>
+        <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>446</v>
+        <v>385</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8323,10 +8369,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>447</v>
+        <v>387</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>447</v>
+        <v>387</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8334,31 +8380,31 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K52" t="s" s="2">
-        <v>448</v>
+        <v>183</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>449</v>
+        <v>327</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>450</v>
+        <v>388</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>451</v>
+        <v>389</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8384,35 +8430,37 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>21</v>
+        <v>390</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>21</v>
+        <v>391</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AC52" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>453</v>
+        <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>447</v>
+        <v>387</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -8421,13 +8469,13 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>454</v>
+        <v>392</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>455</v>
+        <v>393</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8436,16 +8484,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>456</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>21</v>
       </c>
@@ -8454,10 +8500,10 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
@@ -8466,17 +8512,15 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>458</v>
+        <v>395</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>459</v>
+        <v>396</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8525,13 +8569,13 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>447</v>
+        <v>394</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
@@ -8540,31 +8584,29 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>454</v>
+        <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>455</v>
+        <v>398</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>21</v>
+        <v>399</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8573,10 +8615,10 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
@@ -8585,16 +8627,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>462</v>
+        <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>459</v>
+        <v>401</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>450</v>
+        <v>402</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>451</v>
+        <v>403</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8620,13 +8662,13 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>21</v>
+        <v>404</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>21</v>
+        <v>405</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -8644,7 +8686,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8659,31 +8701,29 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>454</v>
+        <v>406</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>21</v>
+        <v>407</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>455</v>
+        <v>408</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>21</v>
+        <v>409</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>21</v>
+        <v>410</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>463</v>
+        <v>411</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>21</v>
       </c>
@@ -8695,7 +8735,7 @@
         <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
@@ -8704,16 +8744,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>465</v>
+        <v>412</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>459</v>
+        <v>413</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>451</v>
+        <v>415</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8763,7 +8803,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>447</v>
+        <v>411</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8778,31 +8818,29 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>454</v>
+        <v>416</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>455</v>
+        <v>417</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>21</v>
+        <v>409</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>466</v>
+        <v>418</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8811,29 +8849,27 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K56" t="s" s="2">
-        <v>468</v>
+        <v>419</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>459</v>
+        <v>420</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -8882,7 +8918,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8897,13 +8933,13 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>454</v>
+        <v>422</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>455</v>
+        <v>423</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8912,16 +8948,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>469</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8930,29 +8964,27 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K57" t="s" s="2">
-        <v>471</v>
+        <v>104</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>459</v>
+        <v>425</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -9001,7 +9033,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9016,13 +9048,13 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>454</v>
+        <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>455</v>
+        <v>423</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -9033,10 +9065,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>472</v>
+        <v>427</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>472</v>
+        <v>427</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9056,16 +9088,16 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>473</v>
+        <v>428</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>474</v>
+        <v>429</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>475</v>
+        <v>430</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9116,13 +9148,13 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>472</v>
+        <v>427</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
@@ -9131,13 +9163,13 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>476</v>
+        <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>477</v>
+        <v>432</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -9146,12 +9178,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>478</v>
+        <v>433</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>478</v>
+        <v>433</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9159,31 +9191,33 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>222</v>
+        <v>163</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>223</v>
+        <v>434</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>224</v>
+        <v>435</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9231,7 +9265,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>225</v>
+        <v>433</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9243,16 +9277,16 @@
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>21</v>
+        <v>437</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>226</v>
+        <v>438</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -9263,21 +9297,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>479</v>
+        <v>439</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>479</v>
+        <v>439</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -9289,16 +9323,16 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>135</v>
+        <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>229</v>
+        <v>440</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>230</v>
+        <v>441</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>159</v>
+        <v>442</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9324,13 +9358,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>21</v>
+        <v>443</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>21</v>
+        <v>444</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9348,19 +9382,19 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>232</v>
+        <v>439</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>21</v>
@@ -9369,7 +9403,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>226</v>
+        <v>445</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9380,46 +9414,42 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>480</v>
+        <v>446</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>480</v>
+        <v>446</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>481</v>
+        <v>21</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>135</v>
+        <v>447</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>482</v>
+        <v>448</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -9467,7 +9497,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>484</v>
+        <v>446</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9479,16 +9509,16 @@
         <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>21</v>
+        <v>450</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>133</v>
+        <v>451</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9497,12 +9527,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9513,10 +9543,10 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>21</v>
@@ -9525,17 +9555,15 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9584,13 +9612,13 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
@@ -9599,13 +9627,13 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>21</v>
+        <v>456</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>21</v>
+        <v>457</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9616,10 +9644,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9627,13 +9655,13 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>21</v>
@@ -9642,15 +9670,17 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>222</v>
+        <v>460</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>223</v>
+        <v>461</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9687,40 +9717,38 @@
         <v>21</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>21</v>
+        <v>465</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>225</v>
+        <v>459</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>226</v>
+        <v>467</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -9729,16 +9757,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>491</v>
+        <v>468</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="D64" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9748,7 +9778,7 @@
         <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
@@ -9757,16 +9787,16 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>470</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>229</v>
+        <v>471</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>230</v>
+        <v>462</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>159</v>
+        <v>463</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9816,7 +9846,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>232</v>
+        <v>459</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9828,16 +9858,16 @@
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>226</v>
+        <v>467</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -9846,16 +9876,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="D65" t="s" s="2">
-        <v>481</v>
+        <v>21</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9865,29 +9897,27 @@
         <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>474</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9935,7 +9965,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>484</v>
+        <v>459</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9947,16 +9977,16 @@
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>133</v>
+        <v>467</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9965,14 +9995,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9981,10 +10013,10 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>21</v>
@@ -9993,15 +10025,17 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -10050,13 +10084,13 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>493</v>
+        <v>459</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
@@ -10065,13 +10099,13 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>497</v>
+        <v>467</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -10080,14 +10114,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>21</v>
       </c>
@@ -10096,10 +10132,10 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>21</v>
@@ -10108,15 +10144,17 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>500</v>
+        <v>471</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -10165,13 +10203,13 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>498</v>
+        <v>459</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
@@ -10180,13 +10218,13 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>502</v>
+        <v>467</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -10195,14 +10233,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>21</v>
       </c>
@@ -10211,10 +10251,10 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
@@ -10223,15 +10263,17 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -10280,13 +10322,13 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>503</v>
+        <v>459</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
@@ -10295,13 +10337,13 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>502</v>
+        <v>467</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10312,10 +10354,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10338,20 +10380,16 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>507</v>
+        <v>485</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>511</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -10399,7 +10437,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10417,10 +10455,10 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10429,12 +10467,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10442,13 +10480,13 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>21</v>
@@ -10457,17 +10495,15 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>515</v>
+        <v>218</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>516</v>
+        <v>219</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10516,7 +10552,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>514</v>
+        <v>221</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10528,44 +10564,44 @@
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>519</v>
+        <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>520</v>
+        <v>222</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>521</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>522</v>
+        <v>491</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>522</v>
+        <v>491</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
@@ -10574,15 +10610,17 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>494</v>
+        <v>135</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>523</v>
+        <v>225</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -10631,76 +10669,78 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>522</v>
+        <v>228</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>525</v>
+        <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>526</v>
+        <v>222</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>527</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>528</v>
+        <v>492</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>528</v>
+        <v>492</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>21</v>
+        <v>493</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>499</v>
+        <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>529</v>
+        <v>494</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>530</v>
+        <v>495</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
@@ -10748,28 +10788,28 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>528</v>
+        <v>496</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>532</v>
+        <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>533</v>
+        <v>133</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
@@ -10780,10 +10820,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>534</v>
+        <v>497</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>534</v>
+        <v>497</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10794,7 +10834,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
@@ -10806,15 +10846,17 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>222</v>
+        <v>485</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>223</v>
+        <v>498</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -10863,7 +10905,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>225</v>
+        <v>497</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10875,7 +10917,7 @@
         <v>21</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>21</v>
@@ -10884,7 +10926,7 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>226</v>
+        <v>501</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10895,21 +10937,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>535</v>
+        <v>502</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>21</v>
@@ -10921,17 +10963,15 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>135</v>
+        <v>218</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10968,31 +11008,31 @@
         <v>21</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>21</v>
@@ -11001,7 +11041,7 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -11012,21 +11052,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>21</v>
@@ -11035,23 +11075,21 @@
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>537</v>
+        <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>538</v>
+        <v>225</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>539</v>
+        <v>226</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>541</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
       </c>
@@ -11099,19 +11137,19 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>542</v>
+        <v>228</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
@@ -11120,32 +11158,32 @@
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>543</v>
+        <v>222</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>544</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>545</v>
+        <v>504</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>545</v>
+        <v>504</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>21</v>
+        <v>493</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -11157,24 +11195,24 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>546</v>
+        <v>494</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O76" t="s" s="2">
-        <v>548</v>
+        <v>160</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q76" t="s" s="2">
-        <v>549</v>
-      </c>
+      <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
         <v>21</v>
       </c>
@@ -11194,13 +11232,13 @@
         <v>21</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>550</v>
+        <v>21</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>551</v>
+        <v>21</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>21</v>
@@ -11218,19 +11256,19 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>552</v>
+        <v>496</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>21</v>
@@ -11239,21 +11277,21 @@
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>553</v>
+        <v>133</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>554</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>555</v>
+        <v>505</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>555</v>
+        <v>505</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11273,21 +11311,19 @@
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>222</v>
+        <v>506</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>556</v>
+        <v>507</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>557</v>
+        <v>508</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" t="s" s="2">
-        <v>558</v>
-      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -11335,7 +11371,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>559</v>
+        <v>505</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11356,21 +11392,21 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>560</v>
+        <v>509</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>561</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>562</v>
+        <v>510</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>562</v>
+        <v>510</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11390,21 +11426,19 @@
         <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>104</v>
+        <v>511</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>563</v>
+        <v>512</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>564</v>
+        <v>513</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>565</v>
-      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -11452,7 +11486,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>566</v>
+        <v>510</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11461,7 +11495,7 @@
         <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>567</v>
+        <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>102</v>
@@ -11473,21 +11507,21 @@
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>568</v>
+        <v>514</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>561</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>569</v>
+        <v>515</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>569</v>
+        <v>515</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11498,7 +11532,7 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>21</v>
@@ -11507,23 +11541,19 @@
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>110</v>
+        <v>511</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>21</v>
       </c>
@@ -11571,7 +11601,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>574</v>
+        <v>515</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11592,21 +11622,21 @@
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>575</v>
+        <v>514</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>561</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>576</v>
+        <v>518</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>576</v>
+        <v>518</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11614,13 +11644,13 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>21</v>
@@ -11629,16 +11659,20 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>577</v>
+        <v>519</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
       </c>
@@ -11686,7 +11720,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>576</v>
+        <v>518</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11704,24 +11738,24 @@
         <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>21</v>
+        <v>524</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>580</v>
+        <v>525</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>387</v>
+        <v>21</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>581</v>
+        <v>526</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>581</v>
+        <v>526</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11729,13 +11763,13 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>21</v>
@@ -11744,15 +11778,17 @@
         <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>473</v>
+        <v>527</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>582</v>
+        <v>528</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>529</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -11801,7 +11837,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>581</v>
+        <v>526</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11819,24 +11855,24 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>584</v>
+        <v>531</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>585</v>
+        <v>532</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>21</v>
+        <v>533</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>586</v>
+        <v>534</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>586</v>
+        <v>534</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11844,13 +11880,13 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>21</v>
@@ -11859,13 +11895,13 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>222</v>
+        <v>506</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>223</v>
+        <v>535</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>224</v>
+        <v>536</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11916,7 +11952,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>225</v>
+        <v>534</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11928,41 +11964,41 @@
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>21</v>
+        <v>537</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>226</v>
+        <v>538</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>21</v>
+        <v>539</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>587</v>
+        <v>540</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>587</v>
+        <v>540</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -11974,16 +12010,16 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>135</v>
+        <v>511</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>229</v>
+        <v>541</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>230</v>
+        <v>542</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>159</v>
+        <v>543</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12033,28 +12069,28 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>232</v>
+        <v>540</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>21</v>
+        <v>544</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>226</v>
+        <v>545</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -12065,46 +12101,42 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>588</v>
+        <v>546</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>588</v>
+        <v>546</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>481</v>
+        <v>21</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>135</v>
+        <v>218</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>482</v>
+        <v>219</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -12152,19 +12184,19 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>484</v>
+        <v>221</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>21</v>
@@ -12173,7 +12205,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -12184,21 +12216,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>589</v>
+        <v>547</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>589</v>
+        <v>547</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>21</v>
@@ -12210,16 +12242,16 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>590</v>
+        <v>135</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>591</v>
+        <v>225</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>592</v>
+        <v>226</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>593</v>
+        <v>159</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12245,66 +12277,66 @@
         <v>21</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>594</v>
+        <v>21</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>595</v>
+        <v>21</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>589</v>
+        <v>228</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>584</v>
+        <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>596</v>
+        <v>222</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>597</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>598</v>
+        <v>548</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>598</v>
+        <v>548</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12324,19 +12356,23 @@
         <v>21</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>183</v>
+        <v>549</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>599</v>
+        <v>550</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
       </c>
@@ -12360,13 +12396,13 @@
         <v>21</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>601</v>
+        <v>21</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>602</v>
+        <v>21</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>21</v>
@@ -12384,7 +12420,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>598</v>
+        <v>554</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12402,24 +12438,24 @@
         <v>21</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>603</v>
+        <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>604</v>
+        <v>555</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>605</v>
+        <v>556</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>606</v>
+        <v>557</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>606</v>
+        <v>557</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12430,32 +12466,36 @@
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>607</v>
+        <v>110</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>608</v>
+        <v>558</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>609</v>
+        <v>559</v>
       </c>
       <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q87" s="2"/>
+      <c r="Q87" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="R87" t="s" s="2">
         <v>21</v>
       </c>
@@ -12475,13 +12515,13 @@
         <v>21</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>21</v>
+        <v>562</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>21</v>
+        <v>563</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>21</v>
@@ -12499,7 +12539,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>606</v>
+        <v>564</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12514,38 +12554,38 @@
         <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>610</v>
+        <v>21</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>603</v>
+        <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>611</v>
+        <v>565</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>21</v>
+        <v>566</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>612</v>
+        <v>567</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>612</v>
+        <v>567</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>613</v>
+        <v>21</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>21</v>
@@ -12554,21 +12594,21 @@
         <v>21</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>614</v>
+        <v>218</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>615</v>
+        <v>568</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>569</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>570</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
       </c>
@@ -12616,13 +12656,13 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>612</v>
+        <v>571</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>21</v>
@@ -12637,21 +12677,21 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>618</v>
+        <v>572</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>21</v>
+        <v>573</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>619</v>
+        <v>574</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>619</v>
+        <v>574</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12662,7 +12702,7 @@
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>21</v>
@@ -12671,21 +12711,21 @@
         <v>21</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>620</v>
+        <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>621</v>
+        <v>575</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>21</v>
       </c>
@@ -12733,38 +12773,1319 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>619</v>
+        <v>578</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>21</v>
+        <v>579</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="AL89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM89" t="s" s="2">
+      <c r="B99" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="AN89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO89" t="s" s="2">
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO100" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO89">
+  <autoFilter ref="A1:AO100">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12774,7 +14095,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI88">
+  <conditionalFormatting sqref="A2:AI99">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3730" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3730" uniqueCount="639">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Bildet eine "Geplante Abgabe" eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab ("MedicationRequest"-Ressource mit Kategorie "Geplante Abgabe"):
+    <t>Bildet eine "Geplante Abgabe" eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag ab ("MedicationRequest"-Ressource mit Kategorie "Geplante Abgabe"):
 Sie enthält die verordnete Medikation und deren Dosierung und spielgelt die Inhalte des e-Rezepts wider. Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation. 
-Werden mehrere Medikamente gleichzeitig verordnet und sollen demselben e-Rezept zugeordnet sein, wird für jedes Medikament eine "Geplante Abgabe" mit demselben "e-Med GroupIdentifier" erstellt (bildet 'Rezept-Klammer'). 
+Werden mehrere Medikamente gleichzeitig verschrieben und sollen demselben e-Rezept zugeordnet sein, wird für jedes Medikament eine "Geplante Abgabe" mit demselben "e-Med GroupIdentifier" erstellt (bildet 'Rezept-Klammer'). 
 Es werden R5-Backport-Extensions verwendet.</t>
   </si>
   <si>
@@ -412,18 +412,14 @@
     <t>MedicationRequest.contained</t>
   </si>
   <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
+    <t xml:space="preserve">Medication {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung}
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+    <t>TODO</t>
+  </si>
+  <si>
+    <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
   </si>
   <si>
     <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
@@ -432,7 +428,16 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>NewRx/MedicationPrescribed+-or-+RxFill/MedicationDispensed+-or-+RxHistoryResponse/MedicationDispensed+-or-+RxHistoryResponse/MedicationPrescribed</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct[classCode=ADMM]</t>
   </si>
   <si>
     <t>MedicationRequest.extension</t>
@@ -527,6 +532,9 @@
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>MedicationRequest.identifier</t>
@@ -2363,7 +2371,7 @@
     <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="59.5390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.41015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="28.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -2642,7 +2650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -2655,13 +2663,13 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>21</v>
@@ -2759,7 +2767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>97</v>
       </c>
@@ -2778,7 +2786,7 @@
         <v>90</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>21</v>
@@ -2890,7 +2898,7 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
@@ -3108,7 +3116,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>118</v>
       </c>
@@ -3121,13 +3129,13 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
@@ -3225,7 +3233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -3234,7 +3242,7 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -3244,7 +3252,7 @@
         <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>21</v>
@@ -3253,16 +3261,16 @@
         <v>21</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3312,7 +3320,7 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -3330,7 +3338,7 @@
         <v>21</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>133</v>
@@ -3803,7 +3811,7 @@
         <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>21</v>
@@ -3814,10 +3822,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3840,16 +3848,16 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3899,7 +3907,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3914,27 +3922,27 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3960,13 +3968,13 @@
         <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3992,11 +4000,11 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -4014,7 +4022,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>90</v>
@@ -4029,16 +4037,16 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>21</v>
@@ -4046,10 +4054,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4072,16 +4080,16 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4107,13 +4115,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -4131,7 +4139,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4146,13 +4154,13 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>21</v>
@@ -4163,10 +4171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4192,13 +4200,13 @@
         <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4209,7 +4217,7 @@
         <v>21</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>21</v>
@@ -4224,13 +4232,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -4248,7 +4256,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>90</v>
@@ -4263,16 +4271,16 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>21</v>
@@ -4280,10 +4288,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4291,7 +4299,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>81</v>
@@ -4306,16 +4314,16 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4341,19 +4349,19 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
@@ -4363,7 +4371,7 @@
         <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4381,13 +4389,13 @@
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>21</v>
@@ -4395,13 +4403,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>21</v>
@@ -4423,16 +4431,16 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4458,11 +4466,11 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -4480,7 +4488,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4498,13 +4506,13 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>21</v>
@@ -4512,10 +4520,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4538,13 +4546,13 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4595,7 +4603,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4616,7 +4624,7 @@
         <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>21</v>
@@ -4627,10 +4635,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4656,10 +4664,10 @@
         <v>135</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>159</v>
@@ -4703,7 +4711,7 @@
         <v>138</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>21</v>
@@ -4712,7 +4720,7 @@
         <v>139</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4733,7 +4741,7 @@
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
@@ -4744,10 +4752,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4770,19 +4778,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4831,7 +4839,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4852,21 +4860,21 @@
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4889,13 +4897,13 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4946,7 +4954,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4967,7 +4975,7 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4978,10 +4986,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5007,10 +5015,10 @@
         <v>135</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>159</v>
@@ -5054,7 +5062,7 @@
         <v>138</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>21</v>
@@ -5063,7 +5071,7 @@
         <v>139</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5084,7 +5092,7 @@
         <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
@@ -5095,10 +5103,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5124,16 +5132,16 @@
         <v>104</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -5143,7 +5151,7 @@
         <v>21</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>21</v>
@@ -5182,7 +5190,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5203,21 +5211,21 @@
         <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5240,16 +5248,16 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5299,7 +5307,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5320,21 +5328,21 @@
         <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5360,14 +5368,14 @@
         <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -5377,7 +5385,7 @@
         <v>21</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>21</v>
@@ -5416,7 +5424,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5437,21 +5445,21 @@
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5474,17 +5482,17 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5533,7 +5541,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5554,21 +5562,21 @@
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5591,19 +5599,19 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -5652,7 +5660,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5673,21 +5681,21 @@
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5710,19 +5718,19 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5771,7 +5779,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5792,24 +5800,24 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>21</v>
@@ -5831,16 +5839,16 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5866,11 +5874,11 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5888,7 +5896,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5906,13 +5914,13 @@
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>21</v>
@@ -5920,10 +5928,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5946,13 +5954,13 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6003,7 +6011,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6024,7 +6032,7 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
@@ -6035,10 +6043,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6064,10 +6072,10 @@
         <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>159</v>
@@ -6111,7 +6119,7 @@
         <v>138</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
@@ -6120,7 +6128,7 @@
         <v>139</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6141,7 +6149,7 @@
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>21</v>
@@ -6152,10 +6160,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6178,19 +6186,19 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -6239,7 +6247,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6260,21 +6268,21 @@
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6297,13 +6305,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6354,7 +6362,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6375,7 +6383,7 @@
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
@@ -6386,10 +6394,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6415,10 +6423,10 @@
         <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>159</v>
@@ -6462,7 +6470,7 @@
         <v>138</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>21</v>
@@ -6471,7 +6479,7 @@
         <v>139</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6492,7 +6500,7 @@
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
@@ -6503,10 +6511,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6532,16 +6540,16 @@
         <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6551,7 +6559,7 @@
         <v>21</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>21</v>
@@ -6590,7 +6598,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6611,21 +6619,21 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6648,16 +6656,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6707,7 +6715,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6728,21 +6736,21 @@
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6768,14 +6776,14 @@
         <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6824,7 +6832,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6845,21 +6853,21 @@
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6882,17 +6890,17 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6941,7 +6949,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6962,21 +6970,21 @@
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6999,19 +7007,19 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -7060,7 +7068,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7081,21 +7089,21 @@
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7118,19 +7126,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -7179,7 +7187,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7200,21 +7208,21 @@
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7240,10 +7248,10 @@
         <v>110</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7270,13 +7278,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -7294,7 +7302,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7309,16 +7317,16 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
@@ -7326,10 +7334,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7352,16 +7360,16 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7411,7 +7419,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7432,7 +7440,7 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7443,10 +7451,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7469,13 +7477,13 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7526,7 +7534,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7547,7 +7555,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7558,10 +7566,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7584,16 +7592,16 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7643,7 +7651,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>90</v>
@@ -7658,27 +7666,27 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7701,16 +7709,16 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7760,7 +7768,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>90</v>
@@ -7775,27 +7783,27 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7818,16 +7826,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7877,7 +7885,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7892,27 +7900,27 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7935,13 +7943,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7992,7 +8000,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8007,16 +8015,16 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -8024,10 +8032,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8050,13 +8058,13 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8107,7 +8115,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8122,27 +8130,27 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8165,13 +8173,13 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8222,7 +8230,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8237,16 +8245,16 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>21</v>
@@ -8254,10 +8262,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8280,13 +8288,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8337,7 +8345,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8352,16 +8360,16 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8369,10 +8377,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8395,16 +8403,16 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8430,13 +8438,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -8454,7 +8462,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8469,13 +8477,13 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8486,10 +8494,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8512,13 +8520,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8569,7 +8577,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8590,10 +8598,10 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -8601,10 +8609,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8627,16 +8635,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8662,13 +8670,13 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -8686,7 +8694,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8701,27 +8709,27 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8744,16 +8752,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8803,7 +8811,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8818,16 +8826,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
@@ -8835,10 +8843,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8861,13 +8869,13 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8918,7 +8926,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8933,13 +8941,13 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8950,10 +8958,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8979,10 +8987,10 @@
         <v>104</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9033,7 +9041,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9054,7 +9062,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -9065,10 +9073,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9091,13 +9099,13 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9148,7 +9156,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9163,13 +9171,13 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -9180,10 +9188,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9206,17 +9214,17 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9265,7 +9273,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9280,13 +9288,13 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -9297,10 +9305,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9323,16 +9331,16 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9358,13 +9366,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9382,7 +9390,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9403,7 +9411,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9414,10 +9422,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9440,13 +9448,13 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9497,7 +9505,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9512,13 +9520,13 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9529,10 +9537,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9555,13 +9563,13 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9612,7 +9620,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9627,13 +9635,13 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9644,10 +9652,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9670,16 +9678,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9717,17 +9725,17 @@
         <v>21</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9742,13 +9750,13 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -9759,13 +9767,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>21</v>
@@ -9787,16 +9795,16 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9846,7 +9854,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9861,13 +9869,13 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -9878,13 +9886,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>21</v>
@@ -9906,16 +9914,16 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9965,7 +9973,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9980,13 +9988,13 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9997,13 +10005,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>21</v>
@@ -10025,16 +10033,16 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10084,7 +10092,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10099,13 +10107,13 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -10116,13 +10124,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>21</v>
@@ -10144,16 +10152,16 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10203,7 +10211,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10218,13 +10226,13 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -10235,13 +10243,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>21</v>
@@ -10263,16 +10271,16 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10322,7 +10330,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10337,13 +10345,13 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10354,10 +10362,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10380,13 +10388,13 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10437,7 +10445,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10455,10 +10463,10 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10469,10 +10477,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10495,13 +10503,13 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10552,7 +10560,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10573,7 +10581,7 @@
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -10584,10 +10592,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10613,10 +10621,10 @@
         <v>135</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>159</v>
@@ -10669,7 +10677,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10690,7 +10698,7 @@
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
@@ -10701,14 +10709,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10730,10 +10738,10 @@
         <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>159</v>
@@ -10788,7 +10796,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10809,7 +10817,7 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
@@ -10820,10 +10828,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10846,16 +10854,16 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10905,7 +10913,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10926,7 +10934,7 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10937,10 +10945,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10963,13 +10971,13 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11020,7 +11028,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11041,7 +11049,7 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -11052,10 +11060,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11081,10 +11089,10 @@
         <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>159</v>
@@ -11137,7 +11145,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11158,7 +11166,7 @@
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -11169,14 +11177,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11198,10 +11206,10 @@
         <v>135</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>159</v>
@@ -11256,7 +11264,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11277,7 +11285,7 @@
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -11288,10 +11296,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11314,13 +11322,13 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11371,7 +11379,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11392,7 +11400,7 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -11403,10 +11411,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11429,13 +11437,13 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11486,7 +11494,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11507,7 +11515,7 @@
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -11518,10 +11526,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11544,13 +11552,13 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11601,7 +11609,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11622,7 +11630,7 @@
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
@@ -11633,10 +11641,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11659,19 +11667,19 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -11720,7 +11728,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11738,10 +11746,10 @@
         <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -11752,10 +11760,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11778,16 +11786,16 @@
         <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11837,7 +11845,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11855,24 +11863,24 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11895,13 +11903,13 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11952,7 +11960,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11970,24 +11978,24 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12010,16 +12018,16 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12069,7 +12077,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12087,10 +12095,10 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -12101,10 +12109,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12127,13 +12135,13 @@
         <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12184,7 +12192,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12205,7 +12213,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -12216,10 +12224,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12245,10 +12253,10 @@
         <v>135</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>159</v>
@@ -12292,7 +12300,7 @@
         <v>138</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>21</v>
@@ -12301,7 +12309,7 @@
         <v>139</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12322,7 +12330,7 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12333,10 +12341,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12359,19 +12367,19 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -12420,7 +12428,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12441,21 +12449,21 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12481,20 +12489,20 @@
         <v>110</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q87" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="R87" t="s" s="2">
         <v>21</v>
@@ -12515,13 +12523,13 @@
         <v>21</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>21</v>
@@ -12539,7 +12547,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12560,21 +12568,21 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12597,17 +12605,17 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -12656,7 +12664,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12677,21 +12685,21 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12717,14 +12725,14 @@
         <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>21</v>
@@ -12773,7 +12781,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12782,7 +12790,7 @@
         <v>90</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>102</v>
@@ -12794,21 +12802,21 @@
         <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12834,16 +12842,16 @@
         <v>110</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -12892,7 +12900,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12913,21 +12921,21 @@
         <v>21</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12950,13 +12958,13 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13007,7 +13015,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13028,10 +13036,10 @@
         <v>21</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>21</v>
@@ -13039,10 +13047,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13065,13 +13073,13 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13122,7 +13130,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13140,10 +13148,10 @@
         <v>21</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>21</v>
@@ -13154,10 +13162,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13180,13 +13188,13 @@
         <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13237,7 +13245,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13258,7 +13266,7 @@
         <v>21</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>21</v>
@@ -13269,10 +13277,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13298,10 +13306,10 @@
         <v>135</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>159</v>
@@ -13354,7 +13362,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13375,7 +13383,7 @@
         <v>21</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>21</v>
@@ -13386,14 +13394,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13415,10 +13423,10 @@
         <v>135</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>159</v>
@@ -13473,7 +13481,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13494,7 +13502,7 @@
         <v>21</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>21</v>
@@ -13505,10 +13513,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13531,16 +13539,16 @@
         <v>21</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13566,13 +13574,13 @@
         <v>21</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>21</v>
@@ -13590,7 +13598,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>90</v>
@@ -13608,24 +13616,24 @@
         <v>21</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13648,13 +13656,13 @@
         <v>21</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13681,13 +13689,13 @@
         <v>21</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>21</v>
@@ -13705,7 +13713,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13723,24 +13731,24 @@
         <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13763,13 +13771,13 @@
         <v>21</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13820,7 +13828,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13835,13 +13843,13 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>21</v>
@@ -13852,14 +13860,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13878,16 +13886,16 @@
         <v>21</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13937,7 +13945,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13958,7 +13966,7 @@
         <v>21</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>21</v>
@@ -13969,10 +13977,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13995,16 +14003,16 @@
         <v>21</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14054,7 +14062,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14069,13 +14077,13 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$93</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3730" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3469" uniqueCount="598">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -544,7 +544,7 @@
 </t>
   </si>
   <si>
-    <t>Logischer Identifier. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>External ids for this request</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -605,7 +605,7 @@
 </t>
   </si>
   <si>
-    <t>Grund des aktuellen Status: https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Reason for current status</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the MedicationRequest.</t>
@@ -1004,7 +1004,7 @@
     <t>MedicationRequest.priority</t>
   </si>
   <si>
-    <t>Priorität der geplanten Abgabe. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>routine | urgent | asap | stat</t>
   </si>
   <si>
     <t>Indicates how quickly the Medication Request should be addressed with respect to other requests.</t>
@@ -1028,7 +1028,7 @@
     <t>MedicationRequest.doNotPerform</t>
   </si>
   <si>
-    <t>Gibt an, ob die Geplante Abgabe untersagt ist. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>True if request is prohibiting action</t>
   </si>
   <si>
     <t>If true indicates that the provider is asking for the medication request not to occur.</t>
@@ -1047,7 +1047,7 @@
 Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)</t>
   </si>
   <si>
-    <t>Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Reported rather than primary record</t>
   </si>
   <si>
     <t>Indicates if this record was captured as a secondary 'reported' record rather than as an original primary source-of-truth record.  It may also indicate the source of the report.</t>
@@ -1249,6 +1249,9 @@
     <t>MedicationRequest.performerType</t>
   </si>
   <si>
+    <t>Keine Verwendung in der geplanten Abgabe.</t>
+  </si>
+  <si>
     <t>Indicates the type of performer of the administration of the medication.</t>
   </si>
   <si>
@@ -1627,7 +1630,7 @@
 </t>
   </si>
   <si>
-    <t>Anzahl der Einheiten für die erste Abgabe, z.B. 30 Kapseln oder 100 mg. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>First fill quantity</t>
   </si>
   <si>
     <t>The amount or quantity to provide as part of the first dispense.</t>
@@ -1655,7 +1658,7 @@
     <t>MedicationRequest.dispenseRequest.dispenseInterval</t>
   </si>
   <si>
-    <t>Mindestzeitraum zwischen den Abgaben. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Minimum period of time between dispenses</t>
   </si>
   <si>
     <t>The minimum period of time that must occur between dispenses of the medication.</t>
@@ -1697,13 +1700,13 @@
 </t>
   </si>
   <si>
-    <t>Die Anzahl der weiteren möglichen Einlösungen (abhängig von Rezeptart): Kassenrezept: keine weitere Einlösung möglich (fixer Wert 0). Privatrezept: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden. Sustitutionsrezept: keine weitere Einlösung möglich (fixer Wert 0)</t>
+    <t>Die Anzahl der weiteren möglichen Einlösungen (abhängig von Rezeptart): Kassenrezept: keine weitere Einlösung möglich (fixer Wert 0). Privatrezept: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden. Substitutionsrezept: keine weitere Einlösung möglich (fixer Wert 0)</t>
   </si>
   <si>
     <t xml:space="preserve">Anzahl der weiteren möglichen Einlösungen:
 * **Kassenrezept**: keine weitere Einlösung möglich (fixer Wert 0)
 * **Privatrezept**: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden
-* **Sustitutionsrezept**: keine weitere Einlösung möglich (fixer Wert 0) </t>
+* **Substitutionsrezept**: keine weitere Einlösung möglich (fixer Wert 0) </t>
   </si>
   <si>
     <t>If displaying "number of authorized fills", add 1 to this number.</t>
@@ -1756,134 +1759,6 @@
     <t>expectedUseTime</t>
   </si>
   <si>
-    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Dauer, für die die bereitgestellte Menge des Medikaments voraussichtlich ausreicht. Keine Verwendung in der geplanten Abgabe.</t>
-  </si>
-  <si>
-    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
-  </si>
-  <si>
-    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
-  </si>
-  <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
-  </si>
-  <si>
-    <t>Quantity.value</t>
-  </si>
-  <si>
-    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>SN.2  / CQ - N/A</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.comparator</t>
-  </si>
-  <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
-    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
-  </si>
-  <si>
-    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
-  </si>
-  <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
-  </si>
-  <si>
-    <t>How the Quantity should be understood and represented.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
-  </si>
-  <si>
-    <t>Quantity.comparator</t>
-  </si>
-  <si>
-    <t>IVL properties</t>
-  </si>
-  <si>
-    <t>SN.1  / CQ.1</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.unit</t>
-  </si>
-  <si>
-    <t>Unit representation</t>
-  </si>
-  <si>
-    <t>A human-readable form of the unit.</t>
-  </si>
-  <si>
-    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
-  </si>
-  <si>
-    <t>Quantity.unit</t>
-  </si>
-  <si>
-    <t>PQ.unit</t>
-  </si>
-  <si>
-    <t>(see OBX.6 etc.) / CQ.2</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.system</t>
-  </si>
-  <si>
-    <t>System that defines coded unit form</t>
-  </si>
-  <si>
-    <t>The identification of the system that provides the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Need to know the system that defines the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Quantity.system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qty-3
-</t>
-  </si>
-  <si>
-    <t>CO.codeSystem, PQ.translation.codeSystem</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.code</t>
-  </si>
-  <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
-  </si>
-  <si>
-    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
-  </si>
-  <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>Quantity.code</t>
-  </si>
-  <si>
-    <t>PQ.code, MO.currency, PQ.translation.code</t>
-  </si>
-  <si>
     <t>MedicationRequest.dispenseRequest.performer</t>
   </si>
   <si>
@@ -1891,7 +1766,7 @@
 </t>
   </si>
   <si>
-    <t>Apotheke oder andere Einrichtung, die die Geplante Abgabe einlösen soll. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Intended dispenser</t>
   </si>
   <si>
     <t>Indicates the intended dispensing Organization specified by the prescriber.</t>
@@ -1903,7 +1778,7 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob das Arzneimittel substituiert werden darf (Absicht des Arztes, der die Geplante Abgabe erstellt). Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Any restrictions on medication substitution</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -1983,7 +1858,7 @@
 </t>
   </si>
   <si>
-    <t>Im Falle einer Änderung wird auf die ersetzte Geplante Abgabe verwiesen. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>An order/prescription that is being replaced</t>
   </si>
   <si>
     <t>A link to a resource representing an earlier order related order or prescription.</t>
@@ -2006,8 +1881,7 @@
 </t>
   </si>
   <si>
-    <t>Klinisches Problem mit Maßnahme, mittels Referenz auf Ressouce DetectedIssue. Keine Verwendung in der geplanten 
-Abgabe.</t>
+    <t>Clinical Issue with action</t>
   </si>
   <si>
     <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. Drug-drug interaction, duplicate therapy, dosage alert etc.</t>
@@ -2026,9 +1900,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf Provenance-Ressourcen, die 
-verschiedene relevante Versionen dieser Ressource dokumentieren. 
-Keine Verwendung in der geplanten Abgabe.</t>
+    <t>A list of events of interest in the lifecycle</t>
   </si>
   <si>
     <t>Links to Provenance records for past versions of this resource or fulfilling request or event resources that identify key state transitions or updates that are likely to be relevant to a user looking at the current version of the resource.</t>
@@ -2365,11 +2237,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO100"/>
+  <dimension ref="A1:AO93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="51.68359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.41015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="28.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -8406,13 +8278,13 @@
         <v>184</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>328</v>
+        <v>389</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8441,10 +8313,10 @@
         <v>188</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -8477,13 +8349,13 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8494,10 +8366,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8520,13 +8392,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8577,7 +8449,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8598,10 +8470,10 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -8609,10 +8481,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8638,13 +8510,13 @@
         <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8673,10 +8545,10 @@
         <v>188</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -8694,7 +8566,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8709,27 +8581,27 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8752,16 +8624,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8811,7 +8683,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8826,16 +8698,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>180</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
@@ -8843,10 +8715,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8869,13 +8741,13 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8926,7 +8798,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8941,13 +8813,13 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8958,10 +8830,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8987,10 +8859,10 @@
         <v>104</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9041,7 +8913,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9062,7 +8934,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -9073,10 +8945,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9099,13 +8971,13 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9156,7 +9028,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9171,13 +9043,13 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -9188,10 +9060,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9199,7 +9071,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
@@ -9217,14 +9089,14 @@
         <v>164</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9273,7 +9145,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9288,13 +9160,13 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -9305,10 +9177,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9334,13 +9206,13 @@
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9369,10 +9241,10 @@
         <v>188</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9390,7 +9262,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9411,7 +9283,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9422,10 +9294,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9448,13 +9320,13 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9505,7 +9377,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9520,13 +9392,13 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9537,10 +9409,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9563,13 +9435,13 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9620,7 +9492,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9635,13 +9507,13 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9652,10 +9524,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9678,16 +9550,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9725,17 +9597,17 @@
         <v>21</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9750,13 +9622,13 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -9767,13 +9639,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>21</v>
@@ -9795,16 +9667,16 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9854,7 +9726,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9869,13 +9741,13 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -9886,13 +9758,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>21</v>
@@ -9914,16 +9786,16 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9973,7 +9845,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9988,13 +9860,13 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -10005,13 +9877,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>21</v>
@@ -10033,16 +9905,16 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10092,7 +9964,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10107,13 +9979,13 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -10124,13 +9996,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>21</v>
@@ -10152,16 +10024,16 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10211,7 +10083,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10226,13 +10098,13 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -10243,13 +10115,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>21</v>
@@ -10271,16 +10143,16 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10330,7 +10202,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10345,13 +10217,13 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10362,10 +10234,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10388,13 +10260,13 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10445,7 +10317,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10463,10 +10335,10 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10477,10 +10349,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10592,10 +10464,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10709,14 +10581,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10738,10 +10610,10 @@
         <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>159</v>
@@ -10796,7 +10668,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10828,10 +10700,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10854,16 +10726,16 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10913,7 +10785,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10934,7 +10806,7 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10945,10 +10817,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11060,10 +10932,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11177,14 +11049,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11206,10 +11078,10 @@
         <v>135</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>159</v>
@@ -11264,7 +11136,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11296,10 +11168,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11322,13 +11194,13 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11379,7 +11251,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11400,7 +11272,7 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -11411,10 +11283,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11437,13 +11309,13 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11494,7 +11366,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11515,7 +11387,7 @@
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -11526,10 +11398,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11552,13 +11424,13 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11609,7 +11481,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11630,7 +11502,7 @@
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
@@ -11641,10 +11513,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11667,19 +11539,19 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -11728,7 +11600,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11746,10 +11618,10 @@
         <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -11760,10 +11632,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11786,16 +11658,16 @@
         <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11845,7 +11717,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11863,24 +11735,24 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11903,13 +11775,13 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11960,7 +11832,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11978,24 +11850,24 @@
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12018,16 +11890,16 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12077,7 +11949,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12095,10 +11967,10 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -12109,10 +11981,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12123,7 +11995,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>21</v>
@@ -12135,13 +12007,13 @@
         <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>219</v>
+        <v>549</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>220</v>
+        <v>550</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12192,7 +12064,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>222</v>
+        <v>548</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12204,7 +12076,7 @@
         <v>21</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>21</v>
@@ -12213,10 +12085,10 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>223</v>
+        <v>552</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>21</v>
@@ -12224,21 +12096,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>21</v>
@@ -12250,17 +12122,15 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>135</v>
+        <v>487</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>226</v>
+        <v>554</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -12297,40 +12167,40 @@
         <v>21</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>229</v>
+        <v>553</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>21</v>
+        <v>556</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>223</v>
+        <v>557</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12341,10 +12211,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12364,23 +12234,19 @@
         <v>21</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>550</v>
+        <v>219</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>551</v>
+        <v>220</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>21</v>
       </c>
@@ -12428,7 +12294,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>555</v>
+        <v>222</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12440,7 +12306,7 @@
         <v>21</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>21</v>
@@ -12449,61 +12315,59 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>556</v>
+        <v>223</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>557</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>559</v>
+        <v>226</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" t="s" s="2">
-        <v>561</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q87" t="s" s="2">
-        <v>562</v>
-      </c>
+      <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
         <v>21</v>
       </c>
@@ -12523,13 +12387,13 @@
         <v>21</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>563</v>
+        <v>21</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>564</v>
+        <v>21</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>21</v>
@@ -12547,19 +12411,19 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>565</v>
+        <v>229</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>21</v>
@@ -12568,54 +12432,56 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>566</v>
+        <v>223</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>567</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>21</v>
+        <v>495</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>219</v>
+        <v>135</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>569</v>
+        <v>496</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O88" t="s" s="2">
-        <v>571</v>
+        <v>160</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -12664,19 +12530,19 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>572</v>
+        <v>498</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>21</v>
@@ -12685,21 +12551,21 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>573</v>
+        <v>162</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>574</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12707,7 +12573,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>90</v>
@@ -12719,21 +12585,21 @@
         <v>21</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>104</v>
+        <v>562</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>21</v>
       </c>
@@ -12757,13 +12623,13 @@
         <v>21</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>21</v>
+        <v>566</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>21</v>
+        <v>567</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>21</v>
@@ -12781,16 +12647,16 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>580</v>
+        <v>21</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>102</v>
@@ -12799,24 +12665,24 @@
         <v>21</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>21</v>
+        <v>556</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12836,23 +12702,19 @@
         <v>21</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>110</v>
+        <v>184</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>586</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>21</v>
       </c>
@@ -12876,13 +12738,13 @@
         <v>21</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>21</v>
+        <v>574</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>21</v>
@@ -12900,7 +12762,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12918,24 +12780,24 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>21</v>
+        <v>575</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12958,13 +12820,13 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13015,7 +12877,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13030,16 +12892,16 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>21</v>
+        <v>582</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>21</v>
+        <v>575</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>400</v>
+        <v>21</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>21</v>
@@ -13047,14 +12909,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>21</v>
+        <v>585</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13073,15 +12935,17 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>486</v>
+        <v>586</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>21</v>
@@ -13130,13 +12994,13 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>21</v>
@@ -13148,10 +13012,10 @@
         <v>21</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>597</v>
+        <v>21</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>21</v>
@@ -13162,10 +13026,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13176,7 +13040,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>21</v>
@@ -13188,15 +13052,17 @@
         <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>219</v>
+        <v>592</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>220</v>
+        <v>593</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>21</v>
@@ -13245,855 +13111,38 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>222</v>
+        <v>591</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>21</v>
+        <v>596</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>223</v>
+        <v>597</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O94" s="2"/>
-      <c r="P94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="P95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
-      <c r="P98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="O99" s="2"/>
-      <c r="P99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O100" s="2"/>
-      <c r="P100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO100" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO100">
+  <autoFilter ref="A1:AO93">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14103,7 +13152,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI99">
+  <conditionalFormatting sqref="A2:AI92">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3469" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3469" uniqueCount="600">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1557,6 +1557,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+frequencySameAsWhenCount:wenn .when verwendet wird und periodUnit = d muss die frequency mit der Anzahl an entries in .when übereinstimmen {(timing.repeat.when.exists() and timing.repeat.periodUnit = 'd') implies timing.repeat.when.distinct().count() = timing.repeat.frequency}weekdaysRequireWeeklyPeriod:DayOfWeek kann nur dann verwendet werden, wenn periodUnit 'wk' ist. {timing.repeat.dayOfWeek.exists() implies timing.repeat.periodUnit = 'wk'}frequencyEqualsEventWeekdayProduct:Wenn Wochentage angegeben sind dann entspricht die frequency dem Produkt aus Wochentagen und der Anzahl an ausgewählten Tageszeiten. {timing.repeat.when.exists() and timing.repeat.dayOfWeek.exists() implies timing.repeat.frequency = timing.repeat.when.distinct().count() * timing.repeat.dayOfWeek.distinct().count()}noDuplicateWhen:Tageszeiten können nicht mehrmals vorkommen. {timing.repeat.when.count() = timing.repeat.when.distinct().count()}noDuplicateDayOfWeek:Wochentage können nicht mehrmals vorkommen. {timing.repeat.dayOfWeek.count() = timing.repeat.dayOfWeek.distinct().count()}allowedPeriodUnitsForStandardAdministration:Für Standarddosierungen im Tageszeitenschema sind nur tägliche, wöchentliche oder monatliche Wiederholungen zulässig. {timing.repeat.periodUnit = 'd' or timing.repeat.periodUnit = 'wk' or timing.repeat.periodUnit = 'm'}</t>
+  </si>
+  <si>
     <t>MedicationRequest.dispenseRequest</t>
   </si>
   <si>
@@ -1634,6 +1638,10 @@
   </si>
   <si>
     <t>The amount or quantity to provide as part of the first dispense.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>Supply.quantity[moodCode=RQO]</t>
@@ -10214,7 +10222,7 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>486</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>468</v>
@@ -10234,10 +10242,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10260,13 +10268,13 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10317,7 +10325,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10335,10 +10343,10 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10349,10 +10357,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10464,10 +10472,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10581,14 +10589,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10610,10 +10618,10 @@
         <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>159</v>
@@ -10668,7 +10676,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10700,10 +10708,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10726,16 +10734,16 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10785,7 +10793,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10806,7 +10814,7 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10817,10 +10825,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10932,10 +10940,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11049,14 +11057,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11078,10 +11086,10 @@
         <v>135</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>159</v>
@@ -11136,7 +11144,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11168,10 +11176,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11194,13 +11202,13 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11251,7 +11259,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11263,7 +11271,7 @@
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
@@ -11272,7 +11280,7 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -11283,10 +11291,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11309,13 +11317,13 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11366,7 +11374,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11387,7 +11395,7 @@
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -11398,10 +11406,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11424,13 +11432,13 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11481,7 +11489,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11502,7 +11510,7 @@
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
@@ -11513,10 +11521,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11539,19 +11547,19 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -11600,7 +11608,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11618,10 +11626,10 @@
         <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -11632,10 +11640,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11658,16 +11666,16 @@
         <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11717,7 +11725,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11735,24 +11743,24 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11775,13 +11783,13 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11832,7 +11840,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11844,30 +11852,30 @@
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11890,16 +11898,16 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11949,7 +11957,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -11967,10 +11975,10 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -11981,10 +11989,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12007,13 +12015,13 @@
         <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12064,7 +12072,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12085,7 +12093,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>401</v>
@@ -12096,10 +12104,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12122,13 +12130,13 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12179,7 +12187,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12197,10 +12205,10 @@
         <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12211,10 +12219,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12326,10 +12334,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12443,14 +12451,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12472,10 +12480,10 @@
         <v>135</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>159</v>
@@ -12530,7 +12538,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12562,10 +12570,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12588,16 +12596,16 @@
         <v>21</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12626,10 +12634,10 @@
         <v>188</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>21</v>
@@ -12647,7 +12655,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>90</v>
@@ -12665,24 +12673,24 @@
         <v>21</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12708,10 +12716,10 @@
         <v>184</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12741,10 +12749,10 @@
         <v>188</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>21</v>
@@ -12762,7 +12770,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12780,24 +12788,24 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12820,13 +12828,13 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12877,7 +12885,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -12892,13 +12900,13 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>21</v>
@@ -12909,14 +12917,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12935,16 +12943,16 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12994,7 +13002,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13015,7 +13023,7 @@
         <v>21</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>21</v>
@@ -13026,10 +13034,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13052,16 +13060,16 @@
         <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13111,7 +13119,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13126,13 +13134,13 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>90</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$105</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3469" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3910" uniqueCount="654">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
+    <t>Technische id der Ressource</t>
   </si>
   <si>
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
@@ -336,14 +336,191 @@
 </t>
   </si>
   <si>
-    <t>MedicationRequest.implicitRules</t>
+    <t>MedicationRequest.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>MedicationRequest.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>MedicationRequest.implicitRules</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: Die Ressource wird nach den Regeln dieses Implementierungsleitfadens interpretiert. Zusätzliche implizite Verarbeitungsregeln werden nicht verwendet.</t>
   </si>
   <si>
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
@@ -407,6 +584,59 @@
   </si>
   <si>
     <t>Act.text?</t>
+  </si>
+  <si>
+    <t>MedicationRequest.text.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.text.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.text.status</t>
+  </si>
+  <si>
+    <t>generated | extensions | additional | empty</t>
+  </si>
+  <si>
+    <t>The status of the narrative - whether it's entirely generated (from just the defined data or the extensions too), or whether a human authored it and it may contain additional data.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The status of a resource narrative.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/narrative-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Narrative.status</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>MedicationRequest.text.div</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xhtml
+</t>
+  </si>
+  <si>
+    <t>Limited xhtml content</t>
+  </si>
+  <si>
+    <t>The actual narrative content, a stripped down version of XHTML.</t>
+  </si>
+  <si>
+    <t>The contents of the html element are an XHTML fragment containing only the basic html formatting elements described in chapters 7-11 and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained stylesheets. The XHTML content SHALL NOT contain a head, a body, external stylesheet references, scripts, forms, base/link/xlink, frames, iframes and objects.</t>
+  </si>
+  <si>
+    <t>Narrative.div</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+txt-1:The narrative SHALL contain only the basic html formatting elements and attributes described in chapters 7-11 (except section 4 of chapter 9) and 15 of the HTML 4.0 standard, &lt;a&gt; elements (either name or href), images and internally contained style attributes {htmlChecks()}txt-2:The narrative SHALL have some non-whitespace content {htmlChecks()}</t>
   </si>
   <si>
     <t>MedicationRequest.contained</t>
@@ -443,28 +673,13 @@
     <t>MedicationRequest.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
     <t>Extension</t>
   </si>
   <si>
     <t>An Extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationRequest.extension:effectiveDosePeriod</t>
@@ -514,10 +729,6 @@
     <t>MedicationRequest.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -525,16 +736,10 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>MedicationRequest.identifier</t>
@@ -580,9 +785,6 @@
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/GeplanteAbgabeStatusVS</t>
   </si>
   <si>
@@ -612,9 +814,6 @@
   </si>
   <si>
     <t>This is generally only used for "exception" statuses such as "suspended" or "cancelled". The reason why the MedicationRequest was created at all is captured in reasonCode, not here.</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Identifies the reasons for a given status.</t>
@@ -716,48 +915,16 @@
     <t>MedicationRequest.category.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>MedicationRequest.category:mrcategory.extension</t>
   </si>
   <si>
     <t>MedicationRequest.category.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>MedicationRequest.category:mrcategory.coding</t>
   </si>
   <si>
     <t>MedicationRequest.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -2245,7 +2412,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO93"/>
+  <dimension ref="A1:AO105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
@@ -2778,16 +2945,16 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>104</v>
@@ -2798,9 +2965,7 @@
       <c r="M5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
@@ -2849,7 +3014,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2861,7 +3026,7 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
@@ -2870,7 +3035,7 @@
         <v>21</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>21</v>
@@ -2888,14 +3053,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2907,16 +3072,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2942,43 +3107,43 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
@@ -2987,7 +3152,7 @@
         <v>21</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>21</v>
@@ -2998,18 +3163,18 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>90</v>
@@ -3021,10 +3186,10 @@
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>121</v>
@@ -3104,7 +3269,7 @@
         <v>21</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>21</v>
@@ -3115,10 +3280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -3129,7 +3294,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>91</v>
@@ -3138,19 +3303,19 @@
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3200,28 +3365,28 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>21</v>
@@ -3232,10 +3397,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3246,7 +3411,7 @@
         <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -3255,18 +3420,20 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -3303,29 +3470,31 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
@@ -3343,16 +3512,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>21</v>
       </c>
@@ -3361,28 +3528,28 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3432,7 +3599,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3441,10 +3608,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -3464,14 +3631,12 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
@@ -3480,7 +3645,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -3489,19 +3654,19 @@
         <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3527,13 +3692,13 @@
         <v>21</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>21</v>
@@ -3551,7 +3716,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3560,10 +3725,10 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
@@ -3583,14 +3748,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3603,26 +3768,24 @@
         <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="J12" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K12" t="s" s="2">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -3646,13 +3809,13 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
@@ -3670,7 +3833,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3682,7 +3845,7 @@
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
@@ -3691,7 +3854,7 @@
         <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>21</v>
@@ -3702,10 +3865,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3722,22 +3885,22 @@
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3787,13 +3950,13 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>21</v>
@@ -3802,27 +3965,27 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3830,31 +3993,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3880,11 +4043,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3905,7 +4070,7 @@
         <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>90</v>
@@ -3917,41 +4082,41 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
@@ -3960,16 +4125,16 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3995,13 +4160,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>189</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -4019,7 +4184,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4034,13 +4199,13 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>21</v>
@@ -4049,12 +4214,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4062,32 +4227,30 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>194</v>
+        <v>105</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -4097,7 +4260,7 @@
         <v>21</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>197</v>
+        <v>21</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>21</v>
@@ -4112,13 +4275,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -4136,10 +4299,10 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>90</v>
@@ -4148,19 +4311,19 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>201</v>
+        <v>108</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>21</v>
@@ -4168,18 +4331,18 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>81</v>
@@ -4194,16 +4357,16 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>205</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>207</v>
+        <v>114</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4229,29 +4392,31 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AC17" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>118</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4263,19 +4428,19 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>212</v>
+        <v>108</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>21</v>
@@ -4283,14 +4448,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>21</v>
       </c>
@@ -4311,17 +4474,15 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>215</v>
+        <v>185</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -4346,11 +4507,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y18" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -4368,13 +4531,13 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
@@ -4386,24 +4549,24 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4411,13 +4574,13 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
@@ -4426,15 +4589,17 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -4483,10 +4648,10 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>90</v>
@@ -4495,7 +4660,7 @@
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
@@ -4504,7 +4669,7 @@
         <v>21</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>21</v>
@@ -4513,16 +4678,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4532,7 +4697,7 @@
         <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>21</v>
@@ -4541,16 +4706,16 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4588,19 +4753,19 @@
         <v>21</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4612,16 +4777,16 @@
         <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
@@ -4632,10 +4797,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4655,23 +4820,19 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>232</v>
+        <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -4707,19 +4868,17 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4731,7 +4890,7 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>21</v>
@@ -4740,23 +4899,25 @@
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>239</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4777,15 +4938,17 @@
         <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4834,19 +4997,19 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>21</v>
@@ -4855,7 +5018,7 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4866,21 +5029,23 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
@@ -4892,16 +5057,16 @@
         <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>220</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>159</v>
+        <v>223</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4939,19 +5104,19 @@
         <v>21</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4960,10 +5125,10 @@
         <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>21</v>
@@ -4972,7 +5137,7 @@
         <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
@@ -4983,45 +5148,45 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>248</v>
+        <v>114</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -5031,7 +5196,7 @@
         <v>21</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>21</v>
@@ -5070,19 +5235,19 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>21</v>
@@ -5091,21 +5256,21 @@
         <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>252</v>
+        <v>191</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5116,7 +5281,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -5125,19 +5290,19 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5187,13 +5352,13 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
@@ -5202,27 +5367,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>21</v>
+        <v>235</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>261</v>
+        <v>238</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5230,33 +5395,33 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -5265,7 +5430,7 @@
         <v>21</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>21</v>
@@ -5280,13 +5445,11 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -5304,10 +5467,10 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>90</v>
@@ -5319,27 +5482,27 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5350,7 +5513,7 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
@@ -5359,21 +5522,21 @@
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -5397,13 +5560,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>21</v>
+        <v>253</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>21</v>
+        <v>254</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -5421,7 +5584,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5436,27 +5599,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>21</v>
+        <v>255</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>277</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5464,35 +5627,33 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>280</v>
+        <v>166</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -5501,7 +5662,7 @@
         <v>21</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>21</v>
+        <v>261</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>21</v>
@@ -5516,13 +5677,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>21</v>
+        <v>263</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5540,10 +5701,10 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>90</v>
@@ -5555,27 +5716,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>287</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5583,10 +5744,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>268</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -5595,23 +5756,21 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5635,37 +5794,35 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>267</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
@@ -5677,27 +5834,27 @@
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>296</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>203</v>
+        <v>267</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>21</v>
@@ -5719,16 +5876,16 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>184</v>
+        <v>249</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>206</v>
+        <v>270</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>207</v>
+        <v>271</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5754,11 +5911,11 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5776,7 +5933,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>203</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5794,13 +5951,13 @@
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>211</v>
+        <v>275</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>212</v>
+        <v>276</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>202</v>
+        <v>266</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>21</v>
@@ -5808,10 +5965,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>218</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5834,13 +5991,13 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>219</v>
+        <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>220</v>
+        <v>105</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>221</v>
+        <v>106</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5891,7 +6048,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>222</v>
+        <v>107</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5912,7 +6069,7 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
@@ -5923,14 +6080,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>225</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5949,16 +6106,16 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>227</v>
+        <v>113</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5996,19 +6153,19 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>229</v>
+        <v>118</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6020,7 +6177,7 @@
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
@@ -6029,7 +6186,7 @@
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>21</v>
@@ -6040,10 +6197,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6051,7 +6208,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>81</v>
@@ -6066,19 +6223,19 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>232</v>
+        <v>144</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>233</v>
+        <v>287</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>234</v>
+        <v>288</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>235</v>
+        <v>289</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>236</v>
+        <v>290</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -6127,7 +6284,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>237</v>
+        <v>291</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6148,21 +6305,21 @@
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>238</v>
+        <v>292</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>239</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>241</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6185,13 +6342,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>219</v>
+        <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>220</v>
+        <v>105</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>221</v>
+        <v>106</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6242,7 +6399,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>222</v>
+        <v>107</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6263,7 +6420,7 @@
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
@@ -6274,14 +6431,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>243</v>
+        <v>297</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6300,16 +6457,16 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>227</v>
+        <v>113</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6347,19 +6504,19 @@
         <v>21</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>229</v>
+        <v>118</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6371,7 +6528,7 @@
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>21</v>
@@ -6380,7 +6537,7 @@
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
@@ -6391,10 +6548,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>245</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6417,19 +6574,19 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>246</v>
+        <v>300</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>247</v>
+        <v>301</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>248</v>
+        <v>302</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>249</v>
+        <v>303</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -6439,7 +6596,7 @@
         <v>21</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>21</v>
@@ -6478,7 +6635,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>251</v>
+        <v>305</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6499,13 +6656,13 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>252</v>
+        <v>306</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>253</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -6513,7 +6670,7 @@
         <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>255</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6536,16 +6693,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>219</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>256</v>
+        <v>310</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>257</v>
+        <v>311</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6595,7 +6752,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>259</v>
+        <v>313</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6616,21 +6773,21 @@
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>260</v>
+        <v>314</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>261</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6638,7 +6795,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>90</v>
@@ -6653,17 +6810,17 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>265</v>
+        <v>319</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>266</v>
+        <v>320</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6673,7 +6830,7 @@
         <v>21</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>21</v>
+        <v>268</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>21</v>
@@ -6712,7 +6869,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>267</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6733,21 +6890,21 @@
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>268</v>
+        <v>322</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>269</v>
+        <v>323</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>271</v>
+        <v>325</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6770,17 +6927,17 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>219</v>
+        <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>273</v>
+        <v>327</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>274</v>
+        <v>328</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6829,7 +6986,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>275</v>
+        <v>329</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6850,21 +7007,21 @@
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>276</v>
+        <v>330</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>277</v>
+        <v>331</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>279</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6887,19 +7044,19 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>280</v>
+        <v>334</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>281</v>
+        <v>335</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>282</v>
+        <v>336</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>283</v>
+        <v>337</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>284</v>
+        <v>338</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6948,7 +7105,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>285</v>
+        <v>339</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6969,21 +7126,21 @@
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>286</v>
+        <v>340</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>287</v>
+        <v>341</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>289</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7006,19 +7163,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>219</v>
+        <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>290</v>
+        <v>344</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>291</v>
+        <v>345</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>292</v>
+        <v>346</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>293</v>
+        <v>347</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -7067,7 +7224,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>294</v>
+        <v>348</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7088,52 +7245,56 @@
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>295</v>
+        <v>349</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>296</v>
+        <v>350</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>110</v>
+        <v>249</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>314</v>
+        <v>353</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -7158,13 +7319,11 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>317</v>
+        <v>354</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -7182,13 +7341,13 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>313</v>
+        <v>267</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
@@ -7197,16 +7356,16 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>318</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>319</v>
+        <v>276</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>320</v>
+        <v>266</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
@@ -7214,10 +7373,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>321</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7228,29 +7387,27 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>280</v>
+        <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>322</v>
+        <v>105</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -7299,7 +7456,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>321</v>
+        <v>107</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7311,7 +7468,7 @@
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
@@ -7320,7 +7477,7 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>325</v>
+        <v>108</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7331,21 +7488,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>326</v>
+        <v>284</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -7354,18 +7511,20 @@
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>327</v>
+        <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>328</v>
+        <v>112</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -7402,31 +7561,31 @@
         <v>21</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>326</v>
+        <v>118</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
@@ -7435,7 +7594,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>330</v>
+        <v>108</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7444,12 +7603,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>331</v>
+        <v>286</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7460,10 +7619,10 @@
         <v>90</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -7472,18 +7631,20 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>332</v>
+        <v>144</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>333</v>
+        <v>287</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>334</v>
+        <v>288</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -7531,13 +7692,13 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
@@ -7546,27 +7707,27 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>338</v>
+        <v>292</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>340</v>
+        <v>293</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>341</v>
+        <v>295</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7574,32 +7735,30 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>342</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>343</v>
+        <v>105</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7648,10 +7807,10 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>341</v>
+        <v>107</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>90</v>
@@ -7660,41 +7819,41 @@
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>346</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>348</v>
+        <v>108</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>349</v>
+        <v>21</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>350</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>351</v>
+        <v>297</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7706,16 +7865,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>352</v>
+        <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>354</v>
+        <v>113</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>355</v>
+        <v>114</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7753,46 +7912,46 @@
         <v>21</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>351</v>
+        <v>118</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>357</v>
+        <v>108</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>359</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -7800,7 +7959,7 @@
         <v>360</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>360</v>
+        <v>299</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7808,10 +7967,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7820,19 +7979,23 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>361</v>
+        <v>132</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>21</v>
       </c>
@@ -7841,7 +8004,7 @@
         <v>21</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>21</v>
@@ -7880,13 +8043,13 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>360</v>
+        <v>305</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
@@ -7895,27 +8058,27 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>365</v>
+        <v>306</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>21</v>
+        <v>307</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>366</v>
+        <v>309</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7923,13 +8086,13 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -7938,15 +8101,17 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>367</v>
+        <v>104</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>368</v>
+        <v>310</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7995,7 +8160,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>366</v>
+        <v>313</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8010,27 +8175,27 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>370</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>371</v>
+        <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>372</v>
+        <v>314</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>373</v>
+        <v>21</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>374</v>
+        <v>315</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>375</v>
+        <v>317</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8044,7 +8209,7 @@
         <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -8053,16 +8218,18 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>376</v>
+        <v>166</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>377</v>
+        <v>318</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>378</v>
+        <v>319</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -8110,7 +8277,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>375</v>
+        <v>321</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8125,27 +8292,27 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>379</v>
+        <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>21</v>
+        <v>323</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>381</v>
+        <v>325</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8156,7 +8323,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -8165,19 +8332,21 @@
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>382</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>383</v>
+        <v>326</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
       </c>
@@ -8225,7 +8394,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>381</v>
+        <v>329</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8240,27 +8409,27 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>387</v>
+        <v>21</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>21</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>388</v>
+        <v>333</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8271,7 +8440,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -8283,18 +8452,20 @@
         <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>184</v>
+        <v>334</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>389</v>
+        <v>335</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>390</v>
+        <v>336</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -8318,13 +8489,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>393</v>
+        <v>21</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -8342,7 +8513,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8357,27 +8528,27 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>394</v>
+        <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>395</v>
+        <v>340</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>21</v>
+        <v>341</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>396</v>
+        <v>366</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>396</v>
+        <v>343</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8388,7 +8559,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -8397,19 +8568,23 @@
         <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>397</v>
+        <v>104</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>398</v>
+        <v>344</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -8457,7 +8632,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>396</v>
+        <v>348</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8478,21 +8653,21 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>400</v>
+        <v>349</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>402</v>
+        <v>367</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>402</v>
+        <v>367</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8512,20 +8687,18 @@
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>403</v>
+        <v>368</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8550,13 +8723,13 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>406</v>
+        <v>370</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>407</v>
+        <v>371</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -8574,13 +8747,13 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>402</v>
+        <v>367</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
@@ -8589,27 +8762,27 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>408</v>
+        <v>372</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>409</v>
+        <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>410</v>
+        <v>373</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>411</v>
+        <v>374</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>412</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>375</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>375</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8620,28 +8793,28 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>414</v>
+        <v>334</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>415</v>
+        <v>376</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>416</v>
+        <v>377</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>417</v>
+        <v>378</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8691,13 +8864,13 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>413</v>
+        <v>375</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
@@ -8706,16 +8879,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>418</v>
+        <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>419</v>
+        <v>379</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>411</v>
+        <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
@@ -8723,10 +8896,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8749,13 +8922,13 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>421</v>
+        <v>381</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>422</v>
+        <v>382</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>423</v>
+        <v>383</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8806,13 +8979,13 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
@@ -8821,13 +8994,13 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>424</v>
+        <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8836,12 +9009,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8849,13 +9022,13 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
@@ -8864,15 +9037,17 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>104</v>
+        <v>386</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8921,13 +9096,13 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
@@ -8936,27 +9111,27 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>21</v>
+        <v>390</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>21</v>
+        <v>391</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>425</v>
+        <v>392</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>21</v>
+        <v>394</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>429</v>
+        <v>395</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>429</v>
+        <v>395</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8979,15 +9154,17 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>430</v>
+        <v>396</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -9036,13 +9213,13 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>429</v>
+        <v>395</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
@@ -9051,27 +9228,27 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>434</v>
+        <v>402</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>21</v>
+        <v>403</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>21</v>
+        <v>404</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>435</v>
+        <v>405</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>435</v>
+        <v>405</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9082,30 +9259,30 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>164</v>
+        <v>406</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>436</v>
+        <v>407</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9153,7 +9330,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>435</v>
+        <v>405</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9168,27 +9345,27 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>439</v>
+        <v>410</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>21</v>
+        <v>413</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9211,17 +9388,15 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>184</v>
+        <v>415</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -9246,13 +9421,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>445</v>
+        <v>21</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9270,13 +9445,13 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
@@ -9285,27 +9460,27 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>447</v>
+        <v>419</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9313,28 +9488,28 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>449</v>
+        <v>421</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>451</v>
+        <v>423</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9385,13 +9560,13 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
@@ -9400,27 +9575,27 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>452</v>
+        <v>424</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>453</v>
+        <v>426</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>21</v>
+        <v>428</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9428,10 +9603,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>91</v>
@@ -9440,16 +9615,16 @@
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9500,13 +9675,13 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
@@ -9515,16 +9690,16 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>459</v>
+        <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>460</v>
+        <v>402</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>21</v>
@@ -9532,10 +9707,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9543,13 +9718,13 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>21</v>
@@ -9558,17 +9733,15 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9605,23 +9778,25 @@
         <v>21</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>467</v>
+        <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
@@ -9630,31 +9805,29 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>469</v>
+        <v>440</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>21</v>
+        <v>441</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>470</v>
+        <v>442</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>471</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9663,28 +9836,28 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K64" t="s" s="2">
-        <v>472</v>
+        <v>249</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>465</v>
+        <v>445</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9710,13 +9883,13 @@
         <v>21</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>21</v>
+        <v>446</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>21</v>
+        <v>447</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>21</v>
@@ -9734,13 +9907,13 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
@@ -9749,13 +9922,13 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>469</v>
+        <v>449</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -9764,16 +9937,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9782,10 +9953,10 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>21</v>
@@ -9794,17 +9965,15 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>476</v>
+        <v>451</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9853,13 +10022,13 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
@@ -9868,31 +10037,29 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>468</v>
+        <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>21</v>
+        <v>455</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>21</v>
       </c>
@@ -9901,10 +10068,10 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>21</v>
@@ -9913,16 +10080,16 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>479</v>
+        <v>249</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9948,13 +10115,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>21</v>
+        <v>460</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>21</v>
+        <v>461</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9972,7 +10139,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9987,31 +10154,29 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>21</v>
+        <v>463</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>21</v>
+        <v>465</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>21</v>
       </c>
@@ -10023,7 +10188,7 @@
         <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>21</v>
@@ -10032,16 +10197,16 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10091,7 +10256,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10106,31 +10271,29 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>21</v>
+        <v>465</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>21</v>
       </c>
@@ -10139,29 +10302,27 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K68" t="s" s="2">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -10210,7 +10371,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10222,16 +10383,16 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>486</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10240,12 +10401,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10253,28 +10414,28 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K69" t="s" s="2">
-        <v>488</v>
+        <v>132</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10325,13 +10486,13 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
@@ -10343,10 +10504,10 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>491</v>
+        <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10355,12 +10516,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10368,28 +10529,28 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>219</v>
+        <v>484</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>220</v>
+        <v>485</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>221</v>
+        <v>486</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10440,28 +10601,28 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>222</v>
+        <v>483</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>21</v>
+        <v>487</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>223</v>
+        <v>488</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -10470,46 +10631,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>226</v>
+        <v>490</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -10557,28 +10718,28 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>229</v>
+        <v>489</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>21</v>
+        <v>493</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>223</v>
+        <v>494</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
@@ -10596,39 +10757,37 @@
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>135</v>
+        <v>249</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="N72" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>160</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
@@ -10652,13 +10811,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>21</v>
+        <v>499</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -10676,19 +10835,19 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
@@ -10697,7 +10856,7 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>162</v>
+        <v>501</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
@@ -10708,10 +10867,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10734,17 +10893,15 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -10793,13 +10950,13 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
@@ -10808,13 +10965,13 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>21</v>
+        <v>506</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10823,12 +10980,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10839,10 +10996,10 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
@@ -10851,13 +11008,13 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>219</v>
+        <v>509</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>220</v>
+        <v>510</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>221</v>
+        <v>511</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10908,28 +11065,28 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>222</v>
+        <v>508</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>21</v>
+        <v>512</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>21</v>
+        <v>513</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>223</v>
+        <v>514</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10940,24 +11097,24 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>21</v>
@@ -10966,16 +11123,16 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>135</v>
+        <v>516</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>226</v>
+        <v>517</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>227</v>
+        <v>518</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>159</v>
+        <v>519</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11013,19 +11170,17 @@
         <v>21</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>21</v>
+        <v>521</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>229</v>
+        <v>515</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11037,16 +11192,16 @@
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>21</v>
+        <v>522</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>223</v>
+        <v>523</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -11055,16 +11210,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="C76" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="D76" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11074,29 +11231,27 @@
         <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>135</v>
+        <v>526</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>497</v>
+        <v>527</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -11144,7 +11299,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11156,16 +11311,16 @@
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>21</v>
+        <v>522</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>162</v>
+        <v>523</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -11174,14 +11329,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>21</v>
       </c>
@@ -11190,10 +11347,10 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>21</v>
@@ -11202,15 +11359,17 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>510</v>
+        <v>527</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>519</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>21</v>
@@ -11259,28 +11418,28 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>512</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>21</v>
+        <v>522</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -11289,14 +11448,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>21</v>
       </c>
@@ -11305,10 +11466,10 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>21</v>
@@ -11317,15 +11478,17 @@
         <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>519</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -11374,13 +11537,13 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>21</v>
@@ -11389,13 +11552,13 @@
         <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>21</v>
+        <v>522</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -11404,14 +11567,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="D79" t="s" s="2">
         <v>21</v>
       </c>
@@ -11420,10 +11585,10 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>21</v>
@@ -11432,15 +11597,17 @@
         <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>519</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -11489,13 +11656,13 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>21</v>
@@ -11504,13 +11671,13 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>21</v>
+        <v>522</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
@@ -11521,21 +11688,23 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="C80" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="D80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>91</v>
@@ -11547,20 +11716,18 @@
         <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>21</v>
       </c>
@@ -11608,28 +11775,28 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AK80" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AL80" t="s" s="2">
-        <v>528</v>
+        <v>21</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -11640,10 +11807,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11666,17 +11833,15 @@
         <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>534</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -11725,7 +11890,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11743,24 +11908,24 @@
         <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>537</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11768,13 +11933,13 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>21</v>
@@ -11783,13 +11948,13 @@
         <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>509</v>
+        <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>539</v>
+        <v>105</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>540</v>
+        <v>106</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11840,7 +12005,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>538</v>
+        <v>107</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11852,41 +12017,41 @@
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>512</v>
+        <v>21</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>541</v>
+        <v>21</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>542</v>
+        <v>108</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>543</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -11898,16 +12063,16 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>515</v>
+        <v>111</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>545</v>
+        <v>112</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>546</v>
+        <v>113</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>547</v>
+        <v>114</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11957,28 +12122,28 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>544</v>
+        <v>118</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>548</v>
+        <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>549</v>
+        <v>108</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -11989,42 +12154,46 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>21</v>
+        <v>550</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+      <c r="N84" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -12072,19 +12241,19 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>21</v>
@@ -12093,10 +12262,10 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>554</v>
+        <v>191</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>21</v>
@@ -12104,10 +12273,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12130,15 +12299,17 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>488</v>
+        <v>542</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -12187,7 +12358,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12205,10 +12376,10 @@
         <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12219,10 +12390,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12245,13 +12416,13 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>219</v>
+        <v>104</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>220</v>
+        <v>105</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>221</v>
+        <v>106</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12302,7 +12473,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>222</v>
+        <v>107</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12323,7 +12494,7 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
@@ -12334,14 +12505,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12360,16 +12531,16 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>227</v>
+        <v>113</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12419,7 +12590,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>229</v>
+        <v>118</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12431,7 +12602,7 @@
         <v>21</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>21</v>
@@ -12440,7 +12611,7 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
@@ -12451,14 +12622,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>496</v>
+        <v>550</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12477,19 +12648,19 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>497</v>
+        <v>551</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>498</v>
+        <v>552</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -12538,7 +12709,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>499</v>
+        <v>553</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12550,7 +12721,7 @@
         <v>21</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>21</v>
@@ -12559,7 +12730,7 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
@@ -12570,10 +12741,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12581,7 +12752,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>90</v>
@@ -12596,17 +12767,15 @@
         <v>21</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>567</v>
-      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>21</v>
@@ -12631,13 +12800,13 @@
         <v>21</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>568</v>
+        <v>21</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>569</v>
+        <v>21</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>21</v>
@@ -12655,10 +12824,10 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>90</v>
@@ -12667,30 +12836,30 @@
         <v>21</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>102</v>
+        <v>566</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>558</v>
+        <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>571</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12713,13 +12882,13 @@
         <v>21</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>184</v>
+        <v>569</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12746,13 +12915,13 @@
         <v>21</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>575</v>
+        <v>21</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>576</v>
+        <v>21</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>21</v>
@@ -12770,7 +12939,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12788,24 +12957,24 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>577</v>
+        <v>21</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>579</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12828,13 +12997,13 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12885,7 +13054,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -12900,13 +13069,13 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>584</v>
+        <v>21</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>577</v>
+        <v>21</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>21</v>
@@ -12915,26 +13084,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>587</v>
+        <v>21</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>21</v>
@@ -12943,18 +13112,20 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>21</v>
       </c>
@@ -13002,13 +13173,13 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>21</v>
@@ -13020,10 +13191,10 @@
         <v>21</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>21</v>
+        <v>582</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>21</v>
@@ -13032,12 +13203,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13045,13 +13216,13 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>21</v>
@@ -13060,16 +13231,16 @@
         <v>21</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13119,13 +13290,13 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>21</v>
@@ -13134,23 +13305,1417 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="AL93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM93" t="s" s="2">
+      <c r="B95" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="AN93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO93" t="s" s="2">
+      <c r="M95" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO105" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO93">
+  <autoFilter ref="A1:AO105">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13160,7 +14725,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI92">
+  <conditionalFormatting sqref="A2:AI104">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$181</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6748" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6710" uniqueCount="876">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1374,8 +1374,7 @@
 </t>
   </si>
   <si>
-    <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit 
-Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
+    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als logische Referenz dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -1473,160 +1472,6 @@
     <t>.identifier</t>
   </si>
   <si>
-    <t>MedicationRequest.medication[x].identifier.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].identifier.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].identifier.type</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].identifier.period</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
     <t>MedicationRequest.medication[x].display</t>
   </si>
   <si>
@@ -1699,19 +1544,149 @@
     <t>MedicationRequest.subject.identifier.use</t>
   </si>
   <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
     <t>MedicationRequest.subject.identifier.type</t>
   </si>
   <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
     <t>MedicationRequest.subject.identifier.system</t>
   </si>
   <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
     <t>MedicationRequest.subject.identifier.value</t>
   </si>
   <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
     <t>MedicationRequest.subject.identifier.period</t>
   </si>
   <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
     <t>MedicationRequest.subject.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
     <t>MedicationRequest.subject.display</t>
@@ -2313,6 +2288,36 @@
     <t>MedicationRequest.dispenseRequest.modifierExtension</t>
   </si>
   <si>
+    <t>Fachliche Begründung: Für die Abgabedetails sind keine zusätzlichen Erweiterungen vorgesehen, die deren Bedeutung verändern.</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.initialFill</t>
+  </si>
+  <si>
+    <t>First fill details</t>
+  </si>
+  <si>
+    <t>Indicates the quantity or duration for the first dispense of the medication.</t>
+  </si>
+  <si>
+    <t>If populating this element, either the quantity or the duration must be included.</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration -&gt; ActRelationship[sequenceNumber = '1'] -&gt; Supply</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.initialFill.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.initialFill.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.initialFill.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user contentmodifiers</t>
   </si>
@@ -2325,33 +2330,6 @@
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.initialFill</t>
-  </si>
-  <si>
-    <t>First fill details</t>
-  </si>
-  <si>
-    <t>Indicates the quantity or duration for the first dispense of the medication.</t>
-  </si>
-  <si>
-    <t>If populating this element, either the quantity or the duration must be included.</t>
-  </si>
-  <si>
-    <t>SubstanceAdministration -&gt; ActRelationship[sequenceNumber = '1'] -&gt; Supply</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.initialFill.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.initialFill.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.initialFill.modifierExtension</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.initialFill.quantity</t>
@@ -2482,6 +2460,134 @@
   </si>
   <si>
     <t>RXD-4-Actual Dispense Amount / RXD-5.1-Actual Dispense Units.code / RXD-5.3-Actual Dispense Units.name of coding system</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.quantity.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.quantity.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.quantity.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
+  </si>
+  <si>
+    <t>SN.2  / CQ - N/A</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.quantity.comparator</t>
+  </si>
+  <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>Not allowed to be used in this context</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>IVL properties</t>
+  </si>
+  <si>
+    <t>SN.1  / CQ.1</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.quantity.unit</t>
+  </si>
+  <si>
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>PQ.unit</t>
+  </si>
+  <si>
+    <t>(see OBX.6 etc.) / CQ.2</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.quantity.system</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
+</t>
+  </si>
+  <si>
+    <t>CO.codeSystem, PQ.translation.codeSystem</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.quantity.code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
@@ -2976,7 +3082,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO182"/>
+  <dimension ref="A1:AO181"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.57421875" customWidth="true" bestFit="true"/>
@@ -11544,7 +11650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>457</v>
       </c>
@@ -11563,7 +11669,7 @@
         <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>21</v>
@@ -11686,18 +11792,20 @@
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>105</v>
+        <v>464</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -11746,7 +11854,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>107</v>
+        <v>467</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11758,7 +11866,7 @@
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
@@ -11767,7 +11875,7 @@
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
@@ -11776,44 +11884,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>111</v>
+        <v>469</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>112</v>
+        <v>470</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>113</v>
+        <v>471</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>114</v>
+        <v>472</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11851,54 +11959,54 @@
         <v>21</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>118</v>
+        <v>468</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>21</v>
+        <v>473</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>21</v>
+        <v>474</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>108</v>
+        <v>475</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>21</v>
+        <v>476</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>21</v>
+        <v>477</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11915,26 +12023,22 @@
         <v>21</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>466</v>
+        <v>105</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -11958,13 +12062,13 @@
         <v>21</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>470</v>
+        <v>21</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>471</v>
+        <v>21</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>21</v>
@@ -11982,7 +12086,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>472</v>
+        <v>107</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11994,7 +12098,7 @@
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
@@ -12003,32 +12107,32 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>473</v>
+        <v>108</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>21</v>
@@ -12037,23 +12141,21 @@
         <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>295</v>
+        <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>475</v>
+        <v>112</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>476</v>
+        <v>113</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -12077,43 +12179,43 @@
         <v>21</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>479</v>
+        <v>21</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>480</v>
+        <v>21</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>481</v>
+        <v>118</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>21</v>
@@ -12122,21 +12224,21 @@
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>473</v>
+        <v>108</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>482</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12159,20 +12261,18 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>485</v>
+        <v>446</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>21</v>
       </c>
@@ -12184,7 +12284,7 @@
         <v>21</v>
       </c>
       <c r="T79" t="s" s="2">
-        <v>488</v>
+        <v>21</v>
       </c>
       <c r="U79" t="s" s="2">
         <v>21</v>
@@ -12220,7 +12320,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>489</v>
+        <v>448</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12229,7 +12329,7 @@
         <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>102</v>
@@ -12241,21 +12341,21 @@
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>490</v>
+        <v>191</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>491</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12269,7 +12369,7 @@
         <v>90</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>21</v>
@@ -12278,16 +12378,16 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>493</v>
+        <v>451</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>494</v>
+        <v>452</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>495</v>
+        <v>453</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12301,7 +12401,7 @@
         <v>21</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>21</v>
@@ -12313,13 +12413,13 @@
         <v>21</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>21</v>
+        <v>455</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>21</v>
@@ -12337,7 +12437,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>497</v>
+        <v>456</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12358,21 +12458,21 @@
         <v>21</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>498</v>
+        <v>191</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>499</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12386,7 +12486,7 @@
         <v>90</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>21</v>
@@ -12395,15 +12495,17 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>231</v>
+        <v>276</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>501</v>
+        <v>458</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -12452,7 +12554,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>503</v>
+        <v>461</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12473,21 +12575,21 @@
         <v>21</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>504</v>
+        <v>462</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>505</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>506</v>
+        <v>483</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12507,20 +12609,18 @@
         <v>21</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>507</v>
+        <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>508</v>
+        <v>105</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -12569,7 +12669,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>511</v>
+        <v>107</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12581,7 +12681,7 @@
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>21</v>
@@ -12590,32 +12690,32 @@
         <v>21</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>512</v>
+        <v>108</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>513</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>514</v>
+        <v>484</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>514</v>
+        <v>484</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -12624,19 +12724,19 @@
         <v>21</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>515</v>
+        <v>112</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>516</v>
+        <v>113</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>517</v>
+        <v>114</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12674,31 +12774,31 @@
         <v>21</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>518</v>
+        <v>118</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>21</v>
@@ -12707,7 +12807,7 @@
         <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>191</v>
+        <v>108</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -12716,12 +12816,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>519</v>
+        <v>485</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>519</v>
+        <v>485</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12729,33 +12829,35 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I84" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J84" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>520</v>
+        <v>166</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>521</v>
+        <v>486</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>522</v>
+        <v>487</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -12779,13 +12881,13 @@
         <v>21</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>21</v>
+        <v>490</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>21</v>
+        <v>491</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>21</v>
@@ -12803,10 +12905,10 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>519</v>
+        <v>492</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>90</v>
@@ -12818,27 +12920,27 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>524</v>
+        <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>525</v>
+        <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>527</v>
+        <v>21</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>528</v>
+        <v>191</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>529</v>
+        <v>494</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>529</v>
+        <v>494</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12858,19 +12960,23 @@
         <v>21</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>104</v>
+        <v>295</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>105</v>
+        <v>495</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
       </c>
@@ -12894,13 +13000,13 @@
         <v>21</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>21</v>
+        <v>499</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>21</v>
@@ -12918,7 +13024,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>107</v>
+        <v>501</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12930,7 +13036,7 @@
         <v>21</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>21</v>
@@ -12939,55 +13045,57 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>108</v>
+        <v>493</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>21</v>
+        <v>502</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>530</v>
+        <v>503</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>530</v>
+        <v>503</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>112</v>
+        <v>504</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>113</v>
+        <v>505</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>507</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
       </c>
@@ -12999,7 +13107,7 @@
         <v>21</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>21</v>
+        <v>508</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>21</v>
@@ -13023,31 +13131,31 @@
         <v>21</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>118</v>
+        <v>509</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>21</v>
@@ -13056,21 +13164,21 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>108</v>
+        <v>510</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>21</v>
+        <v>511</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13096,13 +13204,13 @@
         <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>445</v>
+        <v>513</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>446</v>
+        <v>514</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>447</v>
+        <v>515</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13116,7 +13224,7 @@
         <v>21</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>21</v>
+        <v>516</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>21</v>
@@ -13152,7 +13260,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>448</v>
+        <v>517</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13161,7 +13269,7 @@
         <v>90</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>102</v>
@@ -13173,21 +13281,21 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>191</v>
+        <v>518</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>21</v>
+        <v>519</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13210,17 +13318,15 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>132</v>
+        <v>231</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>451</v>
+        <v>521</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>21</v>
@@ -13245,13 +13351,13 @@
         <v>21</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>454</v>
+        <v>21</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>455</v>
+        <v>21</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>21</v>
@@ -13269,7 +13375,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>456</v>
+        <v>523</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13290,21 +13396,21 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>191</v>
+        <v>524</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>21</v>
+        <v>525</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13318,7 +13424,7 @@
         <v>90</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>21</v>
@@ -13327,16 +13433,16 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>276</v>
+        <v>527</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>458</v>
+        <v>528</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>459</v>
+        <v>529</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>460</v>
+        <v>530</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13386,7 +13492,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>461</v>
+        <v>531</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13407,13 +13513,13 @@
         <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>462</v>
+        <v>532</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>21</v>
+        <v>533</v>
       </c>
     </row>
     <row r="90" hidden="true">
@@ -13441,18 +13547,20 @@
         <v>21</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>105</v>
+        <v>464</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -13501,7 +13609,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>107</v>
+        <v>467</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13513,7 +13621,7 @@
         <v>21</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>21</v>
@@ -13522,7 +13630,7 @@
         <v>21</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>
@@ -13540,14 +13648,14 @@
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>21</v>
@@ -13559,16 +13667,16 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>111</v>
+        <v>536</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>112</v>
+        <v>537</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>113</v>
+        <v>538</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>114</v>
+        <v>539</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13606,54 +13714,54 @@
         <v>21</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>118</v>
+        <v>535</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>21</v>
+        <v>540</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>108</v>
+        <v>541</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>21</v>
+        <v>542</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>21</v>
+        <v>543</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13664,32 +13772,28 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>166</v>
+        <v>545</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>466</v>
+        <v>546</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>21</v>
       </c>
@@ -13713,13 +13817,13 @@
         <v>21</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>470</v>
+        <v>21</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>471</v>
+        <v>21</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>21</v>
@@ -13737,13 +13841,13 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>472</v>
+        <v>544</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>21</v>
@@ -13752,27 +13856,27 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>21</v>
+        <v>548</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>473</v>
+        <v>549</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>21</v>
+        <v>542</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13780,13 +13884,13 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>21</v>
@@ -13795,20 +13899,16 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>295</v>
+        <v>241</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>475</v>
+        <v>551</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>21</v>
       </c>
@@ -13832,13 +13932,13 @@
         <v>21</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>479</v>
+        <v>21</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>480</v>
+        <v>21</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>21</v>
@@ -13856,7 +13956,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>481</v>
+        <v>550</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13871,27 +13971,27 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>21</v>
+        <v>553</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>21</v>
+        <v>554</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>473</v>
+        <v>555</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>21</v>
+        <v>556</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>482</v>
+        <v>557</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13899,7 +13999,7 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>90</v>
@@ -13914,20 +14014,16 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>132</v>
+        <v>559</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>484</v>
+        <v>560</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>21</v>
       </c>
@@ -13939,7 +14035,7 @@
         <v>21</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>488</v>
+        <v>21</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>21</v>
@@ -13975,7 +14071,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>489</v>
+        <v>558</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13990,27 +14086,27 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>21</v>
+        <v>562</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>21</v>
+        <v>563</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>491</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14024,26 +14120,24 @@
         <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>493</v>
+        <v>105</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>495</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>21</v>
@@ -14056,7 +14150,7 @@
         <v>21</v>
       </c>
       <c r="T95" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="U95" t="s" s="2">
         <v>21</v>
@@ -14092,7 +14186,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>497</v>
+        <v>107</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14104,7 +14198,7 @@
         <v>21</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>21</v>
@@ -14113,32 +14207,32 @@
         <v>21</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>498</v>
+        <v>108</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>499</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>540</v>
+        <v>565</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>540</v>
+        <v>565</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>21</v>
@@ -14147,18 +14241,20 @@
         <v>21</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>501</v>
+        <v>112</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>21</v>
@@ -14195,31 +14291,31 @@
         <v>21</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>503</v>
+        <v>118</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>21</v>
@@ -14228,21 +14324,21 @@
         <v>21</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>504</v>
+        <v>108</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>505</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14256,7 +14352,7 @@
         <v>90</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>21</v>
@@ -14265,16 +14361,16 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>507</v>
+        <v>104</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>508</v>
+        <v>445</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>509</v>
+        <v>446</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>510</v>
+        <v>447</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14324,7 +14420,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>511</v>
+        <v>448</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14333,7 +14429,7 @@
         <v>90</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>102</v>
@@ -14345,21 +14441,21 @@
         <v>21</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>512</v>
+        <v>191</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>513</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14382,16 +14478,16 @@
         <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>515</v>
+        <v>451</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>516</v>
+        <v>452</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>517</v>
+        <v>453</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14417,13 +14513,13 @@
         <v>21</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>21</v>
+        <v>454</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>21</v>
+        <v>455</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>21</v>
@@ -14441,7 +14537,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>518</v>
+        <v>456</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14471,12 +14567,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14490,25 +14586,25 @@
         <v>90</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>544</v>
+        <v>276</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>545</v>
+        <v>458</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>546</v>
+        <v>459</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>547</v>
+        <v>460</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14558,7 +14654,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>543</v>
+        <v>461</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14573,27 +14669,27 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>548</v>
+        <v>21</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>549</v>
+        <v>462</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>550</v>
+        <v>21</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>551</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>552</v>
+        <v>569</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>552</v>
+        <v>569</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14604,7 +14700,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>21</v>
@@ -14616,13 +14712,13 @@
         <v>21</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>553</v>
+        <v>104</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>554</v>
+        <v>105</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>555</v>
+        <v>106</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14673,73 +14769,75 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>552</v>
+        <v>107</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>556</v>
+        <v>21</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>557</v>
+        <v>108</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>550</v>
+        <v>21</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>241</v>
+        <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>559</v>
+        <v>112</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14776,54 +14874,54 @@
         <v>21</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>558</v>
+        <v>118</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>561</v>
+        <v>21</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>562</v>
+        <v>21</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>563</v>
+        <v>108</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>564</v>
+        <v>21</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>565</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14831,31 +14929,35 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I102" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J102" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>567</v>
+        <v>166</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>568</v>
+        <v>486</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
       </c>
@@ -14879,13 +14981,13 @@
         <v>21</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>21</v>
+        <v>490</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>21</v>
+        <v>491</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>21</v>
@@ -14903,7 +15005,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>566</v>
+        <v>492</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14918,19 +15020,19 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>570</v>
+        <v>21</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>526</v>
+        <v>493</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>571</v>
+        <v>21</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
     </row>
     <row r="103" hidden="true">
@@ -14958,19 +15060,23 @@
         <v>21</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>104</v>
+        <v>295</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>105</v>
+        <v>495</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
       </c>
@@ -14994,13 +15100,13 @@
         <v>21</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>21</v>
+        <v>499</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>21</v>
@@ -15018,7 +15124,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>107</v>
+        <v>501</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15030,7 +15136,7 @@
         <v>21</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>21</v>
@@ -15039,16 +15145,16 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>108</v>
+        <v>493</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>21</v>
+        <v>502</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>573</v>
       </c>
@@ -15057,37 +15163,39 @@
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>112</v>
+        <v>504</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>113</v>
+        <v>505</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O104" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>507</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
       </c>
@@ -15099,7 +15207,7 @@
         <v>21</v>
       </c>
       <c r="T104" t="s" s="2">
-        <v>21</v>
+        <v>508</v>
       </c>
       <c r="U104" t="s" s="2">
         <v>21</v>
@@ -15123,31 +15231,31 @@
         <v>21</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>118</v>
+        <v>509</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>21</v>
@@ -15156,13 +15264,13 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>108</v>
+        <v>510</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>21</v>
+        <v>511</v>
       </c>
     </row>
     <row r="105">
@@ -15196,13 +15304,13 @@
         <v>104</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>445</v>
+        <v>513</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>446</v>
+        <v>514</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>447</v>
+        <v>515</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15216,7 +15324,7 @@
         <v>21</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>21</v>
+        <v>516</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>21</v>
@@ -15252,7 +15360,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>448</v>
+        <v>517</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15261,7 +15369,7 @@
         <v>90</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>102</v>
@@ -15273,13 +15381,13 @@
         <v>21</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>191</v>
+        <v>518</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>21</v>
+        <v>519</v>
       </c>
     </row>
     <row r="106" hidden="true">
@@ -15310,17 +15418,15 @@
         <v>91</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>132</v>
+        <v>231</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>451</v>
+        <v>521</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>21</v>
@@ -15345,13 +15451,13 @@
         <v>21</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>454</v>
+        <v>21</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>455</v>
+        <v>21</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>21</v>
@@ -15369,7 +15475,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>456</v>
+        <v>523</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15390,16 +15496,16 @@
         <v>21</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>191</v>
+        <v>524</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>21</v>
+        <v>525</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
         <v>576</v>
       </c>
@@ -15418,7 +15524,7 @@
         <v>90</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>21</v>
@@ -15427,16 +15533,16 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>276</v>
+        <v>527</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>458</v>
+        <v>528</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>459</v>
+        <v>529</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>460</v>
+        <v>530</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15486,7 +15592,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>461</v>
+        <v>531</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15507,13 +15613,13 @@
         <v>21</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>462</v>
+        <v>532</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>21</v>
+        <v>533</v>
       </c>
     </row>
     <row r="108" hidden="true">
@@ -15541,18 +15647,20 @@
         <v>21</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>105</v>
+        <v>464</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>21</v>
@@ -15601,7 +15709,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>107</v>
+        <v>467</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15613,7 +15721,7 @@
         <v>21</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>21</v>
@@ -15622,7 +15730,7 @@
         <v>21</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>21</v>
@@ -15640,14 +15748,14 @@
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>21</v>
@@ -15659,17 +15767,15 @@
         <v>21</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>111</v>
+        <v>579</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>112</v>
+        <v>580</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>21</v>
@@ -15706,43 +15812,43 @@
         <v>21</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>118</v>
+        <v>578</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>21</v>
+        <v>582</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>108</v>
+        <v>583</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>21</v>
+        <v>584</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>21</v>
@@ -15750,10 +15856,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15770,26 +15876,24 @@
         <v>21</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J110" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>166</v>
+        <v>295</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>466</v>
+        <v>586</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>467</v>
+        <v>587</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>21</v>
       </c>
@@ -15813,13 +15917,13 @@
         <v>21</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>470</v>
+        <v>589</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>471</v>
+        <v>590</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>21</v>
@@ -15837,7 +15941,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>472</v>
+        <v>585</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15852,27 +15956,27 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>21</v>
+        <v>591</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>473</v>
+        <v>592</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15892,23 +15996,19 @@
         <v>21</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>295</v>
+        <v>594</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>475</v>
+        <v>595</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>21</v>
       </c>
@@ -15932,13 +16032,13 @@
         <v>21</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>479</v>
+        <v>21</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>480</v>
+        <v>21</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>21</v>
@@ -15956,7 +16056,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>481</v>
+        <v>593</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15977,21 +16077,21 @@
         <v>21</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>473</v>
+        <v>597</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>21</v>
+        <v>598</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>482</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16002,32 +16102,30 @@
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>132</v>
+        <v>295</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>484</v>
+        <v>600</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>485</v>
+        <v>601</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>21</v>
       </c>
@@ -16039,7 +16137,7 @@
         <v>21</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>488</v>
+        <v>21</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>21</v>
@@ -16051,13 +16149,13 @@
         <v>21</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>21</v>
+        <v>603</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>21</v>
+        <v>604</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>21</v>
@@ -16075,13 +16173,13 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>489</v>
+        <v>599</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>21</v>
@@ -16090,27 +16188,27 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>21</v>
+        <v>605</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>21</v>
+        <v>606</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>490</v>
+        <v>607</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>21</v>
+        <v>608</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>491</v>
+        <v>609</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16121,28 +16219,28 @@
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>104</v>
+        <v>611</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>493</v>
+        <v>612</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>494</v>
+        <v>613</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>495</v>
+        <v>614</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16156,7 +16254,7 @@
         <v>21</v>
       </c>
       <c r="T113" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="U113" t="s" s="2">
         <v>21</v>
@@ -16192,13 +16290,13 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>497</v>
+        <v>610</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>21</v>
@@ -16207,27 +16305,27 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>21</v>
+        <v>615</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>498</v>
+        <v>616</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>21</v>
+        <v>608</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>499</v>
+        <v>21</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>583</v>
+        <v>617</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>583</v>
+        <v>617</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16238,7 +16336,7 @@
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>21</v>
@@ -16250,13 +16348,13 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>231</v>
+        <v>618</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>501</v>
+        <v>619</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>502</v>
+        <v>620</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16307,13 +16405,13 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>503</v>
+        <v>617</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>21</v>
@@ -16322,27 +16420,27 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>21</v>
+        <v>621</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>504</v>
+        <v>622</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>505</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>584</v>
+        <v>623</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>584</v>
+        <v>623</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16353,7 +16451,7 @@
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>21</v>
@@ -16365,17 +16463,15 @@
         <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>507</v>
+        <v>132</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>508</v>
+        <v>624</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>21</v>
@@ -16424,13 +16520,13 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>511</v>
+        <v>623</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>21</v>
@@ -16445,21 +16541,21 @@
         <v>21</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>512</v>
+        <v>622</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>513</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
-        <v>585</v>
+        <v>626</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>585</v>
+        <v>626</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16467,13 +16563,13 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>21</v>
@@ -16482,17 +16578,15 @@
         <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>104</v>
+        <v>627</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>515</v>
+        <v>628</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>629</v>
+      </c>
+      <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>21</v>
@@ -16541,13 +16635,13 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>518</v>
+        <v>626</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>21</v>
@@ -16556,13 +16650,13 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>21</v>
+        <v>630</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>191</v>
+        <v>631</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>21</v>
@@ -16573,10 +16667,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>586</v>
+        <v>632</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>586</v>
+        <v>632</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16599,13 +16693,13 @@
         <v>21</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>587</v>
+        <v>104</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>588</v>
+        <v>105</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>589</v>
+        <v>106</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16656,7 +16750,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>586</v>
+        <v>107</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16668,19 +16762,19 @@
         <v>21</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>590</v>
+        <v>21</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>591</v>
+        <v>108</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>592</v>
+        <v>21</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>21</v>
@@ -16688,21 +16782,21 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>21</v>
@@ -16711,19 +16805,19 @@
         <v>21</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>295</v>
+        <v>111</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>594</v>
+        <v>112</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>595</v>
+        <v>113</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>596</v>
+        <v>114</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -16749,52 +16843,52 @@
         <v>21</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>597</v>
+        <v>21</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>598</v>
+        <v>21</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>593</v>
+        <v>118</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>599</v>
+        <v>21</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>600</v>
+        <v>108</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>21</v>
@@ -16803,12 +16897,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
-        <v>601</v>
+        <v>634</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>601</v>
+        <v>634</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16822,24 +16916,26 @@
         <v>90</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>602</v>
+        <v>104</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>603</v>
+        <v>445</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>21</v>
@@ -16888,7 +16984,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>601</v>
+        <v>448</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16897,7 +16993,7 @@
         <v>90</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>102</v>
@@ -16909,10 +17005,10 @@
         <v>21</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>605</v>
+        <v>191</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>606</v>
+        <v>21</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>21</v>
@@ -16920,10 +17016,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>607</v>
+        <v>635</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>607</v>
+        <v>635</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16934,7 +17030,7 @@
         <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>21</v>
@@ -16943,19 +17039,19 @@
         <v>21</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>295</v>
+        <v>132</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>608</v>
+        <v>451</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>609</v>
+        <v>452</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>610</v>
+        <v>453</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16981,13 +17077,13 @@
         <v>21</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>611</v>
+        <v>454</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>612</v>
+        <v>455</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>21</v>
@@ -17005,13 +17101,13 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>607</v>
+        <v>456</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>21</v>
@@ -17020,27 +17116,27 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>613</v>
+        <v>21</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>614</v>
+        <v>21</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>615</v>
+        <v>191</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>616</v>
+        <v>21</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>617</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>618</v>
+        <v>636</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>618</v>
+        <v>636</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17051,7 +17147,7 @@
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>21</v>
@@ -17060,19 +17156,19 @@
         <v>21</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>619</v>
+        <v>276</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>620</v>
+        <v>458</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>621</v>
+        <v>459</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>622</v>
+        <v>460</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17122,13 +17218,13 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>618</v>
+        <v>461</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>21</v>
@@ -17137,16 +17233,16 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>623</v>
+        <v>21</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>624</v>
+        <v>462</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>616</v>
+        <v>21</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>21</v>
@@ -17154,10 +17250,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17168,7 +17264,7 @@
         <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>21</v>
@@ -17180,15 +17276,17 @@
         <v>91</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>626</v>
+        <v>104</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>627</v>
+        <v>464</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N122" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>21</v>
@@ -17237,13 +17335,13 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>625</v>
+        <v>467</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>21</v>
@@ -17252,13 +17350,13 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>629</v>
+        <v>21</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>630</v>
+        <v>191</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>21</v>
@@ -17267,12 +17365,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17283,10 +17381,10 @@
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>21</v>
@@ -17295,16 +17393,18 @@
         <v>91</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>132</v>
+        <v>276</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
+      <c r="O123" t="s" s="2">
+        <v>641</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>21</v>
       </c>
@@ -17352,13 +17452,13 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>21</v>
@@ -17367,13 +17467,13 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>21</v>
+        <v>642</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>630</v>
+        <v>643</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>21</v>
@@ -17382,12 +17482,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17395,28 +17495,28 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>635</v>
+        <v>104</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>636</v>
+        <v>105</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>637</v>
+        <v>106</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17467,28 +17567,28 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>634</v>
+        <v>107</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>638</v>
+        <v>21</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>639</v>
+        <v>108</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>21</v>
@@ -17499,21 +17599,21 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>21</v>
@@ -17525,15 +17625,17 @@
         <v>21</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N125" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>21</v>
@@ -17570,31 +17672,31 @@
         <v>21</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>21</v>
@@ -17614,44 +17716,46 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>112</v>
+        <v>486</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>113</v>
+        <v>487</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>21</v>
       </c>
@@ -17675,43 +17779,43 @@
         <v>21</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>21</v>
+        <v>490</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>21</v>
+        <v>491</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>118</v>
+        <v>492</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>21</v>
@@ -17720,21 +17824,21 @@
         <v>21</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>108</v>
+        <v>493</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17748,7 +17852,7 @@
         <v>90</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>21</v>
@@ -17757,18 +17861,20 @@
         <v>91</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>104</v>
+        <v>295</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>445</v>
+        <v>495</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>446</v>
+        <v>496</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O127" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>21</v>
       </c>
@@ -17792,13 +17898,13 @@
         <v>21</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>21</v>
+        <v>499</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>21</v>
@@ -17816,7 +17922,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>448</v>
+        <v>501</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17825,7 +17931,7 @@
         <v>90</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>102</v>
@@ -17837,21 +17943,21 @@
         <v>21</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>191</v>
+        <v>493</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>21</v>
+        <v>502</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17865,7 +17971,7 @@
         <v>90</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>21</v>
@@ -17877,15 +17983,17 @@
         <v>132</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>451</v>
+        <v>504</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>452</v>
+        <v>505</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O128" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>507</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>21</v>
       </c>
@@ -17897,7 +18005,7 @@
         <v>21</v>
       </c>
       <c r="T128" t="s" s="2">
-        <v>21</v>
+        <v>508</v>
       </c>
       <c r="U128" t="s" s="2">
         <v>21</v>
@@ -17909,13 +18017,13 @@
         <v>21</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>454</v>
+        <v>21</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>455</v>
+        <v>21</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>21</v>
@@ -17933,7 +18041,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>456</v>
+        <v>509</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17954,21 +18062,21 @@
         <v>21</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>191</v>
+        <v>510</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>21</v>
+        <v>511</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17982,7 +18090,7 @@
         <v>90</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>21</v>
@@ -17991,16 +18099,16 @@
         <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>276</v>
+        <v>104</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>458</v>
+        <v>513</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>459</v>
+        <v>514</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>460</v>
+        <v>515</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -18014,7 +18122,7 @@
         <v>21</v>
       </c>
       <c r="T129" t="s" s="2">
-        <v>21</v>
+        <v>516</v>
       </c>
       <c r="U129" t="s" s="2">
         <v>21</v>
@@ -18050,7 +18158,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>461</v>
+        <v>517</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18071,21 +18179,21 @@
         <v>21</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>462</v>
+        <v>518</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>21</v>
+        <v>519</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18108,17 +18216,15 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>104</v>
+        <v>231</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>21</v>
@@ -18167,7 +18273,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18188,21 +18294,21 @@
         <v>21</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>191</v>
+        <v>524</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>21</v>
+        <v>525</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18216,7 +18322,7 @@
         <v>90</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>21</v>
@@ -18225,18 +18331,18 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>276</v>
+        <v>527</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>647</v>
+        <v>528</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" t="s" s="2">
-        <v>649</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>21</v>
       </c>
@@ -18284,7 +18390,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>646</v>
+        <v>531</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18299,19 +18405,19 @@
         <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>650</v>
+        <v>21</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>651</v>
+        <v>532</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>21</v>
+        <v>533</v>
       </c>
     </row>
     <row r="132" hidden="true">
@@ -18330,7 +18436,7 @@
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>21</v>
@@ -18342,15 +18448,17 @@
         <v>21</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>104</v>
+        <v>295</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>105</v>
+        <v>653</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N132" s="2"/>
+        <v>654</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>655</v>
+      </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>21</v>
@@ -18375,13 +18483,13 @@
         <v>21</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>21</v>
+        <v>656</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>21</v>
+        <v>657</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>21</v>
@@ -18399,7 +18507,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>107</v>
+        <v>652</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18411,7 +18519,7 @@
         <v>21</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>21</v>
@@ -18420,7 +18528,7 @@
         <v>21</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>108</v>
+        <v>658</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>21</v>
@@ -18431,14 +18539,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -18457,17 +18565,15 @@
         <v>21</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>111</v>
+        <v>660</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>112</v>
+        <v>661</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>662</v>
+      </c>
+      <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>21</v>
@@ -18504,19 +18610,19 @@
         <v>21</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>118</v>
+        <v>659</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18528,16 +18634,16 @@
         <v>21</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>21</v>
+        <v>663</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>108</v>
+        <v>664</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>21</v>
@@ -18546,12 +18652,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="134" hidden="true">
+    <row r="134">
       <c r="A134" t="s" s="2">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18562,32 +18668,28 @@
         <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I134" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>166</v>
+        <v>666</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>466</v>
+        <v>667</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>668</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>21</v>
       </c>
@@ -18611,13 +18713,13 @@
         <v>21</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>470</v>
+        <v>21</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>471</v>
+        <v>21</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>21</v>
@@ -18635,13 +18737,13 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>472</v>
+        <v>665</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>21</v>
@@ -18650,27 +18752,27 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>21</v>
+        <v>669</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>21</v>
+        <v>670</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>473</v>
+        <v>671</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>655</v>
+        <v>672</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>655</v>
+        <v>672</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18690,23 +18792,19 @@
         <v>21</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>295</v>
+        <v>104</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>475</v>
+        <v>105</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>21</v>
       </c>
@@ -18730,13 +18828,13 @@
         <v>21</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>479</v>
+        <v>21</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>480</v>
+        <v>21</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>21</v>
@@ -18754,7 +18852,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>481</v>
+        <v>107</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18766,7 +18864,7 @@
         <v>21</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>21</v>
@@ -18775,57 +18873,55 @@
         <v>21</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>473</v>
+        <v>108</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO135" t="s" s="2">
-        <v>482</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>656</v>
+        <v>673</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>484</v>
+        <v>112</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>485</v>
+        <v>113</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>21</v>
       </c>
@@ -18837,7 +18933,7 @@
         <v>21</v>
       </c>
       <c r="T136" t="s" s="2">
-        <v>488</v>
+        <v>21</v>
       </c>
       <c r="U136" t="s" s="2">
         <v>21</v>
@@ -18861,31 +18957,31 @@
         <v>21</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>489</v>
+        <v>118</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>21</v>
@@ -18894,21 +18990,21 @@
         <v>21</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>490</v>
+        <v>108</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>491</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>657</v>
+        <v>674</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>657</v>
+        <v>674</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18922,7 +19018,7 @@
         <v>90</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>21</v>
@@ -18931,16 +19027,16 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>104</v>
+        <v>675</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>493</v>
+        <v>676</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>494</v>
+        <v>677</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>495</v>
+        <v>678</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -18954,7 +19050,7 @@
         <v>21</v>
       </c>
       <c r="T137" t="s" s="2">
-        <v>496</v>
+        <v>21</v>
       </c>
       <c r="U137" t="s" s="2">
         <v>21</v>
@@ -18990,7 +19086,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>497</v>
+        <v>679</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19011,21 +19107,21 @@
         <v>21</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>498</v>
+        <v>680</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>499</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="138" hidden="true">
+    <row r="138">
       <c r="A138" t="s" s="2">
-        <v>658</v>
+        <v>681</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>658</v>
+        <v>681</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19039,7 +19135,7 @@
         <v>90</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>21</v>
@@ -19048,13 +19144,13 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>501</v>
+        <v>682</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>502</v>
+        <v>683</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19105,7 +19201,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>503</v>
+        <v>684</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19126,21 +19222,21 @@
         <v>21</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>504</v>
+        <v>685</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>505</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="139" hidden="true">
+    <row r="139">
       <c r="A139" t="s" s="2">
-        <v>659</v>
+        <v>686</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>659</v>
+        <v>686</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19148,13 +19244,13 @@
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G139" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>21</v>
@@ -19163,17 +19259,15 @@
         <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>507</v>
+        <v>269</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>508</v>
+        <v>687</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>688</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>21</v>
@@ -19222,10 +19316,10 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>511</v>
+        <v>689</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>90</v>
@@ -19243,21 +19337,21 @@
         <v>21</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>512</v>
+        <v>690</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO139" t="s" s="2">
-        <v>513</v>
+        <v>191</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>660</v>
+        <v>691</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>660</v>
+        <v>691</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19265,13 +19359,13 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>21</v>
@@ -19280,16 +19374,16 @@
         <v>21</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>295</v>
+        <v>692</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>661</v>
+        <v>693</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>662</v>
+        <v>694</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>663</v>
+        <v>695</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19315,37 +19409,35 @@
         <v>21</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>664</v>
+        <v>21</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>665</v>
+        <v>21</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>696</v>
+      </c>
+      <c r="AC140" s="2"/>
       <c r="AD140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>21</v>
+        <v>697</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>660</v>
+        <v>691</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>21</v>
@@ -19354,13 +19446,13 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>21</v>
+        <v>698</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>666</v>
+        <v>699</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>21</v>
@@ -19369,14 +19461,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="141" hidden="true">
+    <row r="141">
       <c r="A141" t="s" s="2">
-        <v>667</v>
+        <v>700</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="C141" s="2"/>
+        <v>691</v>
+      </c>
+      <c r="C141" t="s" s="2">
+        <v>701</v>
+      </c>
       <c r="D141" t="s" s="2">
         <v>21</v>
       </c>
@@ -19388,7 +19482,7 @@
         <v>81</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>21</v>
@@ -19397,15 +19491,17 @@
         <v>21</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>668</v>
+        <v>702</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>669</v>
+        <v>703</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>695</v>
+      </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>21</v>
@@ -19454,7 +19550,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>667</v>
+        <v>691</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19469,13 +19565,13 @@
         <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>671</v>
+        <v>698</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>672</v>
+        <v>699</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>21</v>
@@ -19486,12 +19582,14 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>673</v>
+        <v>704</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="C142" s="2"/>
+        <v>691</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>705</v>
+      </c>
       <c r="D142" t="s" s="2">
         <v>21</v>
       </c>
@@ -19512,15 +19610,17 @@
         <v>21</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>674</v>
+        <v>706</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>675</v>
+        <v>703</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="N142" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>695</v>
+      </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>21</v>
@@ -19569,7 +19669,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>673</v>
+        <v>691</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19584,13 +19684,13 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>677</v>
+        <v>698</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>678</v>
+        <v>21</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>679</v>
+        <v>699</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>21</v>
@@ -19599,14 +19699,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="143" hidden="true">
+    <row r="143">
       <c r="A143" t="s" s="2">
-        <v>680</v>
+        <v>707</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="C143" s="2"/>
+        <v>691</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>708</v>
+      </c>
       <c r="D143" t="s" s="2">
         <v>21</v>
       </c>
@@ -19615,10 +19717,10 @@
         <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>21</v>
@@ -19627,15 +19729,17 @@
         <v>21</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>104</v>
+        <v>709</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>105</v>
+        <v>703</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N143" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>695</v>
+      </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>21</v>
@@ -19684,28 +19788,28 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>107</v>
+        <v>691</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>21</v>
+        <v>698</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>108</v>
+        <v>699</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>21</v>
@@ -19714,16 +19818,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="144" hidden="true">
+    <row r="144">
       <c r="A144" t="s" s="2">
-        <v>681</v>
+        <v>710</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="C144" s="2"/>
+        <v>691</v>
+      </c>
+      <c r="C144" t="s" s="2">
+        <v>711</v>
+      </c>
       <c r="D144" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -19733,7 +19839,7 @@
         <v>81</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>21</v>
@@ -19742,16 +19848,16 @@
         <v>21</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>111</v>
+        <v>712</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>112</v>
+        <v>703</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>113</v>
+        <v>694</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>114</v>
+        <v>695</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19789,19 +19895,19 @@
         <v>21</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>118</v>
+        <v>691</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19813,16 +19919,16 @@
         <v>21</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>21</v>
+        <v>698</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>108</v>
+        <v>699</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>21</v>
@@ -19831,14 +19937,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="145" hidden="true">
+    <row r="145">
       <c r="A145" t="s" s="2">
-        <v>682</v>
+        <v>713</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="C145" s="2"/>
+        <v>691</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>714</v>
+      </c>
       <c r="D145" t="s" s="2">
         <v>21</v>
       </c>
@@ -19847,28 +19955,28 @@
         <v>80</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>683</v>
+        <v>715</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>684</v>
+        <v>703</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -19918,42 +20026,42 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>102</v>
+        <v>716</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>21</v>
+        <v>698</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>689</v>
+        <v>717</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>689</v>
+        <v>717</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19961,7 +20069,7 @@
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G146" t="s" s="2">
         <v>90</v>
@@ -19973,16 +20081,16 @@
         <v>21</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>241</v>
+        <v>718</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>690</v>
+        <v>719</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>691</v>
+        <v>720</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20033,7 +20141,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>692</v>
+        <v>717</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20051,24 +20159,24 @@
         <v>21</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>21</v>
+        <v>721</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>693</v>
+        <v>722</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>694</v>
+        <v>723</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>694</v>
+        <v>723</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20076,28 +20184,28 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G147" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>269</v>
+        <v>104</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>695</v>
+        <v>105</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>696</v>
+        <v>106</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -20148,10 +20256,10 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>697</v>
+        <v>107</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>90</v>
@@ -20160,7 +20268,7 @@
         <v>21</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>21</v>
@@ -20169,35 +20277,35 @@
         <v>21</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>698</v>
+        <v>108</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>699</v>
+        <v>724</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>699</v>
+        <v>724</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>21</v>
@@ -20206,16 +20314,16 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>700</v>
+        <v>111</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>701</v>
+        <v>112</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>702</v>
+        <v>113</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>703</v>
+        <v>114</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20253,17 +20361,19 @@
         <v>21</v>
       </c>
       <c r="AB148" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="AC148" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD148" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE148" t="s" s="2">
-        <v>705</v>
+        <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>699</v>
+        <v>118</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20275,16 +20385,16 @@
         <v>21</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>706</v>
+        <v>21</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>707</v>
+        <v>108</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>21</v>
@@ -20293,16 +20403,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>708</v>
+        <v>725</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="C149" t="s" s="2">
-        <v>709</v>
-      </c>
+        <v>725</v>
+      </c>
+      <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
         <v>21</v>
       </c>
@@ -20311,29 +20419,27 @@
         <v>80</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I149" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I149" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J149" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>710</v>
+        <v>111</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>703</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>21</v>
@@ -20382,7 +20488,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>699</v>
+        <v>727</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20394,16 +20500,16 @@
         <v>21</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>706</v>
+        <v>21</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>707</v>
+        <v>21</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>21</v>
@@ -20412,16 +20518,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>712</v>
+        <v>728</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="C150" t="s" s="2">
-        <v>713</v>
-      </c>
+        <v>728</v>
+      </c>
+      <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
         <v>21</v>
       </c>
@@ -20430,10 +20534,10 @@
         <v>80</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>21</v>
@@ -20442,16 +20546,16 @@
         <v>21</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>711</v>
+        <v>729</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>702</v>
+        <v>730</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>703</v>
+        <v>731</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20501,13 +20605,13 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>699</v>
+        <v>728</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>21</v>
@@ -20516,13 +20620,13 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>706</v>
+        <v>21</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>707</v>
+        <v>732</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>21</v>
@@ -20531,16 +20635,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>715</v>
+        <v>733</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="C151" t="s" s="2">
-        <v>716</v>
-      </c>
+        <v>733</v>
+      </c>
+      <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
         <v>21</v>
       </c>
@@ -20549,10 +20651,10 @@
         <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>21</v>
@@ -20561,17 +20663,15 @@
         <v>21</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>717</v>
+        <v>104</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>711</v>
+        <v>105</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>703</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>21</v>
@@ -20620,28 +20720,28 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>699</v>
+        <v>107</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>706</v>
+        <v>21</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>707</v>
+        <v>108</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>21</v>
@@ -20650,18 +20750,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>718</v>
+        <v>734</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="C152" t="s" s="2">
-        <v>719</v>
-      </c>
+        <v>734</v>
+      </c>
+      <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -20671,7 +20769,7 @@
         <v>81</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>21</v>
@@ -20680,16 +20778,16 @@
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>720</v>
+        <v>111</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>711</v>
+        <v>112</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>702</v>
+        <v>113</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>703</v>
+        <v>114</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -20739,7 +20837,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>699</v>
+        <v>118</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20751,16 +20849,16 @@
         <v>21</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>706</v>
+        <v>21</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>707</v>
+        <v>108</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>21</v>
@@ -20769,18 +20867,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>721</v>
+        <v>735</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="C153" t="s" s="2">
-        <v>722</v>
-      </c>
+        <v>735</v>
+      </c>
+      <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>21</v>
+        <v>736</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
@@ -20790,27 +20886,29 @@
         <v>81</v>
       </c>
       <c r="H153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I153" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I153" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J153" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>723</v>
+        <v>111</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>711</v>
+        <v>737</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>702</v>
+        <v>738</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="O153" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>739</v>
+      </c>
       <c r="P153" t="s" s="2">
         <v>21</v>
       </c>
@@ -20858,7 +20956,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>699</v>
+        <v>727</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20870,16 +20968,16 @@
         <v>21</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>724</v>
+        <v>119</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>706</v>
+        <v>21</v>
       </c>
       <c r="AL153" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>707</v>
+        <v>191</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>21</v>
@@ -20888,12 +20986,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20901,13 +20999,13 @@
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G154" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>21</v>
@@ -20916,13 +21014,13 @@
         <v>21</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>727</v>
+        <v>742</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>728</v>
+        <v>743</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -20973,7 +21071,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -20985,16 +21083,16 @@
         <v>21</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>102</v>
+        <v>744</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>729</v>
+        <v>21</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>730</v>
+        <v>745</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>21</v>
@@ -21005,10 +21103,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>731</v>
+        <v>746</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>731</v>
+        <v>746</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21031,13 +21129,13 @@
         <v>21</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>104</v>
+        <v>747</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>105</v>
+        <v>748</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>106</v>
+        <v>749</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21088,7 +21186,7 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>107</v>
+        <v>746</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21100,7 +21198,7 @@
         <v>21</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>21</v>
@@ -21109,7 +21207,7 @@
         <v>21</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>108</v>
+        <v>750</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>21</v>
@@ -21120,21 +21218,21 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>732</v>
+        <v>751</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>732</v>
+        <v>751</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>21</v>
@@ -21146,17 +21244,15 @@
         <v>21</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>111</v>
+        <v>747</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>112</v>
+        <v>752</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>753</v>
+      </c>
+      <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>21</v>
@@ -21205,19 +21301,19 @@
         <v>21</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>118</v>
+        <v>751</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>21</v>
@@ -21226,7 +21322,7 @@
         <v>21</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>108</v>
+        <v>750</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>21</v>
@@ -21235,47 +21331,47 @@
         <v>21</v>
       </c>
     </row>
-    <row r="157" hidden="true">
+    <row r="157">
       <c r="A157" t="s" s="2">
-        <v>733</v>
+        <v>754</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>733</v>
+        <v>754</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>734</v>
+        <v>21</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I157" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>111</v>
+        <v>231</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>735</v>
+        <v>755</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>114</v>
+        <v>757</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>21</v>
@@ -21324,28 +21420,28 @@
         <v>21</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>738</v>
+        <v>754</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>21</v>
+        <v>759</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>191</v>
+        <v>760</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>21</v>
@@ -21356,10 +21452,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>739</v>
+        <v>761</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>739</v>
+        <v>761</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21382,17 +21478,15 @@
         <v>21</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>726</v>
+        <v>104</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>740</v>
+        <v>105</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>742</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>21</v>
@@ -21441,7 +21535,7 @@
         <v>21</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>739</v>
+        <v>107</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21453,7 +21547,7 @@
         <v>21</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>21</v>
@@ -21462,7 +21556,7 @@
         <v>21</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>743</v>
+        <v>108</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>21</v>
@@ -21473,21 +21567,21 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>744</v>
+        <v>762</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>744</v>
+        <v>762</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>21</v>
@@ -21499,15 +21593,17 @@
         <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N159" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>21</v>
@@ -21544,31 +21640,31 @@
         <v>21</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>21</v>
@@ -21586,44 +21682,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
-        <v>745</v>
+        <v>763</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>745</v>
+        <v>763</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>111</v>
+        <v>241</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>112</v>
+        <v>242</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>113</v>
+        <v>243</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>114</v>
+        <v>244</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -21673,19 +21769,19 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>21</v>
+        <v>246</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>21</v>
@@ -21694,61 +21790,61 @@
         <v>21</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>108</v>
+        <v>247</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
-        <v>746</v>
+        <v>764</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>746</v>
+        <v>764</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>734</v>
+        <v>21</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I161" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J161" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>111</v>
+        <v>241</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>735</v>
+        <v>251</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>736</v>
+        <v>252</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>737</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q161" s="2"/>
+      <c r="Q161" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="R161" t="s" s="2">
         <v>21</v>
       </c>
@@ -21792,19 +21888,19 @@
         <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>738</v>
+        <v>255</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>21</v>
+        <v>246</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>21</v>
@@ -21813,21 +21909,21 @@
         <v>21</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
     </row>
-    <row r="162" hidden="true">
+    <row r="162">
       <c r="A162" t="s" s="2">
-        <v>747</v>
+        <v>765</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>747</v>
+        <v>765</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21835,13 +21931,13 @@
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G162" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>21</v>
@@ -21850,15 +21946,17 @@
         <v>21</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>748</v>
+        <v>766</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>749</v>
+        <v>767</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="N162" s="2"/>
+        <v>768</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>769</v>
+      </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>21</v>
@@ -21907,7 +22005,7 @@
         <v>21</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>747</v>
+        <v>765</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -21919,30 +22017,30 @@
         <v>21</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>751</v>
+        <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>21</v>
+        <v>770</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>752</v>
+        <v>771</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>21</v>
+        <v>772</v>
       </c>
     </row>
-    <row r="163" hidden="true">
+    <row r="163">
       <c r="A163" t="s" s="2">
-        <v>753</v>
+        <v>773</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>753</v>
+        <v>773</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21950,13 +22048,13 @@
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G163" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>21</v>
@@ -21965,13 +22063,13 @@
         <v>21</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>755</v>
+        <v>774</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>756</v>
+        <v>775</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -22022,7 +22120,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>753</v>
+        <v>773</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22034,30 +22132,30 @@
         <v>21</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>102</v>
+        <v>744</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>21</v>
+        <v>776</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>757</v>
+        <v>777</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>21</v>
+        <v>778</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>758</v>
+        <v>779</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>758</v>
+        <v>779</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22080,13 +22178,13 @@
         <v>21</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>754</v>
+        <v>104</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>759</v>
+        <v>105</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>760</v>
+        <v>106</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22137,7 +22235,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>758</v>
+        <v>107</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22149,7 +22247,7 @@
         <v>21</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>21</v>
@@ -22158,7 +22256,7 @@
         <v>21</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>757</v>
+        <v>108</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>21</v>
@@ -22167,26 +22265,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>21</v>
@@ -22195,20 +22293,18 @@
         <v>21</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>762</v>
+        <v>112</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>763</v>
+        <v>113</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>765</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>21</v>
       </c>
@@ -22244,40 +22340,40 @@
         <v>21</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC165" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE165" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>761</v>
+        <v>118</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>766</v>
+        <v>21</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>767</v>
+        <v>108</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>21</v>
@@ -22286,12 +22382,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
-        <v>768</v>
+        <v>781</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>768</v>
+        <v>781</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22305,25 +22401,29 @@
         <v>90</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>104</v>
+        <v>782</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>105</v>
+        <v>783</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N166" s="2"/>
-      <c r="O166" s="2"/>
+        <v>784</v>
+      </c>
+      <c r="N166" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="O166" t="s" s="2">
+        <v>786</v>
+      </c>
       <c r="P166" t="s" s="2">
         <v>21</v>
       </c>
@@ -22371,7 +22471,7 @@
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>107</v>
+        <v>787</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22383,7 +22483,7 @@
         <v>21</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>21</v>
@@ -22392,59 +22492,61 @@
         <v>21</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>108</v>
+        <v>788</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>21</v>
+        <v>789</v>
       </c>
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>769</v>
+        <v>790</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>769</v>
+        <v>790</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I167" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>112</v>
+        <v>791</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O167" s="2"/>
+        <v>792</v>
+      </c>
+      <c r="N167" s="2"/>
+      <c r="O167" t="s" s="2">
+        <v>793</v>
+      </c>
       <c r="P167" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q167" s="2"/>
+      <c r="Q167" t="s" s="2">
+        <v>794</v>
+      </c>
       <c r="R167" t="s" s="2">
         <v>21</v>
       </c>
@@ -22464,43 +22566,43 @@
         <v>21</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>21</v>
+        <v>795</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>21</v>
+        <v>796</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB167" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC167" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE167" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>118</v>
+        <v>797</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>21</v>
@@ -22509,21 +22611,21 @@
         <v>21</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>108</v>
+        <v>798</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>21</v>
+        <v>799</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>770</v>
+        <v>800</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>770</v>
+        <v>800</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22546,18 +22648,18 @@
         <v>91</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>242</v>
+        <v>801</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O168" s="2"/>
+        <v>802</v>
+      </c>
+      <c r="N168" s="2"/>
+      <c r="O168" t="s" s="2">
+        <v>803</v>
+      </c>
       <c r="P168" t="s" s="2">
         <v>21</v>
       </c>
@@ -22605,7 +22707,7 @@
         <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>245</v>
+        <v>804</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22614,7 +22716,7 @@
         <v>90</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>102</v>
@@ -22626,21 +22728,21 @@
         <v>21</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>247</v>
+        <v>805</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>248</v>
+        <v>806</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>771</v>
+        <v>807</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>771</v>
+        <v>807</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22654,7 +22756,7 @@
         <v>90</v>
       </c>
       <c r="H169" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I169" t="s" s="2">
         <v>21</v>
@@ -22663,24 +22765,22 @@
         <v>91</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>241</v>
+        <v>132</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>251</v>
+        <v>808</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O169" s="2"/>
+        <v>809</v>
+      </c>
+      <c r="N169" s="2"/>
+      <c r="O169" t="s" s="2">
+        <v>810</v>
+      </c>
       <c r="P169" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q169" t="s" s="2">
-        <v>254</v>
-      </c>
+      <c r="Q169" s="2"/>
       <c r="R169" t="s" s="2">
         <v>21</v>
       </c>
@@ -22724,7 +22824,7 @@
         <v>21</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>255</v>
+        <v>811</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22733,7 +22833,7 @@
         <v>90</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>246</v>
+        <v>812</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>102</v>
@@ -22745,21 +22845,21 @@
         <v>21</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>256</v>
+        <v>813</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>257</v>
+        <v>806</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>772</v>
+        <v>814</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>772</v>
+        <v>814</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22767,7 +22867,7 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G170" t="s" s="2">
         <v>90</v>
@@ -22779,21 +22879,23 @@
         <v>21</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>773</v>
+        <v>166</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>774</v>
+        <v>815</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>775</v>
+        <v>816</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="O170" s="2"/>
+        <v>817</v>
+      </c>
+      <c r="O170" t="s" s="2">
+        <v>818</v>
+      </c>
       <c r="P170" t="s" s="2">
         <v>21</v>
       </c>
@@ -22841,7 +22943,7 @@
         <v>21</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>772</v>
+        <v>819</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22859,24 +22961,24 @@
         <v>21</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>777</v>
+        <v>21</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>778</v>
+        <v>820</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>779</v>
+        <v>806</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>780</v>
+        <v>821</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>780</v>
+        <v>821</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22884,13 +22986,13 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G171" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>21</v>
@@ -22899,15 +23001,17 @@
         <v>21</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>781</v>
+        <v>822</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="N171" s="2"/>
+        <v>823</v>
+      </c>
+      <c r="N171" t="s" s="2">
+        <v>824</v>
+      </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>21</v>
@@ -22956,7 +23060,7 @@
         <v>21</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>780</v>
+        <v>821</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -22968,30 +23072,30 @@
         <v>21</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>751</v>
+        <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>783</v>
+        <v>825</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>784</v>
+        <v>826</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>785</v>
+        <v>21</v>
       </c>
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>786</v>
+        <v>827</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>786</v>
+        <v>827</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23014,17 +23118,15 @@
         <v>21</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>754</v>
+        <v>527</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>787</v>
+        <v>828</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>789</v>
-      </c>
+        <v>829</v>
+      </c>
+      <c r="N172" s="2"/>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>21</v>
@@ -23073,7 +23175,7 @@
         <v>21</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>786</v>
+        <v>827</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23091,13 +23193,13 @@
         <v>21</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>790</v>
+        <v>21</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>791</v>
+        <v>830</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>21</v>
+        <v>598</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>21</v>
@@ -23105,10 +23207,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>792</v>
+        <v>831</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>792</v>
+        <v>831</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23131,13 +23233,13 @@
         <v>21</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>507</v>
+        <v>718</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>793</v>
+        <v>832</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>794</v>
+        <v>833</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23188,7 +23290,7 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>792</v>
+        <v>831</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23206,13 +23308,13 @@
         <v>21</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>21</v>
+        <v>834</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>795</v>
+        <v>835</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>606</v>
+        <v>21</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>21</v>
@@ -23220,10 +23322,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>796</v>
+        <v>836</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>796</v>
+        <v>836</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23246,13 +23348,13 @@
         <v>21</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>726</v>
+        <v>104</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>797</v>
+        <v>105</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>798</v>
+        <v>106</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -23303,7 +23405,7 @@
         <v>21</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>796</v>
+        <v>107</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23315,16 +23417,16 @@
         <v>21</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>799</v>
+        <v>21</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>800</v>
+        <v>108</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>21</v>
@@ -23335,21 +23437,21 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>801</v>
+        <v>837</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>801</v>
+        <v>837</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>21</v>
@@ -23361,15 +23463,17 @@
         <v>21</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N175" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N175" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>21</v>
@@ -23418,19 +23522,19 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>21</v>
@@ -23450,14 +23554,14 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>802</v>
+        <v>838</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>802</v>
+        <v>838</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>110</v>
+        <v>736</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -23470,24 +23574,26 @@
         <v>21</v>
       </c>
       <c r="I176" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K176" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>112</v>
+        <v>737</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>113</v>
+        <v>738</v>
       </c>
       <c r="N176" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O176" s="2"/>
+      <c r="O176" t="s" s="2">
+        <v>739</v>
+      </c>
       <c r="P176" t="s" s="2">
         <v>21</v>
       </c>
@@ -23535,7 +23641,7 @@
         <v>21</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>118</v>
+        <v>727</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23556,7 +23662,7 @@
         <v>21</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>21</v>
@@ -23567,46 +23673,44 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>803</v>
+        <v>839</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>803</v>
+        <v>839</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>734</v>
+        <v>21</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I177" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>111</v>
+        <v>840</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>735</v>
+        <v>841</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>736</v>
+        <v>842</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>737</v>
-      </c>
+        <v>843</v>
+      </c>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>21</v>
       </c>
@@ -23630,13 +23734,13 @@
         <v>21</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>21</v>
+        <v>844</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>21</v>
@@ -23654,42 +23758,42 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>738</v>
+        <v>839</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>21</v>
+        <v>834</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>191</v>
+        <v>846</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>21</v>
+        <v>847</v>
       </c>
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>804</v>
+        <v>848</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>804</v>
+        <v>848</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23697,7 +23801,7 @@
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G178" t="s" s="2">
         <v>90</v>
@@ -23712,17 +23816,15 @@
         <v>21</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>805</v>
+        <v>295</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>806</v>
+        <v>849</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>808</v>
-      </c>
+        <v>850</v>
+      </c>
+      <c r="N178" s="2"/>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>21</v>
@@ -23750,10 +23852,10 @@
         <v>156</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>809</v>
+        <v>851</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>810</v>
+        <v>852</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>21</v>
@@ -23771,10 +23873,10 @@
         <v>21</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>804</v>
+        <v>848</v>
       </c>
       <c r="AG178" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH178" t="s" s="2">
         <v>90</v>
@@ -23789,24 +23891,24 @@
         <v>21</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>799</v>
+        <v>853</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>811</v>
+        <v>854</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>812</v>
+        <v>855</v>
       </c>
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>813</v>
+        <v>856</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>813</v>
+        <v>856</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -23829,13 +23931,13 @@
         <v>21</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>295</v>
+        <v>857</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>814</v>
+        <v>858</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>815</v>
+        <v>859</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -23862,13 +23964,13 @@
         <v>21</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>816</v>
+        <v>21</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>817</v>
+        <v>21</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>21</v>
@@ -23886,7 +23988,7 @@
         <v>21</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>813</v>
+        <v>856</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -23901,38 +24003,38 @@
         <v>102</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>21</v>
+        <v>860</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>818</v>
+        <v>853</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>819</v>
+        <v>861</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>820</v>
+        <v>21</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>821</v>
+        <v>862</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>821</v>
+        <v>862</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>21</v>
+        <v>863</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>21</v>
@@ -23944,15 +24046,17 @@
         <v>21</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>822</v>
+        <v>864</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>823</v>
+        <v>865</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="N180" s="2"/>
+        <v>866</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>867</v>
+      </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>21</v>
@@ -24001,13 +24105,13 @@
         <v>21</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>821</v>
+        <v>862</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>21</v>
@@ -24016,13 +24120,13 @@
         <v>102</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>825</v>
+        <v>21</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>818</v>
+        <v>21</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>826</v>
+        <v>868</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>21</v>
@@ -24033,14 +24137,14 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>827</v>
+        <v>869</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>827</v>
+        <v>869</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>828</v>
+        <v>21</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
@@ -24059,16 +24163,16 @@
         <v>21</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>829</v>
+        <v>870</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>830</v>
+        <v>871</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>831</v>
+        <v>872</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>832</v>
+        <v>873</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -24118,7 +24222,7 @@
         <v>21</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>827</v>
+        <v>869</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24133,140 +24237,23 @@
         <v>102</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>21</v>
+        <v>874</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>833</v>
+        <v>875</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO181" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="182" hidden="true">
-      <c r="A182" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="C182" s="2"/>
-      <c r="D182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E182" s="2"/>
-      <c r="F182" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K182" t="s" s="2">
-        <v>835</v>
-      </c>
-      <c r="L182" t="s" s="2">
-        <v>836</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>837</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>838</v>
-      </c>
-      <c r="O182" s="2"/>
-      <c r="P182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q182" s="2"/>
-      <c r="R182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF182" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="AG182" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH182" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ182" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK182" t="s" s="2">
-        <v>839</v>
-      </c>
-      <c r="AL182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM182" t="s" s="2">
-        <v>840</v>
-      </c>
-      <c r="AN182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO182" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO182">
+  <autoFilter ref="A1:AO181">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -24276,7 +24263,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI181">
+  <conditionalFormatting sqref="A2:AI180">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1243,7 +1243,7 @@
     <t>MedicationRequest.category.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
+    <t>Fachliche Begründung: TODO</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -1544,9 +1544,6 @@
     <t>MedicationRequest.subject.identifier.use</t>
   </si>
   <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
     <t>The purpose of this identifier.</t>
   </si>
   <si>
@@ -1805,6 +1802,9 @@
   </si>
   <si>
     <t>MedicationRequest.requester.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
   </si>
   <si>
     <t>MedicationRequest.requester.identifier.type</t>
@@ -9209,7 +9209,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -9677,7 +9677,7 @@
         <v>90</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -10617,7 +10617,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -12832,7 +12832,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>21</v>
@@ -12847,16 +12847,16 @@
         <v>166</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -12884,28 +12884,28 @@
         <v>187</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="Z84" t="s" s="2">
+      <c r="AA84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12926,7 +12926,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -12937,10 +12937,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12966,16 +12966,16 @@
         <v>295</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -13003,28 +13003,28 @@
         <v>148</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="Z85" t="s" s="2">
+      <c r="AA85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13045,21 +13045,21 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13085,16 +13085,16 @@
         <v>132</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -13107,43 +13107,43 @@
         <v>21</v>
       </c>
       <c r="T86" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13164,21 +13164,21 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>511</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13204,13 +13204,13 @@
         <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13224,43 +13224,43 @@
         <v>21</v>
       </c>
       <c r="T87" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13281,21 +13281,21 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO87" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>519</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13321,10 +13321,10 @@
         <v>231</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13375,7 +13375,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13396,21 +13396,21 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>525</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13433,16 +13433,16 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13492,7 +13492,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13513,21 +13513,21 @@
         <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>533</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13641,10 +13641,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13667,16 +13667,16 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13726,7 +13726,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13741,27 +13741,27 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>291</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>543</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13784,13 +13784,13 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13841,7 +13841,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13856,16 +13856,16 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="AL92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>549</v>
-      </c>
       <c r="AN92" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>21</v>
@@ -13873,10 +13873,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13902,10 +13902,10 @@
         <v>241</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13956,7 +13956,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13971,27 +13971,27 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AL93" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AL93" t="s" s="2">
+      <c r="AM93" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>557</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14014,13 +14014,13 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14071,7 +14071,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14086,7 +14086,7 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>21</v>
@@ -14095,7 +14095,7 @@
         <v>475</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>21</v>
@@ -14103,10 +14103,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14218,10 +14218,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14335,10 +14335,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14452,10 +14452,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14569,10 +14569,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14686,10 +14686,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14801,10 +14801,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14918,10 +14918,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14947,16 +14947,16 @@
         <v>166</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
@@ -14984,28 +14984,28 @@
         <v>187</v>
       </c>
       <c r="Y102" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="Z102" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="Z102" t="s" s="2">
+      <c r="AA102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15026,7 +15026,7 @@
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>21</v>
@@ -15066,16 +15066,16 @@
         <v>295</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
@@ -15103,28 +15103,28 @@
         <v>148</v>
       </c>
       <c r="Y103" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="Z103" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="Z103" t="s" s="2">
+      <c r="AA103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15145,13 +15145,13 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="104">
@@ -15185,16 +15185,16 @@
         <v>132</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
@@ -15207,43 +15207,43 @@
         <v>21</v>
       </c>
       <c r="T104" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15264,13 +15264,13 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO104" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>511</v>
       </c>
     </row>
     <row r="105">
@@ -15304,13 +15304,13 @@
         <v>104</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15324,43 +15324,43 @@
         <v>21</v>
       </c>
       <c r="T105" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF105" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15381,13 +15381,13 @@
         <v>21</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO105" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>519</v>
       </c>
     </row>
     <row r="106" hidden="true">
@@ -15421,10 +15421,10 @@
         <v>231</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15475,7 +15475,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15496,13 +15496,13 @@
         <v>21</v>
       </c>
       <c r="AM106" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO106" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>525</v>
       </c>
     </row>
     <row r="107" hidden="true">
@@ -15533,16 +15533,16 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15592,7 +15592,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15613,13 +15613,13 @@
         <v>21</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO107" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>533</v>
       </c>
     </row>
     <row r="108" hidden="true">
@@ -17745,16 +17745,16 @@
         <v>166</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>21</v>
@@ -17782,28 +17782,28 @@
         <v>187</v>
       </c>
       <c r="Y126" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="Z126" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="Z126" t="s" s="2">
+      <c r="AA126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17824,7 +17824,7 @@
         <v>21</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>21</v>
@@ -17864,16 +17864,16 @@
         <v>295</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>21</v>
@@ -17901,28 +17901,28 @@
         <v>148</v>
       </c>
       <c r="Y127" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="Z127" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="Z127" t="s" s="2">
+      <c r="AA127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF127" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17943,13 +17943,13 @@
         <v>21</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="128">
@@ -17983,16 +17983,16 @@
         <v>132</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>21</v>
@@ -18005,43 +18005,43 @@
         <v>21</v>
       </c>
       <c r="T128" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF128" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18062,13 +18062,13 @@
         <v>21</v>
       </c>
       <c r="AM128" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO128" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>511</v>
       </c>
     </row>
     <row r="129">
@@ -18102,13 +18102,13 @@
         <v>104</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -18122,43 +18122,43 @@
         <v>21</v>
       </c>
       <c r="T129" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF129" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18179,13 +18179,13 @@
         <v>21</v>
       </c>
       <c r="AM129" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO129" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>519</v>
       </c>
     </row>
     <row r="130" hidden="true">
@@ -18219,10 +18219,10 @@
         <v>231</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18273,7 +18273,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18294,13 +18294,13 @@
         <v>21</v>
       </c>
       <c r="AM130" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO130" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>525</v>
       </c>
     </row>
     <row r="131" hidden="true">
@@ -18331,16 +18331,16 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="L131" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="L131" t="s" s="2">
+      <c r="M131" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18390,7 +18390,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18411,13 +18411,13 @@
         <v>21</v>
       </c>
       <c r="AM131" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO131" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>533</v>
       </c>
     </row>
     <row r="132" hidden="true">
@@ -23118,7 +23118,7 @@
         <v>21</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L172" t="s" s="2">
         <v>828</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,10 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Bildet eine "Geplante Abgabe" eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag ab ("MedicationRequest"-Ressource mit Kategorie "Geplante Abgabe"):
-Sie enthält die verordnete Medikation und deren Dosierung und spielgelt die Inhalte des e-Rezepts wider. Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation. 
-Werden mehrere Medikamente gleichzeitig verschrieben und sollen demselben e-Rezept zugeordnet sein, wird für jedes Medikament eine "Geplante Abgabe" mit demselben "e-Med GroupIdentifier" erstellt (bildet 'Rezept-Klammer'). 
-Es werden R5-Backport-Extensions verwendet.</t>
+    <t>Profil einer "Geplanten Abgabe" eines Arzneimittels aus dem Medikationsplan.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -272,7 +269,7 @@
 </t>
   </si>
   <si>
-    <t>Geplante Abgabe eines Arzneimittels aus dem Medikationsplan. Verwendet R5 Backport Extensions.</t>
+    <t>Ordering of medication for patient or group</t>
   </si>
   <si>
     <t>An order or request for both supply of the medication and the instructions for administration of the medication to a patient. The resource is called "MedicationRequest" rather than "MedicationPrescription" or "MedicationOrder" to generalize the use across inpatient and outpatient settings, including care plans, etc., and to harmonize with workflow patterns.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$178</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6710" uniqueCount="876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="867">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1487,7 +1487,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-patient)
 </t>
   </si>
   <si>
@@ -1736,7 +1736,7 @@
     <t>MedicationRequest.authoredOn</t>
   </si>
   <si>
-    <t>Datum der Ausstellung der geplanten Abgabe.</t>
+    <t>Datum der Verordnung der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
@@ -1760,7 +1760,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
@@ -2187,7 +2187,7 @@
     <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:extension.value}
+    <t xml:space="preserve">value:extension.value.ofType(CodeableConcept).coding.code}
 </t>
   </si>
   <si>
@@ -2198,39 +2198,6 @@
   </si>
   <si>
     <t>see dosageInstruction mapping</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction:otherDosage</t>
-  </si>
-  <si>
-    <t>otherDosage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-other-administration}
-</t>
-  </si>
-  <si>
-    <t>How the medication should be taken</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction:timedDosage</t>
-  </si>
-  <si>
-    <t>timedDosage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-timed-administration}
-</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction:frequencyDosage</t>
-  </si>
-  <si>
-    <t>frequencyDosage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-frequency-administration}
-</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction:freitextDosage</t>
@@ -2241,6 +2208,9 @@
   <si>
     <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-freetext-administration}
 </t>
+  </si>
+  <si>
+    <t>How the medication should be taken</t>
   </si>
   <si>
     <t>MedicationRequest.dosageInstruction:standardDosage</t>
@@ -3079,7 +3049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO181"/>
+  <dimension ref="A1:AO178"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.57421875" customWidth="true" bestFit="true"/>
@@ -3092,7 +3062,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="195.8359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="199.48828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3109,7 +3079,7 @@
     <col min="25" max="25" width="138.53125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="50.23046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -11426,7 +11396,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>90</v>
@@ -18665,7 +18635,7 @@
         <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>91</v>
@@ -19113,7 +19083,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
         <v>681</v>
       </c>
@@ -19132,7 +19102,7 @@
         <v>90</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>21</v>
@@ -19678,7 +19648,7 @@
         <v>21</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>102</v>
+        <v>707</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>698</v>
@@ -19698,23 +19668,21 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="C143" t="s" s="2">
         <v>708</v>
       </c>
+      <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>91</v>
@@ -19729,14 +19697,12 @@
         <v>709</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>695</v>
-      </c>
+        <v>711</v>
+      </c>
+      <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>21</v>
@@ -19785,13 +19751,13 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>691</v>
+        <v>708</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>21</v>
@@ -19800,13 +19766,13 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>698</v>
+        <v>21</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>21</v>
+        <v>712</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>699</v>
+        <v>713</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>21</v>
@@ -19815,16 +19781,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="C144" t="s" s="2">
-        <v>711</v>
-      </c>
+        <v>714</v>
+      </c>
+      <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
         <v>21</v>
       </c>
@@ -19833,10 +19797,10 @@
         <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>21</v>
@@ -19845,17 +19809,15 @@
         <v>21</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>712</v>
+        <v>104</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>703</v>
+        <v>105</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>695</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>21</v>
@@ -19904,28 +19866,28 @@
         <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>691</v>
+        <v>107</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>698</v>
+        <v>21</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>699</v>
+        <v>108</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>21</v>
@@ -19934,18 +19896,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="C145" t="s" s="2">
-        <v>714</v>
-      </c>
+        <v>715</v>
+      </c>
+      <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -19955,7 +19915,7 @@
         <v>81</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>21</v>
@@ -19964,16 +19924,16 @@
         <v>21</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>715</v>
+        <v>111</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>703</v>
+        <v>112</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>694</v>
+        <v>113</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>695</v>
+        <v>114</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -20023,7 +19983,7 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>691</v>
+        <v>118</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20035,30 +19995,30 @@
         <v>21</v>
       </c>
       <c r="AJ145" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO145" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="146" hidden="true">
+      <c r="A146" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="AK145" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="AL145" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM145" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO145" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s" s="2">
-        <v>717</v>
-      </c>
       <c r="B146" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20066,28 +20026,28 @@
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I146" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I146" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J146" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>718</v>
+        <v>111</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>720</v>
+        <v>209</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20138,28 +20098,28 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>721</v>
+        <v>21</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>722</v>
+        <v>21</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>21</v>
@@ -20170,10 +20130,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20196,15 +20156,17 @@
         <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>104</v>
+        <v>709</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>105</v>
+        <v>720</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N147" s="2"/>
+        <v>721</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>722</v>
+      </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>21</v>
@@ -20253,7 +20215,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>107</v>
+        <v>719</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20265,7 +20227,7 @@
         <v>21</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>21</v>
@@ -20274,7 +20236,7 @@
         <v>21</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>108</v>
+        <v>723</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>21</v>
@@ -20292,14 +20254,14 @@
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>21</v>
@@ -20311,17 +20273,15 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>21</v>
@@ -20370,19 +20330,19 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>21</v>
@@ -20409,34 +20369,36 @@
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I149" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>726</v>
+        <v>112</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N149" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>21</v>
@@ -20485,7 +20447,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>727</v>
+        <v>118</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20506,7 +20468,7 @@
         <v>21</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>21</v>
@@ -20517,44 +20479,46 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>21</v>
+        <v>727</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I150" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>718</v>
+        <v>111</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O150" t="s" s="2">
         <v>730</v>
       </c>
-      <c r="N150" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
         <v>21</v>
       </c>
@@ -20602,19 +20566,19 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>21</v>
@@ -20623,7 +20587,7 @@
         <v>21</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>732</v>
+        <v>191</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>21</v>
@@ -20634,10 +20598,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20660,13 +20624,13 @@
         <v>21</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>104</v>
+        <v>732</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>105</v>
+        <v>733</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>106</v>
+        <v>734</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -20717,7 +20681,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>107</v>
+        <v>731</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20729,7 +20693,7 @@
         <v>21</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>21</v>
+        <v>735</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>21</v>
@@ -20738,7 +20702,7 @@
         <v>21</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>108</v>
+        <v>736</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>21</v>
@@ -20749,21 +20713,21 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>21</v>
@@ -20775,17 +20739,15 @@
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>111</v>
+        <v>738</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>112</v>
+        <v>739</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>740</v>
+      </c>
+      <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>21</v>
@@ -20834,19 +20796,19 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>118</v>
+        <v>737</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>21</v>
@@ -20855,7 +20817,7 @@
         <v>21</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>108</v>
+        <v>741</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>21</v>
@@ -20866,46 +20828,42 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>736</v>
+        <v>21</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I153" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>111</v>
+        <v>738</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>739</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="N153" s="2"/>
+      <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>21</v>
       </c>
@@ -20953,19 +20911,19 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>727</v>
+        <v>742</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>21</v>
@@ -20974,7 +20932,7 @@
         <v>21</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>191</v>
+        <v>741</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>21</v>
@@ -20983,12 +20941,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="154" hidden="true">
+    <row r="154">
       <c r="A154" t="s" s="2">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20996,13 +20954,13 @@
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G154" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>21</v>
@@ -21011,16 +20969,20 @@
         <v>21</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>741</v>
+        <v>231</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="N154" s="2"/>
-      <c r="O154" s="2"/>
+        <v>747</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>749</v>
+      </c>
       <c r="P154" t="s" s="2">
         <v>21</v>
       </c>
@@ -21068,7 +21030,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21080,16 +21042,16 @@
         <v>21</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>744</v>
+        <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>21</v>
+        <v>750</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>21</v>
@@ -21100,10 +21062,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21126,13 +21088,13 @@
         <v>21</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>747</v>
+        <v>104</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>748</v>
+        <v>105</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>749</v>
+        <v>106</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21183,7 +21145,7 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>746</v>
+        <v>107</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -21195,7 +21157,7 @@
         <v>21</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK155" t="s" s="2">
         <v>21</v>
@@ -21204,7 +21166,7 @@
         <v>21</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>750</v>
+        <v>108</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>21</v>
@@ -21215,21 +21177,21 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>21</v>
@@ -21241,15 +21203,17 @@
         <v>21</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>747</v>
+        <v>111</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>752</v>
+        <v>112</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="N156" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>21</v>
@@ -21286,31 +21250,31 @@
         <v>21</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>751</v>
+        <v>118</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>21</v>
@@ -21319,7 +21283,7 @@
         <v>21</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>750</v>
+        <v>108</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>21</v>
@@ -21341,7 +21305,7 @@
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G157" t="s" s="2">
         <v>90</v>
@@ -21353,23 +21317,21 @@
         <v>21</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>755</v>
+        <v>242</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>756</v>
+        <v>243</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>758</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>21</v>
       </c>
@@ -21417,7 +21379,7 @@
         <v>21</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>754</v>
+        <v>245</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21426,7 +21388,7 @@
         <v>90</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>21</v>
+        <v>246</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>102</v>
@@ -21435,24 +21397,24 @@
         <v>21</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>759</v>
+        <v>21</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>760</v>
+        <v>247</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>21</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="158" hidden="true">
+    <row r="158">
       <c r="A158" t="s" s="2">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21466,29 +21428,33 @@
         <v>90</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>105</v>
+        <v>251</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N158" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q158" s="2"/>
+      <c r="Q158" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="R158" t="s" s="2">
         <v>21</v>
       </c>
@@ -21532,7 +21498,7 @@
         <v>21</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>107</v>
+        <v>255</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21541,10 +21507,10 @@
         <v>90</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>21</v>
+        <v>246</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>21</v>
@@ -21553,35 +21519,35 @@
         <v>21</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>108</v>
+        <v>256</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
     </row>
-    <row r="159" hidden="true">
+    <row r="159">
       <c r="A159" t="s" s="2">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H159" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I159" t="s" s="2">
         <v>21</v>
@@ -21590,16 +21556,16 @@
         <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>111</v>
+        <v>757</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>112</v>
+        <v>758</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>113</v>
+        <v>759</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>114</v>
+        <v>760</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -21637,54 +21603,54 @@
         <v>21</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>118</v>
+        <v>756</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>21</v>
+        <v>761</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>108</v>
+        <v>762</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>21</v>
+        <v>763</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21692,7 +21658,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>90</v>
@@ -21704,20 +21670,18 @@
         <v>21</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>241</v>
+        <v>732</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>242</v>
+        <v>765</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>766</v>
+      </c>
+      <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>21</v>
@@ -21766,7 +21730,7 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>245</v>
+        <v>764</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21775,33 +21739,33 @@
         <v>90</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>102</v>
+        <v>735</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>21</v>
+        <v>767</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>247</v>
+        <v>768</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>248</v>
+        <v>769</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21815,33 +21779,29 @@
         <v>90</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J161" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>241</v>
+        <v>104</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>251</v>
+        <v>105</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q161" t="s" s="2">
-        <v>254</v>
-      </c>
+      <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
         <v>21</v>
       </c>
@@ -21885,7 +21845,7 @@
         <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>255</v>
+        <v>107</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -21894,10 +21854,10 @@
         <v>90</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>21</v>
@@ -21906,35 +21866,35 @@
         <v>21</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>256</v>
+        <v>108</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>257</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>21</v>
@@ -21943,16 +21903,16 @@
         <v>21</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>766</v>
+        <v>111</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>767</v>
+        <v>112</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>768</v>
+        <v>113</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>769</v>
+        <v>114</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -21990,54 +21950,54 @@
         <v>21</v>
       </c>
       <c r="AB162" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="AC162" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AD162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE162" t="s" s="2">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>765</v>
+        <v>118</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH162" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>770</v>
+        <v>21</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>771</v>
+        <v>108</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>772</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22045,7 +22005,7 @@
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G163" t="s" s="2">
         <v>90</v>
@@ -22057,10 +22017,10 @@
         <v>21</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>741</v>
+        <v>773</v>
       </c>
       <c r="L163" t="s" s="2">
         <v>774</v>
@@ -22068,8 +22028,12 @@
       <c r="M163" t="s" s="2">
         <v>775</v>
       </c>
-      <c r="N163" s="2"/>
-      <c r="O163" s="2"/>
+      <c r="N163" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>777</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>21</v>
       </c>
@@ -22117,7 +22081,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22129,30 +22093,30 @@
         <v>21</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>744</v>
+        <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>776</v>
+        <v>21</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22163,32 +22127,36 @@
         <v>80</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I164" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>105</v>
+        <v>782</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>106</v>
+        <v>783</v>
       </c>
       <c r="N164" s="2"/>
-      <c r="O164" s="2"/>
+      <c r="O164" t="s" s="2">
+        <v>784</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q164" s="2"/>
+      <c r="Q164" t="s" s="2">
+        <v>785</v>
+      </c>
       <c r="R164" t="s" s="2">
         <v>21</v>
       </c>
@@ -22208,13 +22176,13 @@
         <v>21</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>21</v>
+        <v>786</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>21</v>
+        <v>787</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>21</v>
@@ -22232,7 +22200,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>107</v>
+        <v>788</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22244,7 +22212,7 @@
         <v>21</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
         <v>21</v>
@@ -22253,55 +22221,55 @@
         <v>21</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>108</v>
+        <v>789</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>21</v>
+        <v>790</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
-        <v>780</v>
+        <v>791</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>780</v>
+        <v>791</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>112</v>
+        <v>792</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O165" s="2"/>
+        <v>793</v>
+      </c>
+      <c r="N165" s="2"/>
+      <c r="O165" t="s" s="2">
+        <v>794</v>
+      </c>
       <c r="P165" t="s" s="2">
         <v>21</v>
       </c>
@@ -22337,31 +22305,31 @@
         <v>21</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="AC165" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AD165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE165" t="s" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>118</v>
+        <v>795</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>21</v>
@@ -22370,21 +22338,21 @@
         <v>21</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>108</v>
+        <v>796</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>21</v>
+        <v>797</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>781</v>
+        <v>798</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>781</v>
+        <v>798</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22398,7 +22366,7 @@
         <v>90</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>21</v>
@@ -22407,19 +22375,17 @@
         <v>91</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>782</v>
+        <v>132</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>783</v>
+        <v>799</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>785</v>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>21</v>
@@ -22468,7 +22434,7 @@
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22477,7 +22443,7 @@
         <v>90</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>21</v>
+        <v>803</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>102</v>
@@ -22489,21 +22455,21 @@
         <v>21</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>788</v>
+        <v>804</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>789</v>
+        <v>797</v>
       </c>
     </row>
-    <row r="167" hidden="true">
+    <row r="167">
       <c r="A167" t="s" s="2">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22514,13 +22480,13 @@
         <v>80</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I167" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J167" t="s" s="2">
         <v>91</v>
@@ -22529,21 +22495,21 @@
         <v>166</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>791</v>
+        <v>806</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="N167" s="2"/>
+        <v>807</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>808</v>
+      </c>
       <c r="O167" t="s" s="2">
-        <v>793</v>
+        <v>809</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q167" t="s" s="2">
-        <v>794</v>
-      </c>
+      <c r="Q167" s="2"/>
       <c r="R167" t="s" s="2">
         <v>21</v>
       </c>
@@ -22563,13 +22529,13 @@
         <v>21</v>
       </c>
       <c r="X167" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>795</v>
+        <v>21</v>
       </c>
       <c r="Z167" t="s" s="2">
-        <v>796</v>
+        <v>21</v>
       </c>
       <c r="AA167" t="s" s="2">
         <v>21</v>
@@ -22587,7 +22553,7 @@
         <v>21</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>797</v>
+        <v>810</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22608,21 +22574,21 @@
         <v>21</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>798</v>
+        <v>811</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22636,27 +22602,27 @@
         <v>90</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>104</v>
+        <v>738</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="N168" s="2"/>
-      <c r="O168" t="s" s="2">
-        <v>803</v>
-      </c>
+        <v>814</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>21</v>
       </c>
@@ -22704,7 +22670,7 @@
         <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22722,24 +22688,24 @@
         <v>21</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>21</v>
+        <v>816</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>806</v>
+        <v>21</v>
       </c>
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>807</v>
+        <v>818</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>807</v>
+        <v>818</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22759,21 +22725,19 @@
         <v>21</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>132</v>
+        <v>526</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>809</v>
+        <v>820</v>
       </c>
       <c r="N169" s="2"/>
-      <c r="O169" t="s" s="2">
-        <v>810</v>
-      </c>
+      <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>21</v>
       </c>
@@ -22821,7 +22785,7 @@
         <v>21</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22830,7 +22794,7 @@
         <v>90</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>812</v>
+        <v>21</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>102</v>
@@ -22842,21 +22806,21 @@
         <v>21</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>21</v>
+        <v>598</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>806</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22870,29 +22834,25 @@
         <v>90</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J170" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>166</v>
+        <v>709</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>818</v>
-      </c>
+        <v>824</v>
+      </c>
+      <c r="N170" s="2"/>
+      <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>21</v>
       </c>
@@ -22940,7 +22900,7 @@
         <v>21</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22958,24 +22918,24 @@
         <v>21</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>21</v>
+        <v>825</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO170" t="s" s="2">
-        <v>806</v>
+        <v>21</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22998,17 +22958,15 @@
         <v>21</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>747</v>
+        <v>104</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>822</v>
+        <v>105</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>824</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N171" s="2"/>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>21</v>
@@ -23057,7 +23015,7 @@
         <v>21</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>821</v>
+        <v>107</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23069,16 +23027,16 @@
         <v>21</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>825</v>
+        <v>21</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>826</v>
+        <v>108</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>21</v>
@@ -23089,21 +23047,21 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>21</v>
@@ -23115,15 +23073,17 @@
         <v>21</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>526</v>
+        <v>111</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>828</v>
+        <v>112</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="N172" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>21</v>
@@ -23172,19 +23132,19 @@
         <v>21</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>827</v>
+        <v>118</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>21</v>
@@ -23193,10 +23153,10 @@
         <v>21</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>830</v>
+        <v>108</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>598</v>
+        <v>21</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>21</v>
@@ -23204,42 +23164,46 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>21</v>
+        <v>727</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I173" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>718</v>
+        <v>111</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>832</v>
+        <v>728</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="N173" s="2"/>
-      <c r="O173" s="2"/>
+        <v>729</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>730</v>
+      </c>
       <c r="P173" t="s" s="2">
         <v>21</v>
       </c>
@@ -23287,28 +23251,28 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>831</v>
+        <v>718</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI173" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>834</v>
+        <v>21</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>835</v>
+        <v>191</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>21</v>
@@ -23319,10 +23283,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23330,7 +23294,7 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G174" t="s" s="2">
         <v>90</v>
@@ -23345,15 +23309,17 @@
         <v>21</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>104</v>
+        <v>831</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>105</v>
+        <v>832</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N174" s="2"/>
+        <v>833</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>834</v>
+      </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>21</v>
@@ -23378,13 +23344,13 @@
         <v>21</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>21</v>
+        <v>835</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>21</v>
+        <v>836</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>21</v>
@@ -23402,10 +23368,10 @@
         <v>21</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>107</v>
+        <v>830</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>90</v>
@@ -23414,41 +23380,41 @@
         <v>21</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>21</v>
+        <v>825</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>108</v>
+        <v>837</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>21</v>
+        <v>838</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>21</v>
@@ -23460,17 +23426,15 @@
         <v>21</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>111</v>
+        <v>295</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>112</v>
+        <v>840</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>841</v>
+      </c>
+      <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>21</v>
@@ -23495,13 +23459,13 @@
         <v>21</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>21</v>
+        <v>842</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>21</v>
+        <v>843</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>21</v>
@@ -23519,78 +23483,74 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>118</v>
+        <v>839</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>21</v>
+        <v>844</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>108</v>
+        <v>845</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>21</v>
+        <v>846</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>838</v>
+        <v>847</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>736</v>
+        <v>21</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I176" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>111</v>
+        <v>848</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>737</v>
+        <v>849</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>739</v>
-      </c>
+        <v>850</v>
+      </c>
+      <c r="N176" s="2"/>
+      <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
         <v>21</v>
       </c>
@@ -23638,28 +23598,28 @@
         <v>21</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>727</v>
+        <v>847</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>21</v>
+        <v>851</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>21</v>
+        <v>844</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>191</v>
+        <v>852</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>21</v>
@@ -23670,21 +23630,21 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>839</v>
+        <v>853</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>839</v>
+        <v>853</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>21</v>
+        <v>854</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>21</v>
@@ -23696,16 +23656,16 @@
         <v>21</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>841</v>
+        <v>856</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>842</v>
+        <v>857</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>843</v>
+        <v>858</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23731,13 +23691,13 @@
         <v>21</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>844</v>
+        <v>21</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>845</v>
+        <v>21</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>21</v>
@@ -23755,13 +23715,13 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>839</v>
+        <v>853</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>21</v>
@@ -23773,24 +23733,24 @@
         <v>21</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>834</v>
+        <v>21</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>846</v>
+        <v>859</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>847</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23801,7 +23761,7 @@
         <v>80</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>21</v>
@@ -23813,15 +23773,17 @@
         <v>21</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>295</v>
+        <v>861</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="N178" s="2"/>
+        <v>863</v>
+      </c>
+      <c r="N178" t="s" s="2">
+        <v>864</v>
+      </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>21</v>
@@ -23846,13 +23808,13 @@
         <v>21</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>851</v>
+        <v>21</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>852</v>
+        <v>21</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>21</v>
@@ -23870,13 +23832,13 @@
         <v>21</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>21</v>
@@ -23885,372 +23847,23 @@
         <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>21</v>
+        <v>865</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>853</v>
+        <v>21</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="179" hidden="true">
-      <c r="A179" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="C179" s="2"/>
-      <c r="D179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E179" s="2"/>
-      <c r="F179" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G179" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K179" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="L179" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N179" s="2"/>
-      <c r="O179" s="2"/>
-      <c r="P179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q179" s="2"/>
-      <c r="R179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF179" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="AG179" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH179" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ179" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK179" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="AL179" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="AM179" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="AN179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO179" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="180" hidden="true">
-      <c r="A180" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="C180" s="2"/>
-      <c r="D180" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="E180" s="2"/>
-      <c r="F180" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K180" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="L180" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="O180" s="2"/>
-      <c r="P180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q180" s="2"/>
-      <c r="R180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF180" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="AG180" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH180" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ180" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM180" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="AN180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO180" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="181" hidden="true">
-      <c r="A181" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="C181" s="2"/>
-      <c r="D181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E181" s="2"/>
-      <c r="F181" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K181" t="s" s="2">
-        <v>870</v>
-      </c>
-      <c r="L181" t="s" s="2">
-        <v>871</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>872</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="O181" s="2"/>
-      <c r="P181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q181" s="2"/>
-      <c r="R181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF181" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="AG181" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH181" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ181" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK181" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="AL181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM181" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="AN181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO181" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO181">
+  <autoFilter ref="A1:AO178">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -24260,7 +23873,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI180">
+  <conditionalFormatting sqref="A2:AI177">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1336,7 +1336,7 @@
     <t>MedicationRequest.doNotPerform</t>
   </si>
   <si>
-    <t>Fachliche Begründung: Die geplante Abgabe bildet einen positiven Abgabeauftrag ab; ein ausdrückliches Verbot einer Abgabe wird nicht als eigene geplante Abgabe dokumentiert.</t>
+    <t>Fachliche Begründung: Die Geplante Abgabe bildet einen positiven Abgabeauftrag ab; ein ausdrückliches Verbot einer Abgabe wird nicht als eigene Geplante Abgabe dokumentiert.</t>
   </si>
   <si>
     <t>If true indicates that the provider is asking for the medication request not to occur.</t>
@@ -1355,7 +1355,7 @@
 Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)</t>
   </si>
   <si>
-    <t>Fachliche Begründung: Die geplante Abgabe wird als Auftrag dokumentiert; eine Kennzeichnung als lediglich berichteter Auftrag würde die Bedeutung der Ressource verändern und wird daher nicht verwendet.</t>
+    <t>Fachliche Begründung: Die Geplante Abgabe wird als Auftrag dokumentiert; eine Kennzeichnung als lediglich berichteter Auftrag würde die Bedeutung der Ressource verändern und wird daher nicht verwendet.</t>
   </si>
   <si>
     <t>Indicates if this record was captured as a secondary 'reported' record rather than as an original primary source-of-truth record.  It may also indicate the source of the report.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1371,7 +1371,7 @@
 </t>
   </si>
   <si>
-    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als logische Referenz dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
+    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als conditional reference dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="868">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -689,10 +689,10 @@
 </t>
   </si>
   <si>
-    <t>Zeitraum, in dem die Medikation eingenommen werden soll.</t>
-  </si>
-  <si>
-    <t>Zeitraum, über den die Medikation eingenommen werden soll. Wenn mehrere dosageInstruction-Zeilen vorhanden sind (z. B. bei einer ausschleichenden Dosierung), entspricht dieser Zeitraum dem frühesten Startdatum und dem spätesten Enddatum der dosageInstructions.</t>
+    <t>Geplanter Einnahmezeitraum. Beginn: aktuelles Datum oder in der Zukunft, Ende: Datum in der Zukunft oder unbefristet. Der geplante Einnahmezeitraum muss mit den zeitlichen Einschränkungen der Dosage übereinstimmen.</t>
+  </si>
+  <si>
+    <t>R5: `MedicationRequest.effectiveDosePeriod` (new:Period)</t>
   </si>
   <si>
     <t>Element `MedicationRequest.effectiveDosePeriod` has a context of MedicationRequest based on following the parent source element upwards and mapping to `MedicationRequest`.
@@ -914,7 +914,7 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status der geplanten Abgabe. Mögliche Ausprägung: [active | completed | entered-in-error | stopped]. Bedeutung: active: offene, Geplante Abgabe | completed: Geplante Abgabe abgeschlossen | entered-in-error: nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde | stopped: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)</t>
+    <t>Status der Geplanten Abgabe. Mögliche Ausprägung: [active | completed | entered-in-error | stopped | cancelled]. Bedeutung: active: offene, Geplante Abgabe | completed: Geplante Abgabe abgeschlossen (automatisch durch Fachanwendung gesetzt)| entered-in-error: nach fehlerhafter Eingabe (Storno nur möglich, wenn noch keine Abgabe durchgeführt wurde) | stopped: Geplante Abgabe zeitlich abgelaufen (automatisch durch Fachanwendung gesetzt) | cancelled: Geplante Abgabe cancelled, wenn alle Durchgeführten Abgaben (jede Einlösung) den Status cancelled haben (automatisch durch Fachanwendung gesetzt)</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -969,7 +969,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>Die Geplante Abgabe stellt einen Auftrag zur Durchführung und eine Autorisierung des Verfassers dar; daher ist intent immer "order".</t>
+    <t>Fixer Wert: "order".</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -1041,7 +1041,7 @@
     <t>mrcategory</t>
   </si>
   <si>
-    <t>Kategorie zur Unterscheidung eines Medikationsplaneintrags von einer geplanten Abgabe (beide haben intent order)</t>
+    <t>Kategorie zur Unterscheidung einer Geplanten Abgabe von einem Planeintrag (beide haben intent order).</t>
   </si>
   <si>
     <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedicationRequestCategoryVS</t>
@@ -1240,73 +1240,76 @@
     <t>MedicationRequest.category.text</t>
   </si>
   <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype</t>
+  </si>
+  <si>
+    <t>recipetype</t>
+  </si>
+  <si>
+    <t>Kategorie zur Unterscheidung, ob ein Kassen-, Privat- oder Substitutionsrezept erstellt wurde.</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-medikationrezeptart</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.system</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/medikationrezeptart</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.version</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.code</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.display</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.coding.userSelected</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:recipetype.text</t>
+  </si>
+  <si>
     <t>Fachliche Begründung: TODO</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype</t>
-  </si>
-  <si>
-    <t>recipetype</t>
-  </si>
-  <si>
-    <t>Kategorie zur Unterscheidung, ob ein Kassen-, Privat- oder Substitutionsrezept erstellt wurde.</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/ValueSet/elga-medikationrezeptart</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype.coding</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype.coding.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype.coding.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype.coding.system</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/CodeSystem/medikationrezeptart</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype.coding.version</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype.coding.code</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype.coding.display</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype.coding.userSelected</t>
-  </si>
-  <si>
-    <t>MedicationRequest.category:recipetype.text</t>
   </si>
   <si>
     <t>MedicationRequest.priority</t>
@@ -1371,7 +1374,7 @@
 </t>
   </si>
   <si>
-    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als conditional reference dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
+    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als Conditional Reference dokumentiert. Muss mit dem Planeintrag übereinstimmen.</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -1491,7 +1494,7 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den die Geplante Abgabe ausgestellt werden soll (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
+    <t>ELGA-Teilnehmer, für den die Geplante Abgabe erstellt wird.</t>
   </si>
   <si>
     <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
@@ -1541,6 +1544,9 @@
     <t>MedicationRequest.subject.identifier.use</t>
   </si>
   <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
     <t>The purpose of this identifier.</t>
   </si>
   <si>
@@ -1736,7 +1742,7 @@
     <t>MedicationRequest.authoredOn</t>
   </si>
   <si>
-    <t>Datum der Verordnung der geplanten Abgabe.</t>
+    <t>Datum der Erstellung der Geplanten Abgabe.</t>
   </si>
   <si>
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
@@ -1764,8 +1770,7 @@
 </t>
   </si>
   <si>
-    <t>Der Arzt oder die Ärztin, die die Geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist 
-(eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen).</t>
+    <t>GDA, welcher die Geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist.</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -1799,9 +1804,6 @@
   </si>
   <si>
     <t>MedicationRequest.requester.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
   </si>
   <si>
     <t>MedicationRequest.requester.identifier.type</t>
@@ -1977,7 +1979,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf die (aktuelle) Version des zugrundeliegenden Medikationsplaneintrags, auf dem diese Geplante Abgabe basiert.</t>
+    <t>Referenz auf die aktuelle Version des zugrundeliegenden Planeintrags, auf dem diese Geplante Abgabe basiert.</t>
   </si>
   <si>
     <t>A plan or request that is fulfilled in whole or in part by this medication request.</t>
@@ -2010,9 +2012,7 @@
     <t>MedicationRequest.groupIdentifier</t>
   </si>
   <si>
-    <t>Als groupIdentifier dient die eMED-ID, die auch im e-Rezept mitgeführt wird. 
-Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine 
-Geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
+    <t>Der e-Med GroupIdentifier bildet die Rezept-Klammer. Geplante Abgaben, die demselben e-Rezept zugeordnet sind, führen denselben e-Med GroupIdentifier.</t>
   </si>
   <si>
     <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>
@@ -2054,7 +2054,7 @@
     <t>MedicationRequest.courseOfTherapyType</t>
   </si>
   <si>
-    <t>Gesamtmuster der Medikamentengabe (z.B. saisonal). Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Art der Medikation. Keine Verwendung in der Geplanten Abgabe.</t>
   </si>
   <si>
     <t>The description of the overall patte3rn of the administration of the medication to the patient.</t>
@@ -2098,7 +2098,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen zur geplanten Abgabe (Kommunikation zwischen Arzt und Apotheke, die nicht die Dosierung betreffen).</t>
+    <t>Zusätzliche Informationen zur Geplanten Abgabe, die nicht die Dosierung betreffen.</t>
   </si>
   <si>
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
@@ -2234,7 +2234,7 @@
 </t>
   </si>
   <si>
-    <t>Details zur geplanten Abgabe des Arzneimittels.</t>
+    <t>Informationen zur geplanten Abgabe des Arzneimittels.</t>
   </si>
   <si>
     <t>Indicates the specific details for the dispense or medication supply part of a medication request (also known as a Medication Prescription or Medication Order).  Note that this information is not always sent with the order.  There may be in some settings (e.g. hospitals) institutional or system support for completing the dispense details in the pharmacy department.</t>
@@ -2347,14 +2347,10 @@
     <t>MedicationRequest.dispenseRequest.validityPeriod</t>
   </si>
   <si>
-    <t>Gültigkeitszeitraum einer Geplante Abgabe (abhängig von Rezeptart): Kassenrezept: ab Erstelldatum 1 Monat, bei Teilabgabe verlängert sich Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess). Privatrezept: ab Erstelldatum max. 365 Tage, die Gültigkeitsdauer kann vom Arzt definiert werden. Substitutionsrezept: Max. Gültigkeitsdauer 12 Monate.</t>
-  </si>
-  <si>
-    <t>Zeitraum in dem die Geplante Abgabe eingelöst werden kann.
-Der Gültigkeitszeitraum ist abhängig von der **Rezeptart**: 
-* **Kassenrezept**: ab Erstelldatum einen Monat gültig (vom Ausstellungszeitpunkt bis zum gleichen Tag des Folgemonats 23:59 Uhr); validityPeriod.start kein Datum in der Zukunft; bei einer Teilabgabe verlängert sich die gesamte Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess).
-* **Privatrezept**: ab Erstelldatum maximal 365 Tage gültig, wenn die erste Einlösung innerhalb von 1 Monat ab Erstelldatum erfolgt (sonst Status abgelaufen). validityPeriod.start kein Datum in der Zukunft; Die Gültigkeitsdauer (validityPeriod.end) kann vom Arzt definiert werden.
-* **Substitutionsrezept**: Maximale Gültigkeitsdauer 12 Monate. Das validityPeriod.start darf maximal einen Monat in der Zukunft liegen, gültig bis das validityPeriod.end erreicht ist.</t>
+    <t>Gültigkeitszeitraum einer Geplante Abgabe (abhängig von der Rezeptart).</t>
+  </si>
+  <si>
+    <t>This indicates the validity period of a prescription (stale dating the Prescription).</t>
   </si>
   <si>
     <t>It reflects the prescribers' perspective for the validity of the prescription. Dispenses must not be made against the prescription outside of this period. The lower-bound of the Dispensing Window signifies the earliest date that the prescription can be filled for the first time. If an upper-bound is not specified then the Prescription is open-ended or will default to a stale-date based on regulations.</t>
@@ -2388,13 +2384,10 @@
 </t>
   </si>
   <si>
-    <t>Die Anzahl der weiteren möglichen Einlösungen (abhängig von Rezeptart): Kassenrezept: keine weitere Einlösung möglich (fixer Wert 0). Privatrezept: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden. Substitutionsrezept: keine weitere Einlösung möglich (fixer Wert 0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anzahl der weiteren möglichen Einlösungen:
-* **Kassenrezept**: keine weitere Einlösung möglich (fixer Wert 0)
-* **Privatrezept**: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden
-* **Substitutionsrezept**: keine weitere Einlösung möglich (fixer Wert 0) </t>
+    <t>Die Anzahl der weiteren möglichen Einlösungen (abhängig von der Rezeptart).</t>
+  </si>
+  <si>
+    <t>An integer indicating the number of times, in addition to the original dispense, (aka refills or repeats) that the patient can receive the prescribed medication. Usage Notes: This integer does not include the original order dispense. This means that if an order indicates dispense 30 tablets plus "3 repeats", then the order can be dispensed a total of 4 times and the patient can receive a total of 120 tablets.  A prescriber may explicitly say that zero refills are permitted after the initial dispense.</t>
   </si>
   <si>
     <t>If displaying "number of authorized fills", add 1 to this number.</t>
@@ -2412,9 +2405,7 @@
     <t>MedicationRequest.dispenseRequest.quantity</t>
   </si>
   <si>
-    <t>Menge des Medikaments, die bei jeder Abgabe bereitgestellt werden soll.
-Da sich die Angaben zum Arzneimittel jeweils auf eine Packung der Arznei beziehen, MUSS die Anzahl der auszugebenden Packungen angegeben werden (mindestens 1). 
-Dies gilt für Arzneimittel mit PZN und magistralen Zubereitungen.</t>
+    <t>Bereitzustellende Menge bei jeder Abgabe bereitgestellt.</t>
   </si>
   <si>
     <t>The amount that is to be dispensed for one fill.</t>
@@ -10599,7 +10590,7 @@
         <v>104</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>392</v>
@@ -10689,10 +10680,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10718,10 +10709,10 @@
         <v>166</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10751,10 +10742,10 @@
         <v>187</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -10772,7 +10763,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10787,16 +10778,16 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>21</v>
@@ -10804,10 +10795,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10833,13 +10824,13 @@
         <v>381</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10889,7 +10880,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10910,7 +10901,7 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -10921,10 +10912,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10947,13 +10938,13 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -11004,7 +10995,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -11025,7 +11016,7 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -11036,10 +11027,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11062,16 +11053,16 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11121,7 +11112,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>90</v>
@@ -11136,27 +11127,27 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11268,10 +11259,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11385,10 +11376,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11414,13 +11405,13 @@
         <v>104</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11470,7 +11461,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11479,7 +11470,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11502,10 +11493,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11531,13 +11522,13 @@
         <v>132</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11566,10 +11557,10 @@
         <v>148</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>21</v>
@@ -11587,7 +11578,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11619,10 +11610,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11648,13 +11639,13 @@
         <v>276</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11704,7 +11695,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11725,7 +11716,7 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -11736,10 +11727,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11765,13 +11756,13 @@
         <v>104</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11821,7 +11812,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11853,10 +11844,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11879,16 +11870,16 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11938,7 +11929,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>90</v>
@@ -11953,27 +11944,27 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12085,10 +12076,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12202,10 +12193,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12231,13 +12222,13 @@
         <v>104</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12287,7 +12278,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12296,7 +12287,7 @@
         <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>102</v>
@@ -12319,10 +12310,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12348,13 +12339,13 @@
         <v>132</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12383,10 +12374,10 @@
         <v>148</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>21</v>
@@ -12404,7 +12395,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12436,10 +12427,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12465,13 +12456,13 @@
         <v>276</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12521,7 +12512,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12542,7 +12533,7 @@
         <v>21</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -12553,10 +12544,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12668,10 +12659,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12785,10 +12776,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12814,16 +12805,16 @@
         <v>166</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>391</v>
+        <v>487</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -12851,10 +12842,10 @@
         <v>187</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>21</v>
@@ -12872,7 +12863,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12893,7 +12884,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -12904,10 +12895,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12933,16 +12924,16 @@
         <v>295</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -12970,10 +12961,10 @@
         <v>148</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>21</v>
@@ -12991,7 +12982,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13012,21 +13003,21 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13052,16 +13043,16 @@
         <v>132</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -13074,7 +13065,7 @@
         <v>21</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>21</v>
@@ -13110,7 +13101,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13131,21 +13122,21 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13171,13 +13162,13 @@
         <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13191,7 +13182,7 @@
         <v>21</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>21</v>
@@ -13227,7 +13218,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13248,21 +13239,21 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13288,10 +13279,10 @@
         <v>231</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13342,7 +13333,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13363,21 +13354,21 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13400,16 +13391,16 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13459,7 +13450,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13480,21 +13471,21 @@
         <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13520,13 +13511,13 @@
         <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13576,7 +13567,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13608,10 +13599,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13634,16 +13625,16 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13693,7 +13684,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13708,27 +13699,27 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>291</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13751,13 +13742,13 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13808,7 +13799,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13823,16 +13814,16 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>21</v>
@@ -13840,10 +13831,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13869,10 +13860,10 @@
         <v>241</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13923,7 +13914,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13938,27 +13929,27 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13981,13 +13972,13 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14038,7 +14029,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14053,16 +14044,16 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>21</v>
@@ -14070,10 +14061,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14185,10 +14176,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14302,10 +14293,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14331,13 +14322,13 @@
         <v>104</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14387,7 +14378,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14396,7 +14387,7 @@
         <v>90</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>102</v>
@@ -14419,10 +14410,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14448,13 +14439,13 @@
         <v>132</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14483,10 +14474,10 @@
         <v>148</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>21</v>
@@ -14504,7 +14495,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14536,10 +14527,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14565,13 +14556,13 @@
         <v>276</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14621,7 +14612,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14642,7 +14633,7 @@
         <v>21</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>21</v>
@@ -14653,10 +14644,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14768,10 +14759,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14885,10 +14876,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14914,16 +14905,16 @@
         <v>166</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>571</v>
+        <v>487</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
@@ -14951,10 +14942,10 @@
         <v>187</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>21</v>
@@ -14972,7 +14963,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14993,7 +14984,7 @@
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>21</v>
@@ -15004,10 +14995,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15033,16 +15024,16 @@
         <v>295</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
@@ -15070,10 +15061,10 @@
         <v>148</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>21</v>
@@ -15091,7 +15082,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15112,21 +15103,21 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15152,16 +15143,16 @@
         <v>132</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
@@ -15174,7 +15165,7 @@
         <v>21</v>
       </c>
       <c r="T104" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="U104" t="s" s="2">
         <v>21</v>
@@ -15210,7 +15201,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15231,21 +15222,21 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15271,13 +15262,13 @@
         <v>104</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15291,7 +15282,7 @@
         <v>21</v>
       </c>
       <c r="T105" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="U105" t="s" s="2">
         <v>21</v>
@@ -15327,7 +15318,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15348,21 +15339,21 @@
         <v>21</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15388,10 +15379,10 @@
         <v>231</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15442,7 +15433,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15463,21 +15454,21 @@
         <v>21</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15500,16 +15491,16 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15559,7 +15550,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15580,21 +15571,21 @@
         <v>21</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15620,13 +15611,13 @@
         <v>104</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15676,7 +15667,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15708,10 +15699,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15734,13 +15725,13 @@
         <v>21</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15791,7 +15782,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15806,16 +15797,16 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>21</v>
@@ -15823,10 +15814,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15852,13 +15843,13 @@
         <v>295</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15887,10 +15878,10 @@
         <v>156</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>21</v>
@@ -15908,7 +15899,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15923,13 +15914,13 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>21</v>
@@ -15940,10 +15931,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15966,13 +15957,13 @@
         <v>21</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16023,7 +16014,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16044,10 +16035,10 @@
         <v>21</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>21</v>
@@ -16055,10 +16046,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16084,13 +16075,13 @@
         <v>295</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16119,10 +16110,10 @@
         <v>156</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>21</v>
@@ -16140,7 +16131,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16155,27 +16146,27 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16198,16 +16189,16 @@
         <v>21</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16257,7 +16248,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16272,16 +16263,16 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>291</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>21</v>
@@ -16289,10 +16280,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16315,13 +16306,13 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16372,7 +16363,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16387,13 +16378,13 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>21</v>
@@ -16404,10 +16395,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16433,10 +16424,10 @@
         <v>132</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16487,7 +16478,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16508,7 +16499,7 @@
         <v>21</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>21</v>
@@ -16519,10 +16510,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16545,13 +16536,13 @@
         <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16602,7 +16593,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16617,13 +16608,13 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>21</v>
@@ -16634,10 +16625,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16749,10 +16740,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16866,10 +16857,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16895,13 +16886,13 @@
         <v>104</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16951,7 +16942,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16960,7 +16951,7 @@
         <v>90</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>102</v>
@@ -16983,10 +16974,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17012,13 +17003,13 @@
         <v>132</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17047,10 +17038,10 @@
         <v>148</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>21</v>
@@ -17068,7 +17059,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17100,10 +17091,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17129,13 +17120,13 @@
         <v>276</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17185,7 +17176,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17206,7 +17197,7 @@
         <v>21</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>21</v>
@@ -17217,10 +17208,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17246,13 +17237,13 @@
         <v>104</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17302,7 +17293,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17334,10 +17325,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17363,14 +17354,14 @@
         <v>276</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>21</v>
@@ -17419,7 +17410,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17434,13 +17425,13 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>21</v>
@@ -17451,10 +17442,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17566,10 +17557,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17683,10 +17674,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17712,16 +17703,16 @@
         <v>166</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>571</v>
+        <v>487</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>21</v>
@@ -17749,10 +17740,10 @@
         <v>187</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>21</v>
@@ -17770,7 +17761,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17791,7 +17782,7 @@
         <v>21</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>21</v>
@@ -17802,10 +17793,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17831,16 +17822,16 @@
         <v>295</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>21</v>
@@ -17868,10 +17859,10 @@
         <v>148</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>21</v>
@@ -17889,7 +17880,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17910,21 +17901,21 @@
         <v>21</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17950,16 +17941,16 @@
         <v>132</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>21</v>
@@ -17972,7 +17963,7 @@
         <v>21</v>
       </c>
       <c r="T128" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="U128" t="s" s="2">
         <v>21</v>
@@ -18008,7 +17999,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18029,21 +18020,21 @@
         <v>21</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO128" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18069,13 +18060,13 @@
         <v>104</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -18089,7 +18080,7 @@
         <v>21</v>
       </c>
       <c r="T129" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="U129" t="s" s="2">
         <v>21</v>
@@ -18125,7 +18116,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18146,21 +18137,21 @@
         <v>21</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO129" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18186,10 +18177,10 @@
         <v>231</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18240,7 +18231,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18261,21 +18252,21 @@
         <v>21</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18298,16 +18289,16 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18357,7 +18348,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18378,21 +18369,21 @@
         <v>21</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18418,13 +18409,13 @@
         <v>295</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18453,10 +18444,10 @@
         <v>156</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>21</v>
@@ -18474,7 +18465,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18495,7 +18486,7 @@
         <v>21</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>21</v>
@@ -18506,10 +18497,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18532,13 +18523,13 @@
         <v>21</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18589,7 +18580,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18604,13 +18595,13 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>21</v>
@@ -18621,10 +18612,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18647,13 +18638,13 @@
         <v>21</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18704,7 +18695,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18719,13 +18710,13 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>21</v>
@@ -18736,10 +18727,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18851,10 +18842,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18968,10 +18959,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18994,16 +18985,16 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -19053,7 +19044,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19074,7 +19065,7 @@
         <v>21</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>21</v>
@@ -19085,10 +19076,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19114,10 +19105,10 @@
         <v>241</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19168,7 +19159,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19189,7 +19180,7 @@
         <v>21</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>21</v>
@@ -19200,10 +19191,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19229,10 +19220,10 @@
         <v>269</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19283,7 +19274,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>90</v>
@@ -19304,7 +19295,7 @@
         <v>21</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>21</v>
@@ -19315,10 +19306,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19341,16 +19332,16 @@
         <v>21</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19388,17 +19379,17 @@
         <v>21</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AC140" s="2"/>
       <c r="AD140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19413,13 +19404,13 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>21</v>
@@ -19430,13 +19421,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>21</v>
@@ -19458,16 +19449,16 @@
         <v>21</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19517,7 +19508,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19532,13 +19523,13 @@
         <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>21</v>
@@ -19549,13 +19540,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>21</v>
@@ -19577,16 +19568,16 @@
         <v>21</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19636,7 +19627,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19648,16 +19639,16 @@
         <v>21</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>21</v>
@@ -19668,10 +19659,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19694,13 +19685,13 @@
         <v>21</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19751,7 +19742,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19769,10 +19760,10 @@
         <v>21</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>21</v>
@@ -19783,10 +19774,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19898,10 +19889,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20015,10 +20006,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20044,7 +20035,7 @@
         <v>111</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M146" t="s" s="2">
         <v>209</v>
@@ -20098,7 +20089,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20130,10 +20121,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20156,16 +20147,16 @@
         <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -20215,7 +20206,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20236,7 +20227,7 @@
         <v>21</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>21</v>
@@ -20247,10 +20238,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20362,10 +20353,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20479,14 +20470,14 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -20508,16 +20499,16 @@
         <v>111</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N150" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>21</v>
@@ -20566,7 +20557,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20598,10 +20589,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20624,13 +20615,13 @@
         <v>21</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -20681,7 +20672,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20693,7 +20684,7 @@
         <v>21</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>21</v>
@@ -20702,7 +20693,7 @@
         <v>21</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>21</v>
@@ -20713,10 +20704,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20739,13 +20730,13 @@
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20796,7 +20787,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20817,7 +20808,7 @@
         <v>21</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>21</v>
@@ -20828,10 +20819,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20854,13 +20845,13 @@
         <v>21</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -20911,7 +20902,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20932,7 +20923,7 @@
         <v>21</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>21</v>
@@ -20943,10 +20934,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20972,16 +20963,16 @@
         <v>231</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>21</v>
@@ -21030,7 +21021,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21048,10 +21039,10 @@
         <v>21</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>21</v>
@@ -21062,10 +21053,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21177,10 +21168,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21294,10 +21285,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21411,10 +21402,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21530,10 +21521,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21556,16 +21547,16 @@
         <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -21615,7 +21606,7 @@
         <v>21</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21633,24 +21624,24 @@
         <v>21</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21673,13 +21664,13 @@
         <v>21</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21730,7 +21721,7 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21742,30 +21733,30 @@
         <v>21</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21877,10 +21868,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21994,10 +21985,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22020,19 +22011,19 @@
         <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>21</v>
@@ -22081,7 +22072,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22102,21 +22093,21 @@
         <v>21</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22142,20 +22133,20 @@
         <v>166</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q164" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="R164" t="s" s="2">
         <v>21</v>
@@ -22179,10 +22170,10 @@
         <v>187</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>21</v>
@@ -22200,7 +22191,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22221,21 +22212,21 @@
         <v>21</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22261,14 +22252,14 @@
         <v>104</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>21</v>
@@ -22317,7 +22308,7 @@
         <v>21</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22338,21 +22329,21 @@
         <v>21</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22378,14 +22369,14 @@
         <v>132</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>21</v>
@@ -22434,7 +22425,7 @@
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22443,7 +22434,7 @@
         <v>90</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>102</v>
@@ -22455,21 +22446,21 @@
         <v>21</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22495,16 +22486,16 @@
         <v>166</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>21</v>
@@ -22553,7 +22544,7 @@
         <v>21</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22574,21 +22565,21 @@
         <v>21</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22611,16 +22602,16 @@
         <v>21</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -22670,7 +22661,7 @@
         <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22688,10 +22679,10 @@
         <v>21</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>21</v>
@@ -22702,10 +22693,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22728,13 +22719,13 @@
         <v>21</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -22785,7 +22776,7 @@
         <v>21</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22806,10 +22797,10 @@
         <v>21</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>21</v>
@@ -22817,10 +22808,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22843,13 +22834,13 @@
         <v>21</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -22900,7 +22891,7 @@
         <v>21</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22918,10 +22909,10 @@
         <v>21</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>21</v>
@@ -22932,10 +22923,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23047,10 +23038,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23164,14 +23155,14 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
@@ -23193,16 +23184,16 @@
         <v>111</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N173" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>21</v>
@@ -23251,7 +23242,7 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23283,10 +23274,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23309,16 +23300,16 @@
         <v>21</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23347,10 +23338,10 @@
         <v>156</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>21</v>
@@ -23368,7 +23359,7 @@
         <v>21</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>90</v>
@@ -23386,24 +23377,24 @@
         <v>21</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23429,10 +23420,10 @@
         <v>295</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -23462,10 +23453,10 @@
         <v>156</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>21</v>
@@ -23483,7 +23474,7 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23501,24 +23492,24 @@
         <v>21</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23541,13 +23532,13 @@
         <v>21</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23598,7 +23589,7 @@
         <v>21</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23613,13 +23604,13 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>21</v>
@@ -23630,14 +23621,14 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
@@ -23656,16 +23647,16 @@
         <v>21</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23715,7 +23706,7 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23736,7 +23727,7 @@
         <v>21</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>21</v>
@@ -23747,10 +23738,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23773,16 +23764,16 @@
         <v>21</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23832,7 +23823,7 @@
         <v>21</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23847,13 +23838,13 @@
         <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -643,7 +643,7 @@
 </t>
   </si>
   <si>
-    <t>TODO</t>
+    <t>Es sind nur die hier definierten contained Medication-Ressourcen zulässig. Contained (eingebettete) Ressourcen werden nicht separat versioniert, sondern ausschließlich im Rahmen der übergeordneten Ressource versioniert.</t>
   </si>
   <si>
     <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
@@ -1374,7 +1374,7 @@
 </t>
   </si>
   <si>
-    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als Conditional Reference dokumentiert. Muss mit dem Planeintrag übereinstimmen.</t>
+    <t>Das Arzneimittel wird in einer contained Medication Ressource oder als Conditional Reference dokumentiert. Muss bei der Erstellung mit der medication im zugehörigen Planeintrag übereinstimmen.</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
@@ -2178,7 +2178,7 @@
 </t>
   </si>
   <si>
-    <t>Angabe der Dosierinformationen strukturiert oder als Freitext.</t>
+    <t>Angabe der Dosierinformationen strukturiert oder als Freitext. Muss bei der Erstellung mit der dosageInstruction im zugehörigen Planeintrag übereinstimmen.</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -2234,7 +2234,7 @@
 </t>
   </si>
   <si>
-    <t>Informationen zur geplanten Abgabe des Arzneimittels.</t>
+    <t>Informationen zur vorgesehenen Abgabe des Arzneimittels.</t>
   </si>
   <si>
     <t>Indicates the specific details for the dispense or medication supply part of a medication request (also known as a Medication Prescription or Medication Order).  Note that this information is not always sent with the order.  There may be in some settings (e.g. hospitals) institutional or system support for completing the dispense details in the pharmacy department.</t>
@@ -2347,7 +2347,7 @@
     <t>MedicationRequest.dispenseRequest.validityPeriod</t>
   </si>
   <si>
-    <t>Gültigkeitszeitraum einer Geplante Abgabe (abhängig von der Rezeptart).</t>
+    <t>Gültigkeitszeitraum der Geplante Abgabe (u.a. abhängig von der Rezeptart).</t>
   </si>
   <si>
     <t>This indicates the validity period of a prescription (stale dating the Prescription).</t>
@@ -2384,7 +2384,7 @@
 </t>
   </si>
   <si>
-    <t>Die Anzahl der weiteren möglichen Einlösungen (abhängig von der Rezeptart).</t>
+    <t>Die Anzahl der möglichen weiteren Einlösungen (u.a. abhängig von der Rezeptart).</t>
   </si>
   <si>
     <t>An integer indicating the number of times, in addition to the original dispense, (aka refills or repeats) that the patient can receive the prescribed medication. Usage Notes: This integer does not include the original order dispense. This means that if an order indicates dispense 30 tablets plus "3 repeats", then the order can be dispensed a total of 4 times and the patient can receive a total of 120 tablets.  A prescriber may explicitly say that zero refills are permitted after the initial dispense.</t>
@@ -2405,7 +2405,7 @@
     <t>MedicationRequest.dispenseRequest.quantity</t>
   </si>
   <si>
-    <t>Bereitzustellende Menge bei jeder Abgabe bereitgestellt.</t>
+    <t>Bereitzustellende Menge bei jeder Einlösung.</t>
   </si>
   <si>
     <t>The amount that is to be dispensed for one fill.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2012,7 +2012,7 @@
     <t>MedicationRequest.groupIdentifier</t>
   </si>
   <si>
-    <t>Der e-Med GroupIdentifier bildet die Rezept-Klammer. Geplante Abgaben, die demselben e-Rezept zugeordnet sind, führen denselben e-Med GroupIdentifier.</t>
+    <t>Der "e-Med GroupIdentifier" bildet die Rezept-Klammer. Geplante Abgaben, die demselben e-Rezept zugeordnet sind, führen denselben e-Med GroupIdentifier.</t>
   </si>
   <si>
     <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -836,7 +836,7 @@
 </t>
   </si>
   <si>
-    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definiert Regeln befüllt.</t>
+    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definierten Regeln befüllt..</t>
   </si>
   <si>
     <t>R5: `MedicationRequest.renderedDosageInstruction` (new:markdown)</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1766,7 +1766,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole)
 </t>
   </si>
   <si>
@@ -3053,7 +3053,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="199.48828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="180.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil einer "Geplanten Abgabe" eines Arzneimittels aus dem Medikationsplan.</t>
+    <t>Profil einer Geplanten Abgabe eines Arzneimittels aus dem Medikationsplan.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8211,7 +8211,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>331</v>
       </c>
@@ -8224,13 +8224,13 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
@@ -9619,7 +9619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>404</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
@@ -14890,7 +14890,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>21</v>
@@ -17688,7 +17688,7 @@
         <v>80</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -643,7 +643,7 @@
 </t>
   </si>
   <si>
-    <t>Es sind nur die hier definierten contained Medication-Ressourcen zulässig. Contained (eingebettete) Ressourcen werden nicht separat versioniert, sondern ausschließlich im Rahmen der übergeordneten Ressource versioniert.</t>
+    <t>Definition of a Medication</t>
   </si>
   <si>
     <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -568,7 +568,7 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
+    <t>Narrative - wird immer durch die Fachanwendung generiert.</t>
   </si>
   <si>
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>90</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -22338,7 +22338,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
         <v>799</v>
       </c>
@@ -22357,7 +22357,7 @@
         <v>90</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="869">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1370,7 +1370,7 @@
     <t>MedicationRequest.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-standard-medikation|https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medication-magistrale-zubereitung)
 </t>
   </si>
   <si>
@@ -2040,6 +2040,9 @@
   </si>
   <si>
     <t>MedicationRequest.groupIdentifier.system</t>
+  </si>
+  <si>
+    <t>http://tbd.com</t>
   </si>
   <si>
     <t>MedicationRequest.groupIdentifier.value</t>
@@ -3053,7 +3056,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="180.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="168.89453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -17960,7 +17963,7 @@
         <v>21</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>21</v>
+        <v>650</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>509</v>
@@ -18031,10 +18034,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18148,10 +18151,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18263,10 +18266,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18380,10 +18383,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18409,13 +18412,13 @@
         <v>295</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18444,10 +18447,10 @@
         <v>156</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>21</v>
@@ -18465,7 +18468,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18486,7 +18489,7 @@
         <v>21</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>21</v>
@@ -18497,10 +18500,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18523,13 +18526,13 @@
         <v>21</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18580,7 +18583,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18595,13 +18598,13 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>21</v>
@@ -18612,10 +18615,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18638,13 +18641,13 @@
         <v>21</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18695,7 +18698,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18710,13 +18713,13 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>21</v>
@@ -18727,10 +18730,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18842,10 +18845,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18959,10 +18962,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18985,16 +18988,16 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -19044,7 +19047,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19065,7 +19068,7 @@
         <v>21</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>21</v>
@@ -19076,10 +19079,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19105,10 +19108,10 @@
         <v>241</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19159,7 +19162,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19180,7 +19183,7 @@
         <v>21</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>21</v>
@@ -19191,10 +19194,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19220,10 +19223,10 @@
         <v>269</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19274,7 +19277,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>90</v>
@@ -19295,7 +19298,7 @@
         <v>21</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>21</v>
@@ -19306,10 +19309,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19332,16 +19335,16 @@
         <v>21</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19379,17 +19382,17 @@
         <v>21</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AC140" s="2"/>
       <c r="AD140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19404,13 +19407,13 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>21</v>
@@ -19421,13 +19424,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>21</v>
@@ -19449,16 +19452,16 @@
         <v>21</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19508,7 +19511,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19523,13 +19526,13 @@
         <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>21</v>
@@ -19540,13 +19543,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>21</v>
@@ -19568,16 +19571,16 @@
         <v>21</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19627,7 +19630,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19639,16 +19642,16 @@
         <v>21</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>21</v>
@@ -19659,10 +19662,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19685,13 +19688,13 @@
         <v>21</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19742,7 +19745,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19760,10 +19763,10 @@
         <v>21</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>21</v>
@@ -19774,10 +19777,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19889,10 +19892,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20006,10 +20009,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20035,7 +20038,7 @@
         <v>111</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M146" t="s" s="2">
         <v>209</v>
@@ -20089,7 +20092,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20121,10 +20124,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20147,16 +20150,16 @@
         <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -20206,7 +20209,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20227,7 +20230,7 @@
         <v>21</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>21</v>
@@ -20238,10 +20241,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20353,10 +20356,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20470,14 +20473,14 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -20499,16 +20502,16 @@
         <v>111</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N150" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>21</v>
@@ -20557,7 +20560,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20589,10 +20592,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20615,13 +20618,13 @@
         <v>21</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -20672,7 +20675,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20684,7 +20687,7 @@
         <v>21</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>21</v>
@@ -20693,7 +20696,7 @@
         <v>21</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>21</v>
@@ -20704,10 +20707,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20730,13 +20733,13 @@
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20787,7 +20790,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20808,7 +20811,7 @@
         <v>21</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>21</v>
@@ -20819,10 +20822,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20845,13 +20848,13 @@
         <v>21</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -20902,7 +20905,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20923,7 +20926,7 @@
         <v>21</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>21</v>
@@ -20934,10 +20937,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20963,16 +20966,16 @@
         <v>231</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>21</v>
@@ -21021,7 +21024,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21039,10 +21042,10 @@
         <v>21</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>21</v>
@@ -21053,10 +21056,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21168,10 +21171,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21285,10 +21288,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21402,10 +21405,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21521,10 +21524,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21547,16 +21550,16 @@
         <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -21606,7 +21609,7 @@
         <v>21</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21624,24 +21627,24 @@
         <v>21</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21664,13 +21667,13 @@
         <v>21</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21721,7 +21724,7 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21733,30 +21736,30 @@
         <v>21</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO160" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21868,10 +21871,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21985,10 +21988,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22011,19 +22014,19 @@
         <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>21</v>
@@ -22072,7 +22075,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22093,21 +22096,21 @@
         <v>21</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22133,20 +22136,20 @@
         <v>166</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q164" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="R164" t="s" s="2">
         <v>21</v>
@@ -22170,10 +22173,10 @@
         <v>187</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>21</v>
@@ -22191,7 +22194,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22212,21 +22215,21 @@
         <v>21</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22252,14 +22255,14 @@
         <v>104</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>21</v>
@@ -22308,7 +22311,7 @@
         <v>21</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22329,21 +22332,21 @@
         <v>21</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22369,14 +22372,14 @@
         <v>132</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>21</v>
@@ -22425,7 +22428,7 @@
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22434,7 +22437,7 @@
         <v>90</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>102</v>
@@ -22446,21 +22449,21 @@
         <v>21</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22486,16 +22489,16 @@
         <v>166</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>21</v>
@@ -22544,7 +22547,7 @@
         <v>21</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22565,21 +22568,21 @@
         <v>21</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22602,16 +22605,16 @@
         <v>21</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -22661,7 +22664,7 @@
         <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22679,10 +22682,10 @@
         <v>21</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>21</v>
@@ -22693,10 +22696,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22722,10 +22725,10 @@
         <v>528</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -22776,7 +22779,7 @@
         <v>21</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22797,7 +22800,7 @@
         <v>21</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>599</v>
@@ -22808,10 +22811,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22834,13 +22837,13 @@
         <v>21</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -22891,7 +22894,7 @@
         <v>21</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22909,10 +22912,10 @@
         <v>21</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>21</v>
@@ -22923,10 +22926,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23038,10 +23041,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23155,14 +23158,14 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
@@ -23184,16 +23187,16 @@
         <v>111</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N173" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>21</v>
@@ -23242,7 +23245,7 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23274,10 +23277,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23300,16 +23303,16 @@
         <v>21</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23338,10 +23341,10 @@
         <v>156</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>21</v>
@@ -23359,7 +23362,7 @@
         <v>21</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>90</v>
@@ -23377,24 +23380,24 @@
         <v>21</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23420,10 +23423,10 @@
         <v>295</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -23453,10 +23456,10 @@
         <v>156</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>21</v>
@@ -23474,7 +23477,7 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23492,24 +23495,24 @@
         <v>21</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23532,13 +23535,13 @@
         <v>21</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23589,7 +23592,7 @@
         <v>21</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23604,13 +23607,13 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>21</v>
@@ -23621,14 +23624,14 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
@@ -23647,16 +23650,16 @@
         <v>21</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23706,7 +23709,7 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23727,7 +23730,7 @@
         <v>21</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>21</v>
@@ -23738,10 +23741,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23764,16 +23767,16 @@
         <v>21</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23823,7 +23826,7 @@
         <v>21</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23838,13 +23841,13 @@
         <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AL178" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5445,7 +5445,7 @@
         <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
@@ -7769,7 +7769,7 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -923,7 +923,7 @@
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/GeplanteAbgabeStatusVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-geplanteabgabestatus-vs</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -1044,7 +1044,7 @@
     <t>Kategorie zur Unterscheidung einer Geplanten Abgabe von einem Planeintrag (beide haben intent order).</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedicationRequestCategoryVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-medicationrequestcategory-vs</t>
   </si>
   <si>
     <t>MedicationRequest.category:mrcategory.id</t>
@@ -1116,7 +1116,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/MedicationRequestCategoryCS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/at-elga-emed-codesystem-medicationrequestcategory-cs</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -3071,7 +3071,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="138.53125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="75.7265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="50.23046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6596" uniqueCount="868">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -836,7 +836,7 @@
 </t>
   </si>
   <si>
-    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definierten Regeln befüllt..</t>
+    <t>Vollständige textuelle Zusammenfassung der Dosierungsanweisungen - wird von der Fachanwendung anhand der definierten Regeln befüllt.</t>
   </si>
   <si>
     <t>R5: `MedicationRequest.renderedDosageInstruction` (new:markdown)</t>
@@ -1307,9 +1307,6 @@
   </si>
   <si>
     <t>MedicationRequest.category:recipetype.text</t>
-  </si>
-  <si>
-    <t>Fachliche Begründung: TODO</t>
   </si>
   <si>
     <t>MedicationRequest.priority</t>
@@ -10593,7 +10590,7 @@
         <v>104</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="M65" t="s" s="2">
         <v>392</v>
@@ -10683,10 +10680,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10712,10 +10709,10 @@
         <v>166</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10745,11 +10742,11 @@
         <v>187</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
       </c>
@@ -10766,7 +10763,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10781,16 +10778,16 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AL66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>21</v>
@@ -10798,10 +10795,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10827,13 +10824,13 @@
         <v>381</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10883,7 +10880,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10904,7 +10901,7 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -10915,10 +10912,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10941,13 +10938,13 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10998,7 +10995,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -11019,7 +11016,7 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -11030,10 +11027,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11056,16 +11053,16 @@
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11115,7 +11112,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>90</v>
@@ -11130,27 +11127,27 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AL69" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AL69" t="s" s="2">
+      <c r="AM69" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>442</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11262,10 +11259,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11379,10 +11376,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11408,13 +11405,13 @@
         <v>104</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11464,16 +11461,16 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI72" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11496,10 +11493,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11525,13 +11522,13 @@
         <v>132</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11560,28 +11557,28 @@
         <v>148</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="Z73" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="Z73" t="s" s="2">
+      <c r="AA73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11613,10 +11610,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11642,13 +11639,13 @@
         <v>276</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11698,7 +11695,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11719,7 +11716,7 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -11730,10 +11727,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11759,13 +11756,13 @@
         <v>104</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11815,7 +11812,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11847,10 +11844,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11873,16 +11870,16 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11932,7 +11929,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>90</v>
@@ -11947,27 +11944,27 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AL76" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="AM76" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AN76" t="s" s="2">
+      <c r="AO76" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>478</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12079,10 +12076,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12196,10 +12193,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12225,13 +12222,13 @@
         <v>104</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12281,16 +12278,16 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI79" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>102</v>
@@ -12313,10 +12310,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12342,13 +12339,13 @@
         <v>132</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12377,28 +12374,28 @@
         <v>148</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="Z80" t="s" s="2">
+      <c r="AA80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12430,10 +12427,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12459,13 +12456,13 @@
         <v>276</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12515,7 +12512,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12536,7 +12533,7 @@
         <v>21</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -12547,10 +12544,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12662,10 +12659,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12779,10 +12776,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12808,16 +12805,16 @@
         <v>166</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -12845,28 +12842,28 @@
         <v>187</v>
       </c>
       <c r="Y84" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="Z84" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="Z84" t="s" s="2">
+      <c r="AA84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF84" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12887,7 +12884,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -12898,10 +12895,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12927,16 +12924,16 @@
         <v>295</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N85" t="s" s="2">
+      <c r="O85" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -12964,28 +12961,28 @@
         <v>148</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="Z85" t="s" s="2">
+      <c r="AA85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13006,21 +13003,21 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13046,16 +13043,16 @@
         <v>132</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -13068,43 +13065,43 @@
         <v>21</v>
       </c>
       <c r="T86" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13125,21 +13122,21 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>512</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13165,13 +13162,13 @@
         <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13185,43 +13182,43 @@
         <v>21</v>
       </c>
       <c r="T87" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13242,21 +13239,21 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO87" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>520</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13282,10 +13279,10 @@
         <v>231</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13336,7 +13333,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13357,21 +13354,21 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>526</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13394,16 +13391,16 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13453,7 +13450,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13474,21 +13471,21 @@
         <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>534</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13514,13 +13511,13 @@
         <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13570,7 +13567,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13602,10 +13599,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13628,16 +13625,16 @@
         <v>21</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13687,7 +13684,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13702,27 +13699,27 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>291</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="AN91" t="s" s="2">
+      <c r="AO91" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>544</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13745,13 +13742,13 @@
         <v>21</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13802,7 +13799,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13817,16 +13814,16 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AL92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>550</v>
-      </c>
       <c r="AN92" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>21</v>
@@ -13834,10 +13831,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13863,10 +13860,10 @@
         <v>241</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13917,7 +13914,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13932,27 +13929,27 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AL93" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="AL93" t="s" s="2">
+      <c r="AM93" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>558</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13975,13 +13972,13 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14032,7 +14029,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14047,16 +14044,16 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>21</v>
@@ -14064,10 +14061,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14179,10 +14176,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14296,10 +14293,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14325,13 +14322,13 @@
         <v>104</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14381,16 +14378,16 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI97" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>102</v>
@@ -14413,10 +14410,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14442,13 +14439,13 @@
         <v>132</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14477,28 +14474,28 @@
         <v>148</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="Z98" t="s" s="2">
+      <c r="AA98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14530,10 +14527,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14559,13 +14556,13 @@
         <v>276</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14615,7 +14612,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14636,7 +14633,7 @@
         <v>21</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>21</v>
@@ -14647,10 +14644,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14762,10 +14759,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14879,10 +14876,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14908,16 +14905,16 @@
         <v>166</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
@@ -14945,28 +14942,28 @@
         <v>187</v>
       </c>
       <c r="Y102" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="Z102" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="Z102" t="s" s="2">
+      <c r="AA102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14987,7 +14984,7 @@
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>21</v>
@@ -14998,10 +14995,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15027,16 +15024,16 @@
         <v>295</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
@@ -15064,28 +15061,28 @@
         <v>148</v>
       </c>
       <c r="Y103" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="Z103" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="Z103" t="s" s="2">
+      <c r="AA103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15106,21 +15103,21 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15146,16 +15143,16 @@
         <v>132</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
@@ -15168,43 +15165,43 @@
         <v>21</v>
       </c>
       <c r="T104" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15225,21 +15222,21 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO104" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>512</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15265,13 +15262,13 @@
         <v>104</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15285,43 +15282,43 @@
         <v>21</v>
       </c>
       <c r="T105" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF105" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15342,21 +15339,21 @@
         <v>21</v>
       </c>
       <c r="AM105" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO105" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>520</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15382,10 +15379,10 @@
         <v>231</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15436,7 +15433,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15457,21 +15454,21 @@
         <v>21</v>
       </c>
       <c r="AM106" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO106" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>526</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15494,16 +15491,16 @@
         <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15553,7 +15550,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15574,21 +15571,21 @@
         <v>21</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO107" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>534</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15614,13 +15611,13 @@
         <v>104</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15670,7 +15667,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15702,10 +15699,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15728,13 +15725,13 @@
         <v>21</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15785,7 +15782,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15800,16 +15797,16 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="AL109" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM109" t="s" s="2">
+      <c r="AN109" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>21</v>
@@ -15817,10 +15814,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15846,13 +15843,13 @@
         <v>295</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15881,11 +15878,11 @@
         <v>156</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="Z110" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="Z110" t="s" s="2">
-        <v>591</v>
-      </c>
       <c r="AA110" t="s" s="2">
         <v>21</v>
       </c>
@@ -15902,7 +15899,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15917,13 +15914,13 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM110" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>21</v>
@@ -15934,10 +15931,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15960,13 +15957,13 @@
         <v>21</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16017,7 +16014,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16038,10 +16035,10 @@
         <v>21</v>
       </c>
       <c r="AM111" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>21</v>
@@ -16049,10 +16046,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16078,13 +16075,13 @@
         <v>295</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16113,11 +16110,11 @@
         <v>156</v>
       </c>
       <c r="Y112" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="Z112" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="Z112" t="s" s="2">
-        <v>605</v>
-      </c>
       <c r="AA112" t="s" s="2">
         <v>21</v>
       </c>
@@ -16134,7 +16131,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16149,27 +16146,27 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AL112" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="AL112" t="s" s="2">
+      <c r="AM112" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="AM112" t="s" s="2">
+      <c r="AN112" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="AN112" t="s" s="2">
+      <c r="AO112" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>610</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16192,16 +16189,16 @@
         <v>21</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16251,7 +16248,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16266,16 +16263,16 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>291</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>21</v>
@@ -16283,10 +16280,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16309,13 +16306,13 @@
         <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16366,7 +16363,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16381,13 +16378,13 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM114" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>21</v>
@@ -16398,10 +16395,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16427,10 +16424,10 @@
         <v>132</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16481,7 +16478,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16502,7 +16499,7 @@
         <v>21</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>21</v>
@@ -16513,10 +16510,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16539,13 +16536,13 @@
         <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16596,7 +16593,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16611,13 +16608,13 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM116" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>21</v>
@@ -16628,10 +16625,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16743,10 +16740,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16860,10 +16857,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16889,13 +16886,13 @@
         <v>104</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16945,16 +16942,16 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI119" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>102</v>
@@ -16977,10 +16974,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17006,13 +17003,13 @@
         <v>132</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17041,28 +17038,28 @@
         <v>148</v>
       </c>
       <c r="Y120" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="Z120" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="Z120" t="s" s="2">
+      <c r="AA120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF120" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17094,10 +17091,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17123,13 +17120,13 @@
         <v>276</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17179,7 +17176,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17200,7 +17197,7 @@
         <v>21</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>21</v>
@@ -17211,10 +17208,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17240,13 +17237,13 @@
         <v>104</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17296,7 +17293,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17328,10 +17325,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17357,14 +17354,14 @@
         <v>276</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>21</v>
@@ -17413,7 +17410,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17428,13 +17425,13 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM123" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>21</v>
@@ -17445,10 +17442,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17560,10 +17557,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17677,10 +17674,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17706,16 +17703,16 @@
         <v>166</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="N126" t="s" s="2">
+      <c r="O126" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>21</v>
@@ -17743,28 +17740,28 @@
         <v>187</v>
       </c>
       <c r="Y126" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="Z126" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="Z126" t="s" s="2">
+      <c r="AA126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17785,7 +17782,7 @@
         <v>21</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>21</v>
@@ -17796,10 +17793,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17825,16 +17822,16 @@
         <v>295</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>21</v>
@@ -17862,28 +17859,28 @@
         <v>148</v>
       </c>
       <c r="Y127" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="Z127" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="Z127" t="s" s="2">
+      <c r="AA127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF127" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17904,21 +17901,21 @@
         <v>21</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17944,16 +17941,16 @@
         <v>132</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>21</v>
@@ -17963,46 +17960,46 @@
         <v>21</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="T128" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF128" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18023,21 +18020,21 @@
         <v>21</v>
       </c>
       <c r="AM128" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO128" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>512</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18063,13 +18060,13 @@
         <v>104</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -18083,43 +18080,43 @@
         <v>21</v>
       </c>
       <c r="T129" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF129" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18140,21 +18137,21 @@
         <v>21</v>
       </c>
       <c r="AM129" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO129" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>520</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18180,10 +18177,10 @@
         <v>231</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18234,7 +18231,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18255,21 +18252,21 @@
         <v>21</v>
       </c>
       <c r="AM130" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO130" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>526</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18292,16 +18289,16 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L131" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L131" t="s" s="2">
+      <c r="M131" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M131" t="s" s="2">
+      <c r="N131" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18351,7 +18348,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18372,21 +18369,21 @@
         <v>21</v>
       </c>
       <c r="AM131" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO131" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>534</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18412,13 +18409,13 @@
         <v>295</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M132" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18447,11 +18444,11 @@
         <v>156</v>
       </c>
       <c r="Y132" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="Z132" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="Z132" t="s" s="2">
-        <v>659</v>
-      </c>
       <c r="AA132" t="s" s="2">
         <v>21</v>
       </c>
@@ -18468,7 +18465,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18489,7 +18486,7 @@
         <v>21</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>21</v>
@@ -18500,10 +18497,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18526,13 +18523,13 @@
         <v>21</v>
       </c>
       <c r="K133" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="L133" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18583,7 +18580,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18598,13 +18595,13 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM133" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>21</v>
@@ -18615,10 +18612,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18641,13 +18638,13 @@
         <v>21</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -18698,7 +18695,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18713,13 +18710,13 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AL134" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="AL134" t="s" s="2">
+      <c r="AM134" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>21</v>
@@ -18730,10 +18727,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18845,10 +18842,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18962,10 +18959,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18988,16 +18985,16 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -19047,7 +19044,7 @@
         <v>21</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19068,7 +19065,7 @@
         <v>21</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>21</v>
@@ -19079,10 +19076,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19108,10 +19105,10 @@
         <v>241</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19162,7 +19159,7 @@
         <v>21</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19183,7 +19180,7 @@
         <v>21</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>21</v>
@@ -19194,10 +19191,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19223,10 +19220,10 @@
         <v>269</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19277,7 +19274,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>90</v>
@@ -19298,7 +19295,7 @@
         <v>21</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>21</v>
@@ -19309,10 +19306,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19335,16 +19332,16 @@
         <v>21</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="L140" t="s" s="2">
+      <c r="M140" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -19382,17 +19379,17 @@
         <v>21</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AC140" s="2"/>
       <c r="AD140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19407,13 +19404,13 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM140" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AL140" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>21</v>
@@ -19424,13 +19421,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="C141" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="C141" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>21</v>
@@ -19452,16 +19449,16 @@
         <v>21</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="L141" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="L141" t="s" s="2">
-        <v>705</v>
-      </c>
       <c r="M141" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="N141" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19511,7 +19508,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19526,13 +19523,13 @@
         <v>102</v>
       </c>
       <c r="AK141" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AL141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM141" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AL141" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>21</v>
@@ -19543,13 +19540,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="C142" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="C142" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>21</v>
@@ -19571,16 +19568,16 @@
         <v>21</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="M142" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="N142" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19630,7 +19627,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19642,16 +19639,16 @@
         <v>21</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AK142" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM142" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>21</v>
@@ -19662,10 +19659,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19688,13 +19685,13 @@
         <v>21</v>
       </c>
       <c r="K143" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="L143" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="L143" t="s" s="2">
+      <c r="M143" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -19745,7 +19742,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19763,10 +19760,10 @@
         <v>21</v>
       </c>
       <c r="AL143" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="AM143" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>21</v>
@@ -19777,10 +19774,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19892,10 +19889,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20009,10 +20006,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20038,7 +20035,7 @@
         <v>111</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="M146" t="s" s="2">
         <v>209</v>
@@ -20092,7 +20089,7 @@
         <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20124,10 +20121,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20150,16 +20147,16 @@
         <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>723</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>724</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -20209,7 +20206,7 @@
         <v>21</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20230,7 +20227,7 @@
         <v>21</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>21</v>
@@ -20241,10 +20238,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20356,10 +20353,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20473,14 +20470,14 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -20502,16 +20499,16 @@
         <v>111</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="N150" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>21</v>
@@ -20560,7 +20557,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20592,10 +20589,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20618,13 +20615,13 @@
         <v>21</v>
       </c>
       <c r="K151" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="L151" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="L151" t="s" s="2">
+      <c r="M151" t="s" s="2">
         <v>735</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>736</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -20675,7 +20672,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -20687,16 +20684,16 @@
         <v>21</v>
       </c>
       <c r="AJ151" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM151" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="AK151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL151" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>21</v>
@@ -20707,10 +20704,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20733,13 +20730,13 @@
         <v>21</v>
       </c>
       <c r="K152" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="L152" t="s" s="2">
         <v>740</v>
       </c>
-      <c r="L152" t="s" s="2">
+      <c r="M152" t="s" s="2">
         <v>741</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>742</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20790,7 +20787,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20811,7 +20808,7 @@
         <v>21</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>21</v>
@@ -20822,10 +20819,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20848,13 +20845,13 @@
         <v>21</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -20905,7 +20902,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -20926,7 +20923,7 @@
         <v>21</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>21</v>
@@ -20937,10 +20934,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20966,16 +20963,16 @@
         <v>231</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="M154" t="s" s="2">
         <v>748</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>749</v>
       </c>
-      <c r="N154" t="s" s="2">
+      <c r="O154" t="s" s="2">
         <v>750</v>
-      </c>
-      <c r="O154" t="s" s="2">
-        <v>751</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>21</v>
@@ -21024,7 +21021,7 @@
         <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21042,10 +21039,10 @@
         <v>21</v>
       </c>
       <c r="AL154" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="AM154" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>753</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>21</v>
@@ -21056,10 +21053,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21171,10 +21168,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21288,10 +21285,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21405,10 +21402,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21524,10 +21521,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21550,16 +21547,16 @@
         <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="L159" t="s" s="2">
         <v>759</v>
       </c>
-      <c r="L159" t="s" s="2">
+      <c r="M159" t="s" s="2">
         <v>760</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>761</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>762</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -21609,7 +21606,7 @@
         <v>21</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -21627,24 +21624,24 @@
         <v>21</v>
       </c>
       <c r="AL159" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="AM159" t="s" s="2">
         <v>763</v>
       </c>
-      <c r="AM159" t="s" s="2">
+      <c r="AN159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO159" t="s" s="2">
         <v>764</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO159" t="s" s="2">
-        <v>765</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21667,13 +21664,13 @@
         <v>21</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>767</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>768</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -21724,7 +21721,7 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21736,30 +21733,30 @@
         <v>21</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL160" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="AM160" t="s" s="2">
         <v>769</v>
       </c>
-      <c r="AM160" t="s" s="2">
+      <c r="AN160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO160" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO160" t="s" s="2">
-        <v>771</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21871,10 +21868,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21988,10 +21985,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22014,19 +22011,19 @@
         <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="L163" t="s" s="2">
         <v>775</v>
       </c>
-      <c r="L163" t="s" s="2">
+      <c r="M163" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="M163" t="s" s="2">
+      <c r="N163" t="s" s="2">
         <v>777</v>
       </c>
-      <c r="N163" t="s" s="2">
+      <c r="O163" t="s" s="2">
         <v>778</v>
-      </c>
-      <c r="O163" t="s" s="2">
-        <v>779</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>21</v>
@@ -22075,7 +22072,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22096,21 +22093,21 @@
         <v>21</v>
       </c>
       <c r="AM163" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="AN163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO163" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="AN163" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO163" t="s" s="2">
-        <v>782</v>
       </c>
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22136,20 +22133,20 @@
         <v>166</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>784</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>785</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="P164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q164" t="s" s="2">
         <v>786</v>
-      </c>
-      <c r="P164" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q164" t="s" s="2">
-        <v>787</v>
       </c>
       <c r="R164" t="s" s="2">
         <v>21</v>
@@ -22173,28 +22170,28 @@
         <v>187</v>
       </c>
       <c r="Y164" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="Z164" t="s" s="2">
         <v>788</v>
       </c>
-      <c r="Z164" t="s" s="2">
+      <c r="AA164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF164" t="s" s="2">
         <v>789</v>
-      </c>
-      <c r="AA164" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB164" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC164" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD164" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE164" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF164" t="s" s="2">
-        <v>790</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22215,21 +22212,21 @@
         <v>21</v>
       </c>
       <c r="AM164" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="AN164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO164" t="s" s="2">
         <v>791</v>
-      </c>
-      <c r="AN164" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO164" t="s" s="2">
-        <v>792</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22255,14 +22252,14 @@
         <v>104</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>21</v>
@@ -22311,7 +22308,7 @@
         <v>21</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22332,21 +22329,21 @@
         <v>21</v>
       </c>
       <c r="AM165" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="AN165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO165" t="s" s="2">
         <v>798</v>
-      </c>
-      <c r="AN165" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO165" t="s" s="2">
-        <v>799</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22372,14 +22369,14 @@
         <v>132</v>
       </c>
       <c r="L166" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>801</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>802</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>21</v>
@@ -22428,16 +22425,16 @@
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="AG166" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH166" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI166" t="s" s="2">
         <v>804</v>
-      </c>
-      <c r="AG166" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH166" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI166" t="s" s="2">
-        <v>805</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>102</v>
@@ -22449,21 +22446,21 @@
         <v>21</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22489,16 +22486,16 @@
         <v>166</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>808</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>809</v>
       </c>
-      <c r="N167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>810</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>21</v>
@@ -22547,7 +22544,7 @@
         <v>21</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22568,21 +22565,21 @@
         <v>21</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22605,16 +22602,16 @@
         <v>21</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>815</v>
       </c>
-      <c r="M168" t="s" s="2">
+      <c r="N168" t="s" s="2">
         <v>816</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>817</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -22664,7 +22661,7 @@
         <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -22682,10 +22679,10 @@
         <v>21</v>
       </c>
       <c r="AL168" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="AM168" t="s" s="2">
         <v>818</v>
-      </c>
-      <c r="AM168" t="s" s="2">
-        <v>819</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>21</v>
@@ -22696,10 +22693,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22722,13 +22719,13 @@
         <v>21</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -22779,7 +22776,7 @@
         <v>21</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -22800,10 +22797,10 @@
         <v>21</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>21</v>
@@ -22811,10 +22808,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22837,13 +22834,13 @@
         <v>21</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>825</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>826</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -22894,7 +22891,7 @@
         <v>21</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -22912,10 +22909,10 @@
         <v>21</v>
       </c>
       <c r="AL170" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="AM170" t="s" s="2">
         <v>827</v>
-      </c>
-      <c r="AM170" t="s" s="2">
-        <v>828</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>21</v>
@@ -22926,10 +22923,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23041,10 +23038,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23158,14 +23155,14 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
@@ -23187,16 +23184,16 @@
         <v>111</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="N173" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>21</v>
@@ -23245,7 +23242,7 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23277,10 +23274,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23303,16 +23300,16 @@
         <v>21</v>
       </c>
       <c r="K174" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="L174" t="s" s="2">
         <v>833</v>
       </c>
-      <c r="L174" t="s" s="2">
+      <c r="M174" t="s" s="2">
         <v>834</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="N174" t="s" s="2">
         <v>835</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>836</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23341,11 +23338,11 @@
         <v>156</v>
       </c>
       <c r="Y174" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="Z174" t="s" s="2">
         <v>837</v>
       </c>
-      <c r="Z174" t="s" s="2">
-        <v>838</v>
-      </c>
       <c r="AA174" t="s" s="2">
         <v>21</v>
       </c>
@@ -23362,7 +23359,7 @@
         <v>21</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>90</v>
@@ -23380,24 +23377,24 @@
         <v>21</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AM174" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="AN174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO174" t="s" s="2">
         <v>839</v>
-      </c>
-      <c r="AN174" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO174" t="s" s="2">
-        <v>840</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23423,10 +23420,10 @@
         <v>295</v>
       </c>
       <c r="L175" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="M175" t="s" s="2">
         <v>842</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>843</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -23456,11 +23453,11 @@
         <v>156</v>
       </c>
       <c r="Y175" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="Z175" t="s" s="2">
         <v>844</v>
       </c>
-      <c r="Z175" t="s" s="2">
-        <v>845</v>
-      </c>
       <c r="AA175" t="s" s="2">
         <v>21</v>
       </c>
@@ -23477,7 +23474,7 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23495,24 +23492,24 @@
         <v>21</v>
       </c>
       <c r="AL175" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="AM175" t="s" s="2">
         <v>846</v>
       </c>
-      <c r="AM175" t="s" s="2">
+      <c r="AN175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO175" t="s" s="2">
         <v>847</v>
-      </c>
-      <c r="AN175" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO175" t="s" s="2">
-        <v>848</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23535,13 +23532,13 @@
         <v>21</v>
       </c>
       <c r="K176" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="L176" t="s" s="2">
         <v>850</v>
       </c>
-      <c r="L176" t="s" s="2">
+      <c r="M176" t="s" s="2">
         <v>851</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>852</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23592,7 +23589,7 @@
         <v>21</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23607,13 +23604,13 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="AL176" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="AM176" t="s" s="2">
         <v>853</v>
-      </c>
-      <c r="AL176" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="AM176" t="s" s="2">
-        <v>854</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>21</v>
@@ -23624,14 +23621,14 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
@@ -23650,16 +23647,16 @@
         <v>21</v>
       </c>
       <c r="K177" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="L177" t="s" s="2">
         <v>857</v>
       </c>
-      <c r="L177" t="s" s="2">
+      <c r="M177" t="s" s="2">
         <v>858</v>
       </c>
-      <c r="M177" t="s" s="2">
+      <c r="N177" t="s" s="2">
         <v>859</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>860</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
@@ -23709,7 +23706,7 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23730,7 +23727,7 @@
         <v>21</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>21</v>
@@ -23741,10 +23738,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23767,16 +23764,16 @@
         <v>21</v>
       </c>
       <c r="K178" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="L178" t="s" s="2">
         <v>863</v>
       </c>
-      <c r="L178" t="s" s="2">
+      <c r="M178" t="s" s="2">
         <v>864</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>865</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>866</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23826,7 +23823,7 @@
         <v>21</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -23841,13 +23838,13 @@
         <v>102</v>
       </c>
       <c r="AK178" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="AL178" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM178" t="s" s="2">
         <v>867</v>
-      </c>
-      <c r="AL178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM178" t="s" s="2">
-        <v>868</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>At ELGA e-Medikation MedicationRequest Geplante Abgabe</t>
+    <t>AT ELGA e-Medikation MedicationRequest Geplante Abgabe</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
